--- a/docs/collections/sokuchigenkozu/metadata/data.xlsx
+++ b/docs/collections/sokuchigenkozu/metadata/data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="826">
   <si>
     <t>タイトル</t>
   </si>
@@ -179,55 +179,61 @@
     <t>uterms:rtf</t>
   </si>
   <si>
-    <t>測地原稿図(全)</t>
+    <t>測地原圖(全)</t>
+  </si>
+  <si>
+    <t>測地原圖</t>
+  </si>
+  <si>
+    <t>そくちげんず</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図</t>
+  </si>
+  <si>
+    <t>そくちげんこうず|いのうず</t>
+  </si>
+  <si>
+    <t>伊能忠敬</t>
+  </si>
+  <si>
+    <t>写</t>
+  </si>
+  <si>
+    <t>93枚</t>
+  </si>
+  <si>
+    <t>A00:4549</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b7d2dc7b-56a6-6182-0a85-90b5657b01ea.json</t>
+  </si>
+  <si>
+    <t>b7d2dc7b-56a6-6182-0a85-90b5657b01ea</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/sokuchigenkozu/</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/sokuchigenkozu/document/b7d2dc7b-56a6-6182-0a85-90b5657b01ea</t>
+  </si>
+  <si>
+    <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/318465a8ffdedda7a893319b5936bcce553c7a66.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/534102</t>
+  </si>
+  <si>
+    <t>東京大学総合図書館 General Library in the University of Tokyo, JAPAN</t>
+  </si>
+  <si>
+    <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
   </si>
   <si>
     <t>測地原稿図</t>
-  </si>
-  <si>
-    <t>伊能忠敬測地原図</t>
-  </si>
-  <si>
-    <t>いのうただたかそくちげんず</t>
-  </si>
-  <si>
-    <t>伊能忠敬</t>
-  </si>
-  <si>
-    <t>写</t>
-  </si>
-  <si>
-    <t>93枚</t>
-  </si>
-  <si>
-    <t>A00:4549</t>
-  </si>
-  <si>
-    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b7d2dc7b-56a6-6182-0a85-90b5657b01ea.json</t>
-  </si>
-  <si>
-    <t>b7d2dc7b-56a6-6182-0a85-90b5657b01ea</t>
-  </si>
-  <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/sokuchigenkozu/</t>
-  </si>
-  <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/sokuchigenkozu/document/b7d2dc7b-56a6-6182-0a85-90b5657b01ea</t>
-  </si>
-  <si>
-    <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
-  </si>
-  <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/318465a8ffdedda7a893319b5936bcce553c7a66.jpg</t>
-  </si>
-  <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/534102</t>
-  </si>
-  <si>
-    <t>東京大学総合図書館 General Library in the University of Tokyo, JAPAN</t>
-  </si>
-  <si>
-    <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
   </si>
   <si>
     <t>10000000</t>
@@ -3004,62 +3010,64 @@
       <c r="B3" t="s">
         <v>55</v>
       </c>
-      <c r="C3" t="s"/>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Q3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S3" t="s"/>
       <c r="T3" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="V3" t="s"/>
       <c r="W3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="X3" t="s"/>
       <c r="Y3" t="s"/>
@@ -3071,67 +3079,69 @@
     </row>
     <row r="4" spans="1:28">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
       </c>
-      <c r="C4" t="s"/>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S4" t="s"/>
       <c r="T4" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="V4" t="s"/>
       <c r="W4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="X4" t="s"/>
       <c r="Y4" t="s"/>
@@ -3143,67 +3153,69 @@
     </row>
     <row r="5" spans="1:28">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
       </c>
-      <c r="C5" t="s"/>
+      <c r="C5" t="s">
+        <v>56</v>
+      </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="L5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S5" t="s"/>
       <c r="T5" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="V5" t="s"/>
       <c r="W5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="X5" t="s"/>
       <c r="Y5" t="s"/>
@@ -3215,67 +3227,69 @@
     </row>
     <row r="6" spans="1:28">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
       </c>
-      <c r="C6" t="s"/>
+      <c r="C6" t="s">
+        <v>56</v>
+      </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="N6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="P6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S6" t="s"/>
       <c r="T6" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="V6" t="s"/>
       <c r="W6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="X6" t="s"/>
       <c r="Y6" t="s"/>
@@ -3287,67 +3301,69 @@
     </row>
     <row r="7" spans="1:28">
       <c r="A7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
       </c>
-      <c r="C7" t="s"/>
+      <c r="C7" t="s">
+        <v>56</v>
+      </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S7" t="s"/>
       <c r="T7" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="V7" t="s"/>
       <c r="W7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="X7" t="s"/>
       <c r="Y7" t="s"/>
@@ -3359,67 +3375,69 @@
     </row>
     <row r="8" spans="1:28">
       <c r="A8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s">
         <v>55</v>
       </c>
-      <c r="C8" t="s"/>
+      <c r="C8" t="s">
+        <v>56</v>
+      </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="P8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Q8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S8" t="s"/>
       <c r="T8" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="V8" t="s"/>
       <c r="W8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="X8" t="s"/>
       <c r="Y8" t="s"/>
@@ -3431,67 +3449,69 @@
     </row>
     <row r="9" spans="1:28">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B9" t="s">
         <v>55</v>
       </c>
-      <c r="C9" t="s"/>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="P9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S9" t="s"/>
       <c r="T9" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="V9" t="s"/>
       <c r="W9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="X9" t="s"/>
       <c r="Y9" t="s"/>
@@ -3503,67 +3523,69 @@
     </row>
     <row r="10" spans="1:28">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B10" t="s">
         <v>55</v>
       </c>
-      <c r="C10" t="s"/>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="L10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="N10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Q10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S10" t="s"/>
       <c r="T10" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="V10" t="s"/>
       <c r="W10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="X10" t="s"/>
       <c r="Y10" t="s"/>
@@ -3575,67 +3597,69 @@
     </row>
     <row r="11" spans="1:28">
       <c r="A11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B11" t="s">
         <v>55</v>
       </c>
-      <c r="C11" t="s"/>
+      <c r="C11" t="s">
+        <v>56</v>
+      </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="N11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="P11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S11" t="s"/>
       <c r="T11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="V11" t="s"/>
       <c r="W11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X11" t="s"/>
       <c r="Y11" t="s"/>
@@ -3647,67 +3671,69 @@
     </row>
     <row r="12" spans="1:28">
       <c r="A12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B12" t="s">
         <v>55</v>
       </c>
-      <c r="C12" t="s"/>
+      <c r="C12" t="s">
+        <v>56</v>
+      </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="L12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S12" t="s"/>
       <c r="T12" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U12" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="V12" t="s"/>
       <c r="W12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="X12" t="s"/>
       <c r="Y12" t="s"/>
@@ -3719,67 +3745,69 @@
     </row>
     <row r="13" spans="1:28">
       <c r="A13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B13" t="s">
         <v>55</v>
       </c>
-      <c r="C13" t="s"/>
+      <c r="C13" t="s">
+        <v>56</v>
+      </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M13" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S13" t="s"/>
       <c r="T13" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="V13" t="s"/>
       <c r="W13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="X13" t="s"/>
       <c r="Y13" t="s"/>
@@ -3791,67 +3819,69 @@
     </row>
     <row r="14" spans="1:28">
       <c r="A14" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B14" t="s">
         <v>55</v>
       </c>
-      <c r="C14" t="s"/>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J14" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O14" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P14" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S14" t="s"/>
       <c r="T14" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U14" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="V14" t="s"/>
       <c r="W14" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="X14" t="s"/>
       <c r="Y14" t="s"/>
@@ -3863,67 +3893,69 @@
     </row>
     <row r="15" spans="1:28">
       <c r="A15" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B15" t="s">
         <v>55</v>
       </c>
-      <c r="C15" t="s"/>
+      <c r="C15" t="s">
+        <v>56</v>
+      </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J15" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K15" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M15" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O15" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P15" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S15" t="s"/>
       <c r="T15" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U15" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="V15" t="s"/>
       <c r="W15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="X15" t="s"/>
       <c r="Y15" t="s"/>
@@ -3935,67 +3967,69 @@
     </row>
     <row r="16" spans="1:28">
       <c r="A16" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B16" t="s">
         <v>55</v>
       </c>
-      <c r="C16" t="s"/>
+      <c r="C16" t="s">
+        <v>56</v>
+      </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J16" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K16" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M16" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="N16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O16" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="P16" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S16" t="s"/>
       <c r="T16" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U16" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="V16" t="s"/>
       <c r="W16" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="X16" t="s"/>
       <c r="Y16" t="s"/>
@@ -4007,67 +4041,69 @@
     </row>
     <row r="17" spans="1:28">
       <c r="A17" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s">
         <v>55</v>
       </c>
-      <c r="C17" t="s"/>
+      <c r="C17" t="s">
+        <v>56</v>
+      </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J17" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K17" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M17" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O17" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="P17" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S17" t="s"/>
       <c r="T17" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U17" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="V17" t="s"/>
       <c r="W17" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="X17" t="s"/>
       <c r="Y17" t="s"/>
@@ -4079,67 +4115,69 @@
     </row>
     <row r="18" spans="1:28">
       <c r="A18" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B18" t="s">
         <v>55</v>
       </c>
-      <c r="C18" t="s"/>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J18" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K18" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M18" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O18" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P18" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S18" t="s"/>
       <c r="T18" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U18" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="V18" t="s"/>
       <c r="W18" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="X18" t="s"/>
       <c r="Y18" t="s"/>
@@ -4151,67 +4189,69 @@
     </row>
     <row r="19" spans="1:28">
       <c r="A19" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s">
         <v>55</v>
       </c>
-      <c r="C19" t="s"/>
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J19" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K19" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M19" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="N19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O19" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="P19" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S19" t="s"/>
       <c r="T19" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U19" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="V19" t="s"/>
       <c r="W19" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="X19" t="s"/>
       <c r="Y19" t="s"/>
@@ -4223,67 +4263,69 @@
     </row>
     <row r="20" spans="1:28">
       <c r="A20" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s">
         <v>55</v>
       </c>
-      <c r="C20" t="s"/>
+      <c r="C20" t="s">
+        <v>56</v>
+      </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J20" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K20" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M20" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O20" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P20" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S20" t="s"/>
       <c r="T20" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U20" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="V20" t="s"/>
       <c r="W20" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="X20" t="s"/>
       <c r="Y20" t="s"/>
@@ -4295,67 +4337,69 @@
     </row>
     <row r="21" spans="1:28">
       <c r="A21" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s">
         <v>55</v>
       </c>
-      <c r="C21" t="s"/>
+      <c r="C21" t="s">
+        <v>56</v>
+      </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J21" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K21" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M21" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O21" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P21" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S21" t="s"/>
       <c r="T21" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U21" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="V21" t="s"/>
       <c r="W21" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="X21" t="s"/>
       <c r="Y21" t="s"/>
@@ -4367,67 +4411,69 @@
     </row>
     <row r="22" spans="1:28">
       <c r="A22" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s">
         <v>55</v>
       </c>
-      <c r="C22" t="s"/>
+      <c r="C22" t="s">
+        <v>56</v>
+      </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J22" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K22" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M22" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O22" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="P22" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S22" t="s"/>
       <c r="T22" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U22" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="V22" t="s"/>
       <c r="W22" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="X22" t="s"/>
       <c r="Y22" t="s"/>
@@ -4439,67 +4485,69 @@
     </row>
     <row r="23" spans="1:28">
       <c r="A23" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s">
         <v>55</v>
       </c>
-      <c r="C23" t="s"/>
+      <c r="C23" t="s">
+        <v>56</v>
+      </c>
       <c r="D23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J23" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K23" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M23" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O23" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P23" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R23" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S23" t="s"/>
       <c r="T23" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U23" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="V23" t="s"/>
       <c r="W23" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="X23" t="s"/>
       <c r="Y23" t="s"/>
@@ -4511,67 +4559,69 @@
     </row>
     <row r="24" spans="1:28">
       <c r="A24" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s">
         <v>55</v>
       </c>
-      <c r="C24" t="s"/>
+      <c r="C24" t="s">
+        <v>56</v>
+      </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J24" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K24" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M24" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O24" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P24" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q24" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S24" t="s"/>
       <c r="T24" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U24" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="V24" t="s"/>
       <c r="W24" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="X24" t="s"/>
       <c r="Y24" t="s"/>
@@ -4583,67 +4633,69 @@
     </row>
     <row r="25" spans="1:28">
       <c r="A25" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B25" t="s">
         <v>55</v>
       </c>
-      <c r="C25" t="s"/>
+      <c r="C25" t="s">
+        <v>56</v>
+      </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J25" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K25" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M25" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="N25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O25" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="P25" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S25" t="s"/>
       <c r="T25" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U25" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="V25" t="s"/>
       <c r="W25" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="X25" t="s"/>
       <c r="Y25" t="s"/>
@@ -4655,67 +4707,69 @@
     </row>
     <row r="26" spans="1:28">
       <c r="A26" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s">
         <v>55</v>
       </c>
-      <c r="C26" t="s"/>
+      <c r="C26" t="s">
+        <v>56</v>
+      </c>
       <c r="D26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J26" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K26" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M26" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O26" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="P26" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S26" t="s"/>
       <c r="T26" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U26" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="V26" t="s"/>
       <c r="W26" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="X26" t="s"/>
       <c r="Y26" t="s"/>
@@ -4727,67 +4781,69 @@
     </row>
     <row r="27" spans="1:28">
       <c r="A27" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s">
         <v>55</v>
       </c>
-      <c r="C27" t="s"/>
+      <c r="C27" t="s">
+        <v>56</v>
+      </c>
       <c r="D27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J27" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="K27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M27" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O27" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P27" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S27" t="s"/>
       <c r="T27" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U27" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="V27" t="s"/>
       <c r="W27" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="X27" t="s"/>
       <c r="Y27" t="s"/>
@@ -4799,67 +4855,69 @@
     </row>
     <row r="28" spans="1:28">
       <c r="A28" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s">
         <v>55</v>
       </c>
-      <c r="C28" t="s"/>
+      <c r="C28" t="s">
+        <v>56</v>
+      </c>
       <c r="D28" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J28" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K28" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M28" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O28" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P28" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S28" t="s"/>
       <c r="T28" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U28" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="V28" t="s"/>
       <c r="W28" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="X28" t="s"/>
       <c r="Y28" t="s"/>
@@ -4871,67 +4929,69 @@
     </row>
     <row r="29" spans="1:28">
       <c r="A29" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s">
         <v>55</v>
       </c>
-      <c r="C29" t="s"/>
+      <c r="C29" t="s">
+        <v>56</v>
+      </c>
       <c r="D29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J29" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K29" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M29" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O29" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P29" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S29" t="s"/>
       <c r="T29" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U29" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="V29" t="s"/>
       <c r="W29" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="X29" t="s"/>
       <c r="Y29" t="s"/>
@@ -4943,67 +5003,69 @@
     </row>
     <row r="30" spans="1:28">
       <c r="A30" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s">
         <v>55</v>
       </c>
-      <c r="C30" t="s"/>
+      <c r="C30" t="s">
+        <v>56</v>
+      </c>
       <c r="D30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J30" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K30" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M30" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O30" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P30" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S30" t="s"/>
       <c r="T30" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U30" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="V30" t="s"/>
       <c r="W30" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="X30" t="s"/>
       <c r="Y30" t="s"/>
@@ -5015,67 +5077,69 @@
     </row>
     <row r="31" spans="1:28">
       <c r="A31" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s">
         <v>55</v>
       </c>
-      <c r="C31" t="s"/>
+      <c r="C31" t="s">
+        <v>56</v>
+      </c>
       <c r="D31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G31" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J31" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K31" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L31" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M31" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N31" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q31" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S31" t="s"/>
       <c r="T31" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U31" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="V31" t="s"/>
       <c r="W31" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="X31" t="s"/>
       <c r="Y31" t="s"/>
@@ -5087,67 +5151,69 @@
     </row>
     <row r="32" spans="1:28">
       <c r="A32" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B32" t="s">
         <v>55</v>
       </c>
-      <c r="C32" t="s"/>
+      <c r="C32" t="s">
+        <v>56</v>
+      </c>
       <c r="D32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H32" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J32" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K32" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="L32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M32" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O32" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="P32" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S32" t="s"/>
       <c r="T32" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U32" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="V32" t="s"/>
       <c r="W32" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="X32" t="s"/>
       <c r="Y32" t="s"/>
@@ -5159,67 +5225,69 @@
     </row>
     <row r="33" spans="1:28">
       <c r="A33" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B33" t="s">
         <v>55</v>
       </c>
-      <c r="C33" t="s"/>
+      <c r="C33" t="s">
+        <v>56</v>
+      </c>
       <c r="D33" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J33" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="K33" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M33" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O33" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="P33" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S33" t="s"/>
       <c r="T33" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U33" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="V33" t="s"/>
       <c r="W33" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="X33" t="s"/>
       <c r="Y33" t="s"/>
@@ -5231,67 +5299,69 @@
     </row>
     <row r="34" spans="1:28">
       <c r="A34" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B34" t="s">
         <v>55</v>
       </c>
-      <c r="C34" t="s"/>
+      <c r="C34" t="s">
+        <v>56</v>
+      </c>
       <c r="D34" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J34" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K34" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M34" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N34" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O34" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P34" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S34" t="s"/>
       <c r="T34" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U34" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="V34" t="s"/>
       <c r="W34" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="X34" t="s"/>
       <c r="Y34" t="s"/>
@@ -5303,67 +5373,69 @@
     </row>
     <row r="35" spans="1:28">
       <c r="A35" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B35" t="s">
         <v>55</v>
       </c>
-      <c r="C35" t="s"/>
+      <c r="C35" t="s">
+        <v>56</v>
+      </c>
       <c r="D35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J35" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K35" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L35" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M35" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O35" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P35" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R35" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S35" t="s"/>
       <c r="T35" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U35" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="V35" t="s"/>
       <c r="W35" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="X35" t="s"/>
       <c r="Y35" t="s"/>
@@ -5375,67 +5447,69 @@
     </row>
     <row r="36" spans="1:28">
       <c r="A36" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B36" t="s">
         <v>55</v>
       </c>
-      <c r="C36" t="s"/>
+      <c r="C36" t="s">
+        <v>56</v>
+      </c>
       <c r="D36" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F36" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H36" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J36" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K36" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L36" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M36" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N36" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O36" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P36" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S36" t="s"/>
       <c r="T36" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U36" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="V36" t="s"/>
       <c r="W36" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="X36" t="s"/>
       <c r="Y36" t="s"/>
@@ -5447,67 +5521,69 @@
     </row>
     <row r="37" spans="1:28">
       <c r="A37" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B37" t="s">
         <v>55</v>
       </c>
-      <c r="C37" t="s"/>
+      <c r="C37" t="s">
+        <v>56</v>
+      </c>
       <c r="D37" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F37" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H37" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J37" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K37" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M37" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N37" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O37" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="P37" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q37" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S37" t="s"/>
       <c r="T37" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U37" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="V37" t="s"/>
       <c r="W37" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="X37" t="s"/>
       <c r="Y37" t="s"/>
@@ -5519,67 +5595,69 @@
     </row>
     <row r="38" spans="1:28">
       <c r="A38" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B38" t="s">
         <v>55</v>
       </c>
-      <c r="C38" t="s"/>
+      <c r="C38" t="s">
+        <v>56</v>
+      </c>
       <c r="D38" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H38" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J38" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K38" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M38" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N38" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O38" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P38" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q38" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S38" t="s"/>
       <c r="T38" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U38" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="V38" t="s"/>
       <c r="W38" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="X38" t="s"/>
       <c r="Y38" t="s"/>
@@ -5591,67 +5669,69 @@
     </row>
     <row r="39" spans="1:28">
       <c r="A39" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B39" t="s">
         <v>55</v>
       </c>
-      <c r="C39" t="s"/>
+      <c r="C39" t="s">
+        <v>56</v>
+      </c>
       <c r="D39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J39" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K39" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L39" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M39" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O39" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="P39" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q39" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R39" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S39" t="s"/>
       <c r="T39" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U39" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="V39" t="s"/>
       <c r="W39" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="X39" t="s"/>
       <c r="Y39" t="s"/>
@@ -5663,67 +5743,69 @@
     </row>
     <row r="40" spans="1:28">
       <c r="A40" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B40" t="s">
         <v>55</v>
       </c>
-      <c r="C40" t="s"/>
+      <c r="C40" t="s">
+        <v>56</v>
+      </c>
       <c r="D40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E40" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F40" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H40" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I40" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J40" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K40" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L40" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M40" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O40" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="P40" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q40" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S40" t="s"/>
       <c r="T40" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U40" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="V40" t="s"/>
       <c r="W40" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="X40" t="s"/>
       <c r="Y40" t="s"/>
@@ -5735,67 +5817,69 @@
     </row>
     <row r="41" spans="1:28">
       <c r="A41" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B41" t="s">
         <v>55</v>
       </c>
-      <c r="C41" t="s"/>
+      <c r="C41" t="s">
+        <v>56</v>
+      </c>
       <c r="D41" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E41" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F41" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J41" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K41" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L41" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M41" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N41" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O41" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="P41" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S41" t="s"/>
       <c r="T41" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U41" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="V41" t="s"/>
       <c r="W41" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="X41" t="s"/>
       <c r="Y41" t="s"/>
@@ -5807,67 +5891,69 @@
     </row>
     <row r="42" spans="1:28">
       <c r="A42" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B42" t="s">
         <v>55</v>
       </c>
-      <c r="C42" t="s"/>
+      <c r="C42" t="s">
+        <v>56</v>
+      </c>
       <c r="D42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E42" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F42" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G42" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H42" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J42" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K42" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L42" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M42" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N42" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O42" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P42" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S42" t="s"/>
       <c r="T42" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U42" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="V42" t="s"/>
       <c r="W42" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="X42" t="s"/>
       <c r="Y42" t="s"/>
@@ -5879,67 +5965,69 @@
     </row>
     <row r="43" spans="1:28">
       <c r="A43" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B43" t="s">
         <v>55</v>
       </c>
-      <c r="C43" t="s"/>
+      <c r="C43" t="s">
+        <v>56</v>
+      </c>
       <c r="D43" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F43" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J43" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="K43" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M43" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O43" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P43" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q43" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S43" t="s"/>
       <c r="T43" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U43" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="V43" t="s"/>
       <c r="W43" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="X43" t="s"/>
       <c r="Y43" t="s"/>
@@ -5951,67 +6039,69 @@
     </row>
     <row r="44" spans="1:28">
       <c r="A44" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B44" t="s">
         <v>55</v>
       </c>
-      <c r="C44" t="s"/>
+      <c r="C44" t="s">
+        <v>56</v>
+      </c>
       <c r="D44" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E44" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F44" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G44" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H44" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I44" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J44" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K44" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L44" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M44" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N44" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O44" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P44" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Q44" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S44" t="s"/>
       <c r="T44" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U44" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="V44" t="s"/>
       <c r="W44" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="X44" t="s"/>
       <c r="Y44" t="s"/>
@@ -6023,67 +6113,69 @@
     </row>
     <row r="45" spans="1:28">
       <c r="A45" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B45" t="s">
         <v>55</v>
       </c>
-      <c r="C45" t="s"/>
+      <c r="C45" t="s">
+        <v>56</v>
+      </c>
       <c r="D45" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E45" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F45" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G45" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H45" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I45" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J45" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K45" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M45" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N45" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O45" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P45" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Q45" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S45" t="s"/>
       <c r="T45" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U45" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="V45" t="s"/>
       <c r="W45" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="X45" t="s"/>
       <c r="Y45" t="s"/>
@@ -6095,67 +6187,69 @@
     </row>
     <row r="46" spans="1:28">
       <c r="A46" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B46" t="s">
         <v>55</v>
       </c>
-      <c r="C46" t="s"/>
+      <c r="C46" t="s">
+        <v>56</v>
+      </c>
       <c r="D46" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E46" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F46" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G46" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H46" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I46" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J46" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K46" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L46" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M46" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N46" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O46" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="P46" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q46" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R46" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S46" t="s"/>
       <c r="T46" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U46" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="V46" t="s"/>
       <c r="W46" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="X46" t="s"/>
       <c r="Y46" t="s"/>
@@ -6167,67 +6261,69 @@
     </row>
     <row r="47" spans="1:28">
       <c r="A47" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B47" t="s">
         <v>55</v>
       </c>
-      <c r="C47" t="s"/>
+      <c r="C47" t="s">
+        <v>56</v>
+      </c>
       <c r="D47" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E47" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F47" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G47" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H47" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I47" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J47" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="K47" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L47" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M47" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O47" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P47" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Q47" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R47" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S47" t="s"/>
       <c r="T47" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U47" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="V47" t="s"/>
       <c r="W47" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="X47" t="s"/>
       <c r="Y47" t="s"/>
@@ -6239,67 +6335,69 @@
     </row>
     <row r="48" spans="1:28">
       <c r="A48" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B48" t="s">
         <v>55</v>
       </c>
-      <c r="C48" t="s"/>
+      <c r="C48" t="s">
+        <v>56</v>
+      </c>
       <c r="D48" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E48" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F48" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G48" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H48" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I48" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J48" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K48" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L48" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M48" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N48" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O48" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P48" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="Q48" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R48" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S48" t="s"/>
       <c r="T48" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U48" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="V48" t="s"/>
       <c r="W48" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="X48" t="s"/>
       <c r="Y48" t="s"/>
@@ -6311,67 +6409,69 @@
     </row>
     <row r="49" spans="1:28">
       <c r="A49" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B49" t="s">
         <v>55</v>
       </c>
-      <c r="C49" t="s"/>
+      <c r="C49" t="s">
+        <v>56</v>
+      </c>
       <c r="D49" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E49" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F49" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G49" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H49" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I49" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J49" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K49" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L49" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M49" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N49" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O49" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="P49" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="Q49" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S49" t="s"/>
       <c r="T49" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U49" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="V49" t="s"/>
       <c r="W49" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="X49" t="s"/>
       <c r="Y49" t="s"/>
@@ -6383,67 +6483,69 @@
     </row>
     <row r="50" spans="1:28">
       <c r="A50" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B50" t="s">
         <v>55</v>
       </c>
-      <c r="C50" t="s"/>
+      <c r="C50" t="s">
+        <v>56</v>
+      </c>
       <c r="D50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F50" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G50" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J50" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K50" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="L50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M50" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O50" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="P50" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="Q50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S50" t="s"/>
       <c r="T50" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U50" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="V50" t="s"/>
       <c r="W50" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="X50" t="s"/>
       <c r="Y50" t="s"/>
@@ -6455,67 +6557,69 @@
     </row>
     <row r="51" spans="1:28">
       <c r="A51" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B51" t="s">
         <v>55</v>
       </c>
-      <c r="C51" t="s"/>
+      <c r="C51" t="s">
+        <v>56</v>
+      </c>
       <c r="D51" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E51" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F51" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G51" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H51" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I51" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J51" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K51" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L51" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M51" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="N51" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O51" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="P51" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="Q51" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S51" t="s"/>
       <c r="T51" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U51" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="V51" t="s"/>
       <c r="W51" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="X51" t="s"/>
       <c r="Y51" t="s"/>
@@ -6527,67 +6631,69 @@
     </row>
     <row r="52" spans="1:28">
       <c r="A52" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B52" t="s">
         <v>55</v>
       </c>
-      <c r="C52" t="s"/>
+      <c r="C52" t="s">
+        <v>56</v>
+      </c>
       <c r="D52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E52" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F52" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G52" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H52" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I52" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J52" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K52" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L52" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M52" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N52" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O52" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="P52" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="Q52" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S52" t="s"/>
       <c r="T52" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U52" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="V52" t="s"/>
       <c r="W52" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="X52" t="s"/>
       <c r="Y52" t="s"/>
@@ -6599,67 +6705,69 @@
     </row>
     <row r="53" spans="1:28">
       <c r="A53" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B53" t="s">
         <v>55</v>
       </c>
-      <c r="C53" t="s"/>
+      <c r="C53" t="s">
+        <v>56</v>
+      </c>
       <c r="D53" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E53" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F53" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G53" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H53" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I53" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J53" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K53" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L53" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M53" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N53" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O53" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="P53" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="Q53" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S53" t="s"/>
       <c r="T53" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U53" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="V53" t="s"/>
       <c r="W53" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="X53" t="s"/>
       <c r="Y53" t="s"/>
@@ -6671,67 +6779,69 @@
     </row>
     <row r="54" spans="1:28">
       <c r="A54" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B54" t="s">
         <v>55</v>
       </c>
-      <c r="C54" t="s"/>
+      <c r="C54" t="s">
+        <v>56</v>
+      </c>
       <c r="D54" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E54" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F54" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G54" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H54" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I54" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J54" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K54" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="L54" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M54" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="N54" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O54" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="P54" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="Q54" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S54" t="s"/>
       <c r="T54" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U54" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="V54" t="s"/>
       <c r="W54" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="X54" t="s"/>
       <c r="Y54" t="s"/>
@@ -6743,67 +6853,69 @@
     </row>
     <row r="55" spans="1:28">
       <c r="A55" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B55" t="s">
         <v>55</v>
       </c>
-      <c r="C55" t="s"/>
+      <c r="C55" t="s">
+        <v>56</v>
+      </c>
       <c r="D55" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E55" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F55" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G55" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H55" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I55" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J55" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="K55" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L55" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M55" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N55" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O55" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="P55" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="Q55" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R55" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S55" t="s"/>
       <c r="T55" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U55" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="V55" t="s"/>
       <c r="W55" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X55" t="s"/>
       <c r="Y55" t="s"/>
@@ -6815,67 +6927,69 @@
     </row>
     <row r="56" spans="1:28">
       <c r="A56" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B56" t="s">
         <v>55</v>
       </c>
-      <c r="C56" t="s"/>
+      <c r="C56" t="s">
+        <v>56</v>
+      </c>
       <c r="D56" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E56" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F56" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G56" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H56" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I56" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J56" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K56" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="L56" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M56" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N56" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O56" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="P56" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="Q56" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S56" t="s"/>
       <c r="T56" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U56" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="V56" t="s"/>
       <c r="W56" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="X56" t="s"/>
       <c r="Y56" t="s"/>
@@ -6887,67 +7001,69 @@
     </row>
     <row r="57" spans="1:28">
       <c r="A57" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B57" t="s">
         <v>55</v>
       </c>
-      <c r="C57" t="s"/>
+      <c r="C57" t="s">
+        <v>56</v>
+      </c>
       <c r="D57" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E57" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F57" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G57" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H57" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I57" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J57" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="K57" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L57" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M57" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="N57" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O57" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="P57" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="Q57" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R57" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S57" t="s"/>
       <c r="T57" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U57" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="V57" t="s"/>
       <c r="W57" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="X57" t="s"/>
       <c r="Y57" t="s"/>
@@ -6959,67 +7075,69 @@
     </row>
     <row r="58" spans="1:28">
       <c r="A58" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B58" t="s">
         <v>55</v>
       </c>
-      <c r="C58" t="s"/>
+      <c r="C58" t="s">
+        <v>56</v>
+      </c>
       <c r="D58" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E58" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F58" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G58" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H58" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I58" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J58" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K58" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L58" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M58" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N58" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O58" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="P58" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="Q58" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R58" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S58" t="s"/>
       <c r="T58" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U58" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="V58" t="s"/>
       <c r="W58" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="X58" t="s"/>
       <c r="Y58" t="s"/>
@@ -7031,67 +7149,69 @@
     </row>
     <row r="59" spans="1:28">
       <c r="A59" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B59" t="s">
         <v>55</v>
       </c>
-      <c r="C59" t="s"/>
+      <c r="C59" t="s">
+        <v>56</v>
+      </c>
       <c r="D59" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E59" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F59" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G59" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H59" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I59" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J59" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K59" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="L59" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M59" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="N59" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O59" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="P59" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="Q59" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R59" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S59" t="s"/>
       <c r="T59" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U59" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="V59" t="s"/>
       <c r="W59" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="X59" t="s"/>
       <c r="Y59" t="s"/>
@@ -7103,67 +7223,69 @@
     </row>
     <row r="60" spans="1:28">
       <c r="A60" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B60" t="s">
         <v>55</v>
       </c>
-      <c r="C60" t="s"/>
+      <c r="C60" t="s">
+        <v>56</v>
+      </c>
       <c r="D60" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E60" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F60" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G60" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H60" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I60" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J60" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="K60" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L60" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M60" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N60" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O60" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="P60" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="Q60" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R60" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S60" t="s"/>
       <c r="T60" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U60" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="V60" t="s"/>
       <c r="W60" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="X60" t="s"/>
       <c r="Y60" t="s"/>
@@ -7175,67 +7297,69 @@
     </row>
     <row r="61" spans="1:28">
       <c r="A61" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B61" t="s">
         <v>55</v>
       </c>
-      <c r="C61" t="s"/>
+      <c r="C61" t="s">
+        <v>56</v>
+      </c>
       <c r="D61" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E61" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F61" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G61" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H61" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I61" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J61" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K61" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L61" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M61" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N61" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O61" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P61" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="Q61" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R61" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S61" t="s"/>
       <c r="T61" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U61" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="V61" t="s"/>
       <c r="W61" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="X61" t="s"/>
       <c r="Y61" t="s"/>
@@ -7247,67 +7371,69 @@
     </row>
     <row r="62" spans="1:28">
       <c r="A62" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B62" t="s">
         <v>55</v>
       </c>
-      <c r="C62" t="s"/>
+      <c r="C62" t="s">
+        <v>56</v>
+      </c>
       <c r="D62" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E62" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F62" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G62" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H62" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I62" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J62" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="K62" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="L62" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M62" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="N62" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O62" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="P62" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="Q62" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R62" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S62" t="s"/>
       <c r="T62" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U62" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="V62" t="s"/>
       <c r="W62" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="X62" t="s"/>
       <c r="Y62" t="s"/>
@@ -7319,67 +7445,69 @@
     </row>
     <row r="63" spans="1:28">
       <c r="A63" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B63" t="s">
         <v>55</v>
       </c>
-      <c r="C63" t="s"/>
+      <c r="C63" t="s">
+        <v>56</v>
+      </c>
       <c r="D63" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E63" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F63" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G63" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H63" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J63" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="K63" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L63" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M63" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="N63" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O63" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="P63" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="Q63" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R63" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S63" t="s"/>
       <c r="T63" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U63" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="V63" t="s"/>
       <c r="W63" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="X63" t="s"/>
       <c r="Y63" t="s"/>
@@ -7391,67 +7519,69 @@
     </row>
     <row r="64" spans="1:28">
       <c r="A64" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B64" t="s">
         <v>55</v>
       </c>
-      <c r="C64" t="s"/>
+      <c r="C64" t="s">
+        <v>56</v>
+      </c>
       <c r="D64" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E64" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F64" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G64" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H64" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I64" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J64" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K64" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L64" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M64" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="N64" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O64" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="P64" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="Q64" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S64" t="s"/>
       <c r="T64" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U64" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="V64" t="s"/>
       <c r="W64" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="X64" t="s"/>
       <c r="Y64" t="s"/>
@@ -7463,67 +7593,69 @@
     </row>
     <row r="65" spans="1:28">
       <c r="A65" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B65" t="s">
         <v>55</v>
       </c>
-      <c r="C65" t="s"/>
+      <c r="C65" t="s">
+        <v>56</v>
+      </c>
       <c r="D65" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E65" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F65" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G65" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H65" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I65" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J65" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="K65" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="L65" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M65" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="N65" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O65" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="P65" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="Q65" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R65" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S65" t="s"/>
       <c r="T65" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U65" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="V65" t="s"/>
       <c r="W65" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="X65" t="s"/>
       <c r="Y65" t="s"/>
@@ -7535,67 +7667,69 @@
     </row>
     <row r="66" spans="1:28">
       <c r="A66" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B66" t="s">
         <v>55</v>
       </c>
-      <c r="C66" t="s"/>
+      <c r="C66" t="s">
+        <v>56</v>
+      </c>
       <c r="D66" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E66" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G66" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H66" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I66" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J66" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="K66" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="L66" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M66" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="N66" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O66" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="P66" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="Q66" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R66" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S66" t="s"/>
       <c r="T66" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U66" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="V66" t="s"/>
       <c r="W66" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="X66" t="s"/>
       <c r="Y66" t="s"/>
@@ -7607,67 +7741,69 @@
     </row>
     <row r="67" spans="1:28">
       <c r="A67" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B67" t="s">
         <v>55</v>
       </c>
-      <c r="C67" t="s"/>
+      <c r="C67" t="s">
+        <v>56</v>
+      </c>
       <c r="D67" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E67" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F67" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G67" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H67" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I67" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J67" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="K67" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="L67" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M67" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="N67" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O67" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="P67" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Q67" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R67" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S67" t="s"/>
       <c r="T67" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U67" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="V67" t="s"/>
       <c r="W67" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="X67" t="s"/>
       <c r="Y67" t="s"/>
@@ -7679,67 +7815,69 @@
     </row>
     <row r="68" spans="1:28">
       <c r="A68" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B68" t="s">
         <v>55</v>
       </c>
-      <c r="C68" t="s"/>
+      <c r="C68" t="s">
+        <v>56</v>
+      </c>
       <c r="D68" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E68" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F68" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G68" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H68" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I68" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J68" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="K68" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L68" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M68" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="N68" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O68" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="P68" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="Q68" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R68" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S68" t="s"/>
       <c r="T68" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U68" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="V68" t="s"/>
       <c r="W68" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="X68" t="s"/>
       <c r="Y68" t="s"/>
@@ -7751,67 +7889,69 @@
     </row>
     <row r="69" spans="1:28">
       <c r="A69" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B69" t="s">
         <v>55</v>
       </c>
-      <c r="C69" t="s"/>
+      <c r="C69" t="s">
+        <v>56</v>
+      </c>
       <c r="D69" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E69" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F69" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G69" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H69" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I69" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J69" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="K69" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="L69" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M69" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N69" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O69" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="P69" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="Q69" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R69" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S69" t="s"/>
       <c r="T69" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U69" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="V69" t="s"/>
       <c r="W69" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="X69" t="s"/>
       <c r="Y69" t="s"/>
@@ -7823,67 +7963,69 @@
     </row>
     <row r="70" spans="1:28">
       <c r="A70" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B70" t="s">
         <v>55</v>
       </c>
-      <c r="C70" t="s"/>
+      <c r="C70" t="s">
+        <v>56</v>
+      </c>
       <c r="D70" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E70" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F70" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G70" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H70" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I70" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J70" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="K70" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="L70" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M70" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="N70" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O70" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="P70" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="Q70" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R70" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S70" t="s"/>
       <c r="T70" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U70" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="V70" t="s"/>
       <c r="W70" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="X70" t="s"/>
       <c r="Y70" t="s"/>
@@ -7895,67 +8037,69 @@
     </row>
     <row r="71" spans="1:28">
       <c r="A71" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B71" t="s">
         <v>55</v>
       </c>
-      <c r="C71" t="s"/>
+      <c r="C71" t="s">
+        <v>56</v>
+      </c>
       <c r="D71" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E71" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F71" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G71" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H71" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I71" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J71" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="K71" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="L71" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M71" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="N71" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O71" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="P71" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="Q71" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R71" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S71" t="s"/>
       <c r="T71" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U71" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="V71" t="s"/>
       <c r="W71" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="X71" t="s"/>
       <c r="Y71" t="s"/>
@@ -7967,67 +8111,69 @@
     </row>
     <row r="72" spans="1:28">
       <c r="A72" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B72" t="s">
         <v>55</v>
       </c>
-      <c r="C72" t="s"/>
+      <c r="C72" t="s">
+        <v>56</v>
+      </c>
       <c r="D72" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E72" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F72" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G72" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H72" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I72" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J72" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="K72" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="L72" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M72" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="N72" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O72" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="P72" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="Q72" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R72" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S72" t="s"/>
       <c r="T72" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U72" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="V72" t="s"/>
       <c r="W72" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="X72" t="s"/>
       <c r="Y72" t="s"/>
@@ -8039,67 +8185,69 @@
     </row>
     <row r="73" spans="1:28">
       <c r="A73" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B73" t="s">
         <v>55</v>
       </c>
-      <c r="C73" t="s"/>
+      <c r="C73" t="s">
+        <v>56</v>
+      </c>
       <c r="D73" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E73" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F73" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G73" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H73" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I73" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J73" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="K73" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="L73" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M73" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="N73" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O73" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="P73" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="Q73" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R73" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S73" t="s"/>
       <c r="T73" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U73" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="V73" t="s"/>
       <c r="W73" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="X73" t="s"/>
       <c r="Y73" t="s"/>
@@ -8111,67 +8259,69 @@
     </row>
     <row r="74" spans="1:28">
       <c r="A74" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B74" t="s">
         <v>55</v>
       </c>
-      <c r="C74" t="s"/>
+      <c r="C74" t="s">
+        <v>56</v>
+      </c>
       <c r="D74" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E74" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F74" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G74" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H74" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I74" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J74" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K74" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L74" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M74" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="N74" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O74" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="P74" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="Q74" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R74" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S74" t="s"/>
       <c r="T74" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U74" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="V74" t="s"/>
       <c r="W74" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="X74" t="s"/>
       <c r="Y74" t="s"/>
@@ -8183,67 +8333,69 @@
     </row>
     <row r="75" spans="1:28">
       <c r="A75" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B75" t="s">
         <v>55</v>
       </c>
-      <c r="C75" t="s"/>
+      <c r="C75" t="s">
+        <v>56</v>
+      </c>
       <c r="D75" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E75" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F75" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G75" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H75" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I75" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J75" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="K75" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="L75" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M75" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="N75" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O75" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="P75" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="Q75" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R75" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S75" t="s"/>
       <c r="T75" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U75" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="V75" t="s"/>
       <c r="W75" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="X75" t="s"/>
       <c r="Y75" t="s"/>
@@ -8255,67 +8407,69 @@
     </row>
     <row r="76" spans="1:28">
       <c r="A76" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B76" t="s">
         <v>55</v>
       </c>
-      <c r="C76" t="s"/>
+      <c r="C76" t="s">
+        <v>56</v>
+      </c>
       <c r="D76" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E76" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F76" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G76" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H76" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I76" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J76" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="K76" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="L76" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M76" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="N76" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O76" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="P76" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="Q76" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R76" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S76" t="s"/>
       <c r="T76" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U76" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="V76" t="s"/>
       <c r="W76" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="X76" t="s"/>
       <c r="Y76" t="s"/>
@@ -8327,67 +8481,69 @@
     </row>
     <row r="77" spans="1:28">
       <c r="A77" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B77" t="s">
         <v>55</v>
       </c>
-      <c r="C77" t="s"/>
+      <c r="C77" t="s">
+        <v>56</v>
+      </c>
       <c r="D77" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E77" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F77" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G77" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H77" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I77" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J77" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="K77" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="L77" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M77" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="N77" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O77" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="P77" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="Q77" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R77" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S77" t="s"/>
       <c r="T77" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U77" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="V77" t="s"/>
       <c r="W77" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="X77" t="s"/>
       <c r="Y77" t="s"/>
@@ -8399,67 +8555,69 @@
     </row>
     <row r="78" spans="1:28">
       <c r="A78" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B78" t="s">
         <v>55</v>
       </c>
-      <c r="C78" t="s"/>
+      <c r="C78" t="s">
+        <v>56</v>
+      </c>
       <c r="D78" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E78" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F78" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G78" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H78" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I78" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J78" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="K78" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="L78" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M78" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="N78" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O78" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="P78" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="Q78" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R78" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S78" t="s"/>
       <c r="T78" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U78" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="V78" t="s"/>
       <c r="W78" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="X78" t="s"/>
       <c r="Y78" t="s"/>
@@ -8471,67 +8629,69 @@
     </row>
     <row r="79" spans="1:28">
       <c r="A79" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B79" t="s">
         <v>55</v>
       </c>
-      <c r="C79" t="s"/>
+      <c r="C79" t="s">
+        <v>56</v>
+      </c>
       <c r="D79" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E79" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F79" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G79" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H79" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I79" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J79" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="K79" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="L79" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M79" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="N79" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O79" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="P79" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="Q79" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R79" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S79" t="s"/>
       <c r="T79" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U79" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="V79" t="s"/>
       <c r="W79" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="X79" t="s"/>
       <c r="Y79" t="s"/>
@@ -8543,67 +8703,69 @@
     </row>
     <row r="80" spans="1:28">
       <c r="A80" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B80" t="s">
         <v>55</v>
       </c>
-      <c r="C80" t="s"/>
+      <c r="C80" t="s">
+        <v>56</v>
+      </c>
       <c r="D80" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E80" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F80" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G80" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H80" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I80" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J80" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="K80" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="L80" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M80" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="N80" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O80" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="P80" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="Q80" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R80" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S80" t="s"/>
       <c r="T80" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U80" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="V80" t="s"/>
       <c r="W80" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="X80" t="s"/>
       <c r="Y80" t="s"/>
@@ -8615,67 +8777,69 @@
     </row>
     <row r="81" spans="1:28">
       <c r="A81" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B81" t="s">
         <v>55</v>
       </c>
-      <c r="C81" t="s"/>
+      <c r="C81" t="s">
+        <v>56</v>
+      </c>
       <c r="D81" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E81" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F81" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G81" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H81" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I81" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J81" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="K81" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="L81" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M81" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="N81" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O81" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="P81" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="Q81" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R81" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S81" t="s"/>
       <c r="T81" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U81" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="V81" t="s"/>
       <c r="W81" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="X81" t="s"/>
       <c r="Y81" t="s"/>
@@ -8687,67 +8851,69 @@
     </row>
     <row r="82" spans="1:28">
       <c r="A82" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B82" t="s">
         <v>55</v>
       </c>
-      <c r="C82" t="s"/>
+      <c r="C82" t="s">
+        <v>56</v>
+      </c>
       <c r="D82" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E82" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F82" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G82" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H82" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I82" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J82" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="K82" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="L82" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M82" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="N82" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O82" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="P82" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="Q82" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R82" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S82" t="s"/>
       <c r="T82" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U82" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="V82" t="s"/>
       <c r="W82" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="X82" t="s"/>
       <c r="Y82" t="s"/>
@@ -8759,67 +8925,69 @@
     </row>
     <row r="83" spans="1:28">
       <c r="A83" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B83" t="s">
         <v>55</v>
       </c>
-      <c r="C83" t="s"/>
+      <c r="C83" t="s">
+        <v>56</v>
+      </c>
       <c r="D83" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E83" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F83" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G83" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H83" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I83" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J83" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="K83" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="L83" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M83" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="N83" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O83" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="P83" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="Q83" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R83" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S83" t="s"/>
       <c r="T83" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U83" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="V83" t="s"/>
       <c r="W83" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="X83" t="s"/>
       <c r="Y83" t="s"/>
@@ -8831,67 +8999,69 @@
     </row>
     <row r="84" spans="1:28">
       <c r="A84" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B84" t="s">
         <v>55</v>
       </c>
-      <c r="C84" t="s"/>
+      <c r="C84" t="s">
+        <v>56</v>
+      </c>
       <c r="D84" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E84" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F84" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G84" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H84" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I84" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J84" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="K84" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="L84" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M84" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="N84" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O84" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="P84" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="Q84" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R84" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S84" t="s"/>
       <c r="T84" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U84" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="V84" t="s"/>
       <c r="W84" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="X84" t="s"/>
       <c r="Y84" t="s"/>
@@ -8903,67 +9073,69 @@
     </row>
     <row r="85" spans="1:28">
       <c r="A85" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B85" t="s">
         <v>55</v>
       </c>
-      <c r="C85" t="s"/>
+      <c r="C85" t="s">
+        <v>56</v>
+      </c>
       <c r="D85" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E85" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F85" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G85" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H85" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I85" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J85" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="K85" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="L85" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M85" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="N85" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O85" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="P85" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="Q85" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R85" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S85" t="s"/>
       <c r="T85" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U85" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="V85" t="s"/>
       <c r="W85" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="X85" t="s"/>
       <c r="Y85" t="s"/>
@@ -8975,67 +9147,69 @@
     </row>
     <row r="86" spans="1:28">
       <c r="A86" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B86" t="s">
         <v>55</v>
       </c>
-      <c r="C86" t="s"/>
+      <c r="C86" t="s">
+        <v>56</v>
+      </c>
       <c r="D86" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E86" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F86" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G86" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H86" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I86" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J86" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="K86" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="L86" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M86" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="N86" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O86" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="P86" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="Q86" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R86" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S86" t="s"/>
       <c r="T86" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U86" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="V86" t="s"/>
       <c r="W86" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="X86" t="s"/>
       <c r="Y86" t="s"/>
@@ -9047,67 +9221,69 @@
     </row>
     <row r="87" spans="1:28">
       <c r="A87" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B87" t="s">
         <v>55</v>
       </c>
-      <c r="C87" t="s"/>
+      <c r="C87" t="s">
+        <v>56</v>
+      </c>
       <c r="D87" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E87" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F87" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G87" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H87" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I87" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J87" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="K87" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="L87" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M87" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="N87" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O87" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="P87" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="Q87" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R87" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S87" t="s"/>
       <c r="T87" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U87" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="V87" t="s"/>
       <c r="W87" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="X87" t="s"/>
       <c r="Y87" t="s"/>
@@ -9119,67 +9295,69 @@
     </row>
     <row r="88" spans="1:28">
       <c r="A88" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B88" t="s">
         <v>55</v>
       </c>
-      <c r="C88" t="s"/>
+      <c r="C88" t="s">
+        <v>56</v>
+      </c>
       <c r="D88" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E88" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F88" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G88" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H88" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I88" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J88" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="K88" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="L88" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M88" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="N88" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O88" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="P88" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="Q88" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R88" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S88" t="s"/>
       <c r="T88" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U88" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="V88" t="s"/>
       <c r="W88" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="X88" t="s"/>
       <c r="Y88" t="s"/>
@@ -9191,67 +9369,69 @@
     </row>
     <row r="89" spans="1:28">
       <c r="A89" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B89" t="s">
         <v>55</v>
       </c>
-      <c r="C89" t="s"/>
+      <c r="C89" t="s">
+        <v>56</v>
+      </c>
       <c r="D89" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E89" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F89" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G89" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H89" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I89" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J89" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="K89" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="L89" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M89" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="N89" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O89" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="P89" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="Q89" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R89" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S89" t="s"/>
       <c r="T89" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U89" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="V89" t="s"/>
       <c r="W89" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="X89" t="s"/>
       <c r="Y89" t="s"/>
@@ -9263,67 +9443,69 @@
     </row>
     <row r="90" spans="1:28">
       <c r="A90" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B90" t="s">
         <v>55</v>
       </c>
-      <c r="C90" t="s"/>
+      <c r="C90" t="s">
+        <v>56</v>
+      </c>
       <c r="D90" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E90" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F90" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G90" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H90" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I90" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J90" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="K90" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="L90" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M90" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="N90" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O90" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="P90" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="Q90" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R90" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S90" t="s"/>
       <c r="T90" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U90" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="V90" t="s"/>
       <c r="W90" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="X90" t="s"/>
       <c r="Y90" t="s"/>
@@ -9335,67 +9517,69 @@
     </row>
     <row r="91" spans="1:28">
       <c r="A91" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="B91" t="s">
         <v>55</v>
       </c>
-      <c r="C91" t="s"/>
+      <c r="C91" t="s">
+        <v>56</v>
+      </c>
       <c r="D91" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E91" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F91" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G91" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H91" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I91" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J91" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="K91" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="L91" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M91" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="N91" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O91" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="P91" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="Q91" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R91" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S91" t="s"/>
       <c r="T91" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U91" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="V91" t="s"/>
       <c r="W91" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="X91" t="s"/>
       <c r="Y91" t="s"/>
@@ -9407,67 +9591,69 @@
     </row>
     <row r="92" spans="1:28">
       <c r="A92" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B92" t="s">
         <v>55</v>
       </c>
-      <c r="C92" t="s"/>
+      <c r="C92" t="s">
+        <v>56</v>
+      </c>
       <c r="D92" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E92" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H92" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I92" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J92" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="K92" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="L92" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M92" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="N92" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O92" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="P92" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="Q92" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R92" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S92" t="s"/>
       <c r="T92" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U92" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="V92" t="s"/>
       <c r="W92" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="X92" t="s"/>
       <c r="Y92" t="s"/>
@@ -9479,67 +9665,69 @@
     </row>
     <row r="93" spans="1:28">
       <c r="A93" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B93" t="s">
         <v>55</v>
       </c>
-      <c r="C93" t="s"/>
+      <c r="C93" t="s">
+        <v>56</v>
+      </c>
       <c r="D93" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E93" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F93" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G93" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H93" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I93" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J93" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="K93" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="L93" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M93" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="N93" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O93" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="P93" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="Q93" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R93" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S93" t="s"/>
       <c r="T93" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U93" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="V93" t="s"/>
       <c r="W93" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="X93" t="s"/>
       <c r="Y93" t="s"/>
@@ -9551,67 +9739,69 @@
     </row>
     <row r="94" spans="1:28">
       <c r="A94" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B94" t="s">
         <v>55</v>
       </c>
-      <c r="C94" t="s"/>
+      <c r="C94" t="s">
+        <v>56</v>
+      </c>
       <c r="D94" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E94" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F94" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G94" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H94" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I94" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J94" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="K94" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="L94" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M94" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="N94" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O94" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="P94" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="Q94" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R94" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S94" t="s"/>
       <c r="T94" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U94" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="V94" t="s"/>
       <c r="W94" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="X94" t="s"/>
       <c r="Y94" t="s"/>
@@ -9623,67 +9813,69 @@
     </row>
     <row r="95" spans="1:28">
       <c r="A95" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B95" t="s">
         <v>55</v>
       </c>
-      <c r="C95" t="s"/>
+      <c r="C95" t="s">
+        <v>56</v>
+      </c>
       <c r="D95" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E95" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F95" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G95" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H95" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I95" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J95" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="K95" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="L95" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M95" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="N95" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O95" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="P95" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="Q95" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R95" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S95" t="s"/>
       <c r="T95" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U95" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="V95" t="s"/>
       <c r="W95" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="X95" t="s"/>
       <c r="Y95" t="s"/>
@@ -9695,67 +9887,69 @@
     </row>
     <row r="96" spans="1:28">
       <c r="A96" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B96" t="s">
         <v>55</v>
       </c>
-      <c r="C96" t="s"/>
+      <c r="C96" t="s">
+        <v>56</v>
+      </c>
       <c r="D96" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E96" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F96" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G96" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H96" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I96" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J96" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="K96" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="L96" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M96" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="N96" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O96" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="P96" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="Q96" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R96" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S96" t="s"/>
       <c r="T96" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U96" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="V96" t="s"/>
       <c r="W96" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="X96" t="s"/>
       <c r="Y96" t="s"/>
@@ -9767,67 +9961,69 @@
     </row>
     <row r="97" spans="1:28">
       <c r="A97" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B97" t="s">
         <v>55</v>
       </c>
-      <c r="C97" t="s"/>
+      <c r="C97" t="s">
+        <v>56</v>
+      </c>
       <c r="D97" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E97" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F97" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G97" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H97" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I97" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J97" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="K97" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="L97" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M97" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="N97" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O97" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="P97" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="Q97" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R97" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S97" t="s"/>
       <c r="T97" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U97" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="V97" t="s"/>
       <c r="W97" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="X97" t="s"/>
       <c r="Y97" t="s"/>

--- a/docs/collections/sokuchigenkozu/metadata/data.xlsx
+++ b/docs/collections/sokuchigenkozu/metadata/data.xlsx
@@ -242,7 +242,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b7d2dc7b-56a6-6182-0a85-90b5657b01ea/manifest</t>
   </si>
   <si>
-    <t>甲州巨摩郡 自 身延山山門之石 至 福士村人家前</t>
+    <t>甲州巨摩郡自身延山山門之石至福士村人家前 : 三分一里之元図</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0c6ecc75-597f-4469-8ba1-b70a5ff27fd8.json</t>
@@ -266,7 +266,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0c6ecc75-597f-4469-8ba1-b70a5ff27fd8/manifest</t>
   </si>
   <si>
-    <t>自 辻堂村東海道追分 至 大山歴テ田原村制礼</t>
+    <t>自辻堂村東海道追分至大山歴テ田原村制札</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/eea7a8bd-7951-30a9-8c0c-5c0a56787b38.json</t>
@@ -290,7 +290,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/eea7a8bd-7951-30a9-8c0c-5c0a56787b38/manifest</t>
   </si>
   <si>
-    <t>従 武州大里郡熊谷宿歴川越 至 入間郡大仙波新田</t>
+    <t>従武州大里郡熊谷宿歴川越至入間郡大仙波新田大印 : 六分一里之圖</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e3cd2bc9-2785-451c-57ec-9dd080779fca.json</t>
@@ -314,7 +314,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e3cd2bc9-2785-451c-57ec-9dd080779fca/manifest</t>
   </si>
   <si>
-    <t>自 江府深川測処 至 大堀村</t>
+    <t>自江府深川測処至大堀村 : 㐧一圖之内猫実 : 六分一里の圖</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d1ba2b6b-19cd-9336-9d31-eca0f7f1a602.json</t>
@@ -338,7 +338,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d1ba2b6b-19cd-9336-9d31-eca0f7f1a602/manifest</t>
   </si>
   <si>
-    <t>自 信州筑摩郡洗馬宿大門村歴松本 至 更級郡川中島塩崎</t>
+    <t>自信州筑摩郡洗馬宿大門村歴松本至更級郡川中嶋塩崎江戸善光寺道追分并姨捨山 : 六分一里之圖</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/86168cb3-3911-6091-322c-efab3c982238.json</t>
@@ -362,7 +362,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/86168cb3-3911-6091-322c-efab3c982238/manifest</t>
   </si>
   <si>
-    <t>従 飛州大野郡無敷河村 至 信州筑摩郡藪原宿制札</t>
+    <t>従飛刕大野郡無數河村ム印高山町ヲ歴至信刕筑摩郡藪原宿制札 : 六分一里之図</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4fa5f500-6b90-482f-5ed9-874f653504d8.json</t>
@@ -386,7 +386,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4fa5f500-6b90-482f-5ed9-874f653504d8/manifest</t>
   </si>
   <si>
-    <t>従 信州佐久郡借宿村下仁田通リ 至 武州児玉郡本庄宿制札 多胡碑</t>
+    <t>従信州佐久郡借宿村下仁田通り至武州兒玉郡本庄宿制札多胡碑 : 六分一里之図</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8ea3dff1-5584-4016-1b93-8b4298a3415e.json</t>
@@ -410,7 +410,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8ea3dff1-5584-4016-1b93-8b4298a3415e/manifest</t>
   </si>
   <si>
-    <t>従 周防国吉敷郡山口道場門前町 至 佐波郡東佐波令制札, 長門阿武郡地福村字□, 周防吉敷郡宮野村□七房, 防芸州界亀尾川峠</t>
+    <t>従周防國吉敷郡山口道塲門前町至佐波郡東佐波令制札, 長門阿武郡地福村字掛, 周防吉敷郡宮野村枝七房, 防藝州界亀尾川峠 : 六分一里之図</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a27d5425-9b21-7938-1910-fc869954009d.json</t>
@@ -434,7 +434,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a27d5425-9b21-7938-1910-fc869954009d/manifest</t>
   </si>
   <si>
-    <t>従 長門豊浦郡小月宿制札 至 阿武郡萩市中入口</t>
+    <t>従長門豊浦郡小月宿制札至阿武郡萩市中入口 : 六分一里之図</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cbee3a35-3741-65a3-7482-aa1c2850438c.json</t>
@@ -458,7 +458,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cbee3a35-3741-65a3-7482-aa1c2850438c/manifest</t>
   </si>
   <si>
-    <t>自 中山道歴名古屋 至 岡崎趣甲州街道 2</t>
+    <t>自中山道歴名古屋至岡崎趣甲州街道二</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/24d93f3d-7479-01c5-6bab-8cae59aca1ba.json</t>
@@ -482,7 +482,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/24d93f3d-7479-01c5-6bab-8cae59aca1ba/manifest</t>
   </si>
   <si>
-    <t>自 岡崎趣甲州街道 3</t>
+    <t>自岡嵜趣甲州街道三</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/355c0ab5-3ceb-0797-9343-5b6c273a6509.json</t>
@@ -506,7 +506,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/355c0ab5-3ceb-0797-9343-5b6c273a6509/manifest</t>
   </si>
   <si>
-    <t>[記載なし][葛西川村, 亀戸村, 小名木村 等]</t>
+    <t>[自葛西川村歴亀戸村小名木村至入舩町] : 三寸六分一里</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/94371ff9-2ba1-9e62-a307-cfa886dc6da4.json</t>
@@ -530,7 +530,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/94371ff9-2ba1-9e62-a307-cfa886dc6da4/manifest</t>
   </si>
   <si>
-    <t>岡崎ヨリ甲州街道ニ趣 5</t>
+    <t>岡嵜ヨリ甲州街道ニ趣五</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fb41fbbc-6232-59a6-a516-be7750d633ee.json</t>
@@ -554,7 +554,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fb41fbbc-6232-59a6-a516-be7750d633ee/manifest</t>
   </si>
   <si>
-    <t>従 信州水内郡長野村内善光寺宿善光寺門前飯山須坂松代ヲ歴テ 至 高井郡屋代宿</t>
+    <t>従信州水内郡長野村内善光寺宿善光寺門前飯山湏坂松代ヲ歴テ至高井郡屋代宿旧測印 : 六分一里之図</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/68cf6f00-3081-069c-0fb2-306b821f9815.json</t>
@@ -578,7 +578,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/68cf6f00-3081-069c-0fb2-306b821f9815/manifest</t>
   </si>
   <si>
-    <t>中山道六分之原図 4</t>
+    <t>中山道六分之原圖四 : 從塩名田宿至贅河宿 : 自上原村塚原村界至贄川宿</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/285997ad-158b-843a-05c7-cfe8d95f9877.json</t>
@@ -602,7 +602,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/285997ad-158b-843a-05c7-cfe8d95f9877/manifest</t>
   </si>
   <si>
-    <t>中山道六分之元図 第6</t>
+    <t>中山道六分之元圖第六 : 自中河原至本郷村</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a7a3db90-5f23-5e18-86da-823535a3770b.json</t>
@@ -626,7 +626,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a7a3db90-5f23-5e18-86da-823535a3770b/manifest</t>
   </si>
   <si>
-    <t>中山道六分之原図 5</t>
+    <t>中山道六分之原図五 : 六分一里之元圖 : 従贄川至野尻字中河原</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d0bb794d-3918-6f23-666c-ce0c66eb4196.json</t>
@@ -650,7 +650,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d0bb794d-3918-6f23-666c-ce0c66eb4196/manifest</t>
   </si>
   <si>
-    <t>従 作州大庭郡下長田村字犬挟峠 至 伯州日野郡二部村字間地, 備中阿賀郡小坂部村, 同上房郡□□村字塩坪, 作州大庭郡久世村歴方中嶋村境</t>
+    <t>従作州大庭郡下長田村字犬挟峠長印至伯州日野郡二部村字間地, 備中阿賀郡小坂部村未年壬二月残印, 同上房郡片岡村字塩坪前同年残印, 作州大庭郡久世村原方中嶋村境中印 : 六分一里之圖</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/828d4f3b-68ec-2870-2331-aedb9954109d.json</t>
@@ -674,7 +674,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/828d4f3b-68ec-2870-2331-aedb9954109d/manifest</t>
   </si>
   <si>
-    <t>両国街道 5 自 備後安那郡川北村 至 安芸豊田郡本郷村</t>
+    <t>西国街道五 : 自備後安那郡川北村神辺至安藝豊田郡夲郷村測処又福山測所 : 六分啚</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d76eef77-a2fb-0ad5-7929-ba1bd036620e.json</t>
@@ -698,7 +698,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d76eef77-a2fb-0ad5-7929-ba1bd036620e/manifest</t>
   </si>
   <si>
-    <t>両国街道 6 芸州 従 豊田郡本郷村 至 安芸郡上瀬野村</t>
+    <t>西国街道六 : 藝刕従豊田郡本郷村測所至安藝郡上瀬野村一貫田</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5d6c36e2-5d9f-862e-5c08-07f8641c0d62.json</t>
@@ -722,7 +722,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5d6c36e2-5d9f-862e-5c08-07f8641c0d62/manifest</t>
   </si>
   <si>
-    <t>両国街道 4 従 岡山下町 至 神辺又油木, 八川ニ至ル</t>
+    <t>西国街道四 : 従岡山下町至神辺又油木八川ニ至ル : 六分一里之図</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0e76e3be-97ce-0bde-521c-ce96ae7d2efd.json</t>
@@ -746,7 +746,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0e76e3be-97ce-0bde-521c-ce96ae7d2efd/manifest</t>
   </si>
   <si>
-    <t>両国街道 1 山城淀, 播磨神戸村</t>
+    <t>西国街道一 : [従]山城淀測処[至]播磨神戸村 : 六分一里之図</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a0374157-4f3e-6c85-348b-38363d4a841f.json</t>
@@ -770,7 +770,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a0374157-4f3e-6c85-348b-38363d4a841f/manifest</t>
   </si>
   <si>
-    <t>従 摂州豊島郡半町止宿 至 播州加西郡坂本村</t>
+    <t>従摂刕豊嶌郡半町止宿至播刕加西郡坂本村測処</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/31606d80-64cd-7362-4302-35e960f900e8.json</t>
@@ -794,7 +794,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/31606d80-64cd-7362-4302-35e960f900e8/manifest</t>
   </si>
   <si>
-    <t>第37番 自 田老村 至 唐舟之図</t>
+    <t>第三十七番 : 自田老村至唐舟之圖</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d8694eeb-a144-4b6b-07d8-1a3bbca66089.json</t>
@@ -818,7 +818,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d8694eeb-a144-4b6b-07d8-1a3bbca66089/manifest</t>
   </si>
   <si>
-    <t>第38番 自 唐舟 至 岩尻村図</t>
+    <t>第卅八番 : 自唐舟至岩尻村圖</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cff7647e-93b0-1c96-109e-dea91230a63e.json</t>
@@ -842,7 +842,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cff7647e-93b0-1c96-109e-dea91230a63e/manifest</t>
   </si>
   <si>
-    <t>第4番 自 白川 至 矢吹, 第5番 自 矢吹 至 清水町図</t>
+    <t>第四番 : 自白川至矢吹六分圖 , 第五番 : 自矢吹至清水町圖</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f2c3ea81-1462-3963-1747-6692f3cb29fa.json</t>
@@ -866,7 +866,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f2c3ea81-1462-3963-1747-6692f3cb29fa/manifest</t>
   </si>
   <si>
-    <t>西国街道 3 自 播磨揖西郡正条 至 備前御野郡岡山</t>
+    <t>西國街道三 : 自播磨揖西郡正条至備前御野郡岡山下町 : 六分之図</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/053829e7-2a8c-079b-3181-9cd265bf95a5.json</t>
@@ -890,7 +890,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/053829e7-2a8c-079b-3181-9cd265bf95a5/manifest</t>
   </si>
   <si>
-    <t>自 大隅国桑原郡濱市村野尻ヲ歴テ加久藤, 本庄ニ至ル</t>
+    <t>自大隅國桑原郡濵市村野尻ヲ歴テ加久藤本庄ニ至ル : 六分一里之図</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4ac68437-8c91-8042-9c2f-bb50ee060488.json</t>
@@ -914,7 +914,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4ac68437-8c91-8042-9c2f-bb50ee060488/manifest</t>
   </si>
   <si>
-    <t>日向本庄村佐土原, 幸州ヲ歴恒冨村ニ至ル</t>
+    <t>日向本庄村佐土原幸脇ヲ歴恒冨村ニ至ル : 附米良道南方村椎葉道神門村ニ至ル : 六分一里之図</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f3f2230c-9d58-2bb7-875f-2ec3e4092df2.json</t>
@@ -938,7 +938,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f3f2230c-9d58-2bb7-875f-2ec3e4092df2/manifest</t>
   </si>
   <si>
-    <t>九州第7 日向国 平脇才岩境ヨリ田吉村八手迄</t>
+    <t>九州第七 : 日向國平岩才脇境ヨリ田吉村八手迠 : 六分之源図</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/04781c89-7280-6c75-3b54-5f93d96d9590.json</t>
@@ -962,7 +962,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/04781c89-7280-6c75-3b54-5f93d96d9590/manifest</t>
   </si>
   <si>
-    <t>九州第8 日向 田吉村字八手 至 贄波海北村界</t>
+    <t>九州第八 : 日向自田吉村字八手至贄波海北村界 : 附牛ヶ嶺迠 : 六分之源図</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2003763f-55a3-9ffa-7684-536a955458c8.json</t>
@@ -986,7 +986,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2003763f-55a3-9ffa-7684-536a955458c8/manifest</t>
   </si>
   <si>
-    <t>九州第12 自 廻村牧場 至 牛ヶ嶺</t>
+    <t>九州第十二 : 自廻村牧場至牛ヶ嶺</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9cfe1650-28b3-8367-61b5-b20ab9ca10d3.json</t>
@@ -1010,7 +1010,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9cfe1650-28b3-8367-61b5-b20ab9ca10d3/manifest</t>
   </si>
   <si>
-    <t>九州第13 自 鹿児島城下街道追分 至 御領村</t>
+    <t>九刕第十三 : 自鹿児嶋城下街道追分至御領村之内石垣浦 : 附肥後街道清藤村迠</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a9f0e478-44c6-4a8a-954e-9aacf0bc59c6.json</t>
@@ -1034,7 +1034,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a9f0e478-44c6-4a8a-954e-9aacf0bc59c6/manifest</t>
   </si>
   <si>
-    <t>九州14 自 御領村 至 串木野五反川</t>
+    <t>九州第十四 : 自御領村石垣浦至串木野五反川 : 附肥後街道清藤村より市来湊迠</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1872793a-16cb-96f4-5d5d-44874d800e1e.json</t>
@@ -1058,7 +1058,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1872793a-16cb-96f4-5d5d-44874d800e1e/manifest</t>
   </si>
   <si>
-    <t>九州第15 自 串木野五反川 至 薩肥国境</t>
+    <t>九州第十五 : 自串木野五反川至薩肥国境</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c93e2868-3dc1-3f38-81c1-9f9299e742b8.json</t>
@@ -1082,7 +1082,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c93e2868-3dc1-3f38-81c1-9f9299e742b8/manifest</t>
   </si>
   <si>
-    <t>九州第17甲 自 下松球ヲ村字段 至 有川村</t>
+    <t>九州第十七甲 : 自下松球麻村字段至有川村字合人吉街道</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/aa5277b2-2a68-564a-4701-407cce1315b9.json</t>
@@ -1106,7 +1106,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/aa5277b2-2a68-564a-4701-407cce1315b9/manifest</t>
   </si>
   <si>
-    <t>自 美濃不破郡赤坂宿谷汲山ヲ歴テ 至 山県郡岐阜町及厚見郡東鏡島鏡島村境</t>
+    <t>自美濃不破郡赤坂宿谷汲山ヲ歴テ至山縣郡岐阜町及厚見郡東鏡嶋鏡嶋村境 : 六分一里之図</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d938b608-1abf-69f9-8a44-69706dde9363.json</t>
@@ -1130,7 +1130,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d938b608-1abf-69f9-8a44-69706dde9363/manifest</t>
   </si>
   <si>
-    <t>中国第5番</t>
+    <t>中国第五番 : 三分図</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/65838979-81ec-576b-5db2-0bc138df26aa.json</t>
@@ -1154,7 +1154,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/65838979-81ec-576b-5db2-0bc138df26aa/manifest</t>
   </si>
   <si>
-    <t>中国第6番</t>
+    <t>中国第六番 : 三分図</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d55ba9e1-8361-6137-24b1-016c78878703.json</t>
@@ -1178,7 +1178,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d55ba9e1-8361-6137-24b1-016c78878703/manifest</t>
   </si>
   <si>
-    <t>中国第7番</t>
+    <t>中国第七番 : 三分之啚</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1d7df6f4-145b-7c54-83b5-035c90427359.json</t>
@@ -1202,7 +1202,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1d7df6f4-145b-7c54-83b5-035c90427359/manifest</t>
   </si>
   <si>
-    <t>中国第9番</t>
+    <t>中國第九圖 : 三分一里 / 平野縮圖</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/95990629-523a-7921-4215-324413fe2e3a.json</t>
@@ -1226,7 +1226,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/95990629-523a-7921-4215-324413fe2e3a/manifest</t>
   </si>
   <si>
-    <t>中国第10番</t>
+    <t>中國第十番 : 三分一里之圖 / 平野縮圖</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7dcc56fc-61f3-106e-11e2-1fbe3da1124e.json</t>
@@ -1250,7 +1250,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7dcc56fc-61f3-106e-11e2-1fbe3da1124e/manifest</t>
   </si>
   <si>
-    <t>中国第11番</t>
+    <t>中國第拾壹番 : 三分清圖</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9cd385e0-99d9-8e18-7b28-dddb54884bc4.json</t>
@@ -1274,7 +1274,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9cd385e0-99d9-8e18-7b28-dddb54884bc4/manifest</t>
   </si>
   <si>
-    <t>中国12番</t>
+    <t>中國十二番 : 三分一里之圖 / 平野縮圖</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/54228905-4145-3425-78c1-567f03507de4.json</t>
@@ -1298,7 +1298,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/54228905-4145-3425-78c1-567f03507de4/manifest</t>
   </si>
   <si>
-    <t>中国第13番</t>
+    <t>中國第十三圖 : 三分一里図 / 平野縮圖</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1ac7f767-1b66-67e7-6697-2a2de86844e9.json</t>
@@ -1322,7 +1322,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1ac7f767-1b66-67e7-6697-2a2de86844e9/manifest</t>
   </si>
   <si>
-    <t>中国第14番</t>
+    <t>中國第十四番 : 三分一里圖 / 平野縮</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6ab43728-1ef6-125c-6c13-534d0290195e.json</t>
@@ -1346,7 +1346,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6ab43728-1ef6-125c-6c13-534d0290195e/manifest</t>
   </si>
   <si>
-    <t>中国15番</t>
+    <t>中國拾五番 : 三分啚</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/12879a0e-60a6-1eaf-0e6a-fac487f49ce5.json</t>
@@ -1370,7 +1370,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/12879a0e-60a6-1eaf-0e6a-fac487f49ce5/manifest</t>
   </si>
   <si>
-    <t>中国第16番</t>
+    <t>中國第拾六番 : 三分啚</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/248668c6-50c2-1b90-a558-918849c140a0.json</t>
@@ -1394,7 +1394,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/248668c6-50c2-1b90-a558-918849c140a0/manifest</t>
   </si>
   <si>
-    <t>中国第17番</t>
+    <t>中國第拾七番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/08314ea5-1be0-5a1b-9bcf-09c51b240ffd.json</t>
@@ -1418,7 +1418,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/08314ea5-1be0-5a1b-9bcf-09c51b240ffd/manifest</t>
   </si>
   <si>
-    <t>中国第18番</t>
+    <t>中國第十八圖 : 三分一里圖 / 平野縮</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9a90cecc-0f65-a5f4-5e0d-2fae249057fb.json</t>
@@ -1442,7 +1442,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9a90cecc-0f65-a5f4-5e0d-2fae249057fb/manifest</t>
   </si>
   <si>
-    <t>中国19番</t>
+    <t>中國第拾九番 : 三分啚</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e0834548-a0f6-7b1f-3fc5-949c2ff374fd.json</t>
@@ -1466,7 +1466,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e0834548-a0f6-7b1f-3fc5-949c2ff374fd/manifest</t>
   </si>
   <si>
-    <t>中国23番</t>
+    <t>中国二十三番 : 三分図</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/08901ba3-64ce-7293-1703-e4fc4e955c7b.json</t>
@@ -1490,7 +1490,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/08901ba3-64ce-7293-1703-e4fc4e955c7b/manifest</t>
   </si>
   <si>
-    <t>中国27番</t>
+    <t>中国弐拾七番 : 三分啚</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2638742c-1cc1-8e30-8bf4-9bbf3dd77783.json</t>
@@ -1514,7 +1514,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2638742c-1cc1-8e30-8bf4-9bbf3dd77783/manifest</t>
   </si>
   <si>
-    <t>中国28番</t>
+    <t>中国廿八番 : 三分図</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9f730109-4c30-778a-0a70-cda4fd4b4cb1.json</t>
@@ -1538,7 +1538,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9f730109-4c30-778a-0a70-cda4fd4b4cb1/manifest</t>
   </si>
   <si>
-    <t>中国29番</t>
+    <t>中国廿九番 : 三分啚</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b50add2e-9cf8-4e80-6d7c-385a482c1d0f.json</t>
@@ -1562,7 +1562,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b50add2e-9cf8-4e80-6d7c-385a482c1d0f/manifest</t>
   </si>
   <si>
-    <t>中国31番</t>
+    <t>中国三十壹番 : 三分圖</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a48739d6-5abb-3d54-0779-14cf9ab85764.json</t>
@@ -1586,7 +1586,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a48739d6-5abb-3d54-0779-14cf9ab85764/manifest</t>
   </si>
   <si>
-    <t>52番</t>
+    <t>五十二番 : [高畑村-伊賀村]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/75bedba5-7b1d-31fc-15be-b4a1a2c56171.json</t>
@@ -1610,7 +1610,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/75bedba5-7b1d-31fc-15be-b4a1a2c56171/manifest</t>
   </si>
   <si>
-    <t>55番</t>
+    <t>第五十五番 : [北比良村-橋爪村]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cd181886-57c3-276c-2d0e-1417026a5c00.json</t>
@@ -1634,7 +1634,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cd181886-57c3-276c-2d0e-1417026a5c00/manifest</t>
   </si>
   <si>
-    <t>58番</t>
+    <t>五十八番 : [元比田村-片野村]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3b6bf159-46cb-0328-36bc-1860e2bf5e2b.json</t>
@@ -1658,7 +1658,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3b6bf159-46cb-0328-36bc-1860e2bf5e2b/manifest</t>
   </si>
   <si>
-    <t>58番属</t>
+    <t>五十八番属 : [加賀白山-冨士庄山]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7564e3ba-41f4-97f3-608c-7b8e524e4f09.json</t>
@@ -1682,7 +1682,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7564e3ba-41f4-97f3-608c-7b8e524e4f09/manifest</t>
   </si>
   <si>
-    <t>59番</t>
+    <t>五十九番 : [片野村-大野村]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b840752a-a204-65df-68c2-cc310f205a8e.json</t>
@@ -1706,7 +1706,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b840752a-a204-65df-68c2-cc310f205a8e/manifest</t>
   </si>
   <si>
-    <t>65番</t>
+    <t>六十五番 : [大井宿-細畑村]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c9d00e33-76ea-a419-3f44-3bd087c8a560.json</t>
@@ -1730,7 +1730,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c9d00e33-76ea-a419-3f44-3bd087c8a560/manifest</t>
   </si>
   <si>
-    <t>66番</t>
+    <t>六十六番 : [曽代村-付知村]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d7ab22f9-773f-36f7-085d-3397c1a4362f.json</t>
@@ -1754,7 +1754,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d7ab22f9-773f-36f7-085d-3397c1a4362f/manifest</t>
   </si>
   <si>
-    <t>70番</t>
+    <t>七十番 : [芋木村-川田村]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/05ec4eaf-700f-1568-247f-e938c63030d2.json</t>
@@ -1778,7 +1778,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/05ec4eaf-700f-1568-247f-e938c63030d2/manifest</t>
   </si>
   <si>
-    <t>72番</t>
+    <t>七十二番 : [蒲原-法京村]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4056c19f-0495-a797-3f31-d1206b137cc4.json</t>
@@ -1802,7 +1802,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4056c19f-0495-a797-3f31-d1206b137cc4/manifest</t>
   </si>
   <si>
-    <t>75番上</t>
+    <t>七十五番上 : [神津島, 式根島, 新島] : 三分啚</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/25870962-112e-7e74-a06f-80f7db8b4be9.json</t>
@@ -1826,7 +1826,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/25870962-112e-7e74-a06f-80f7db8b4be9/manifest</t>
   </si>
   <si>
-    <t>75番下属</t>
+    <t>七十五番下属 : [青ケ島]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3957e247-27be-0ab1-a0d2-041e50263235.json</t>
@@ -1850,7 +1850,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3957e247-27be-0ab1-a0d2-041e50263235/manifest</t>
   </si>
   <si>
-    <t>87番</t>
+    <t>八十七番 : [奈良井宿-馬場峠]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6620e99a-0352-5444-1048-a5f8b98e8235.json</t>
@@ -1874,7 +1874,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6620e99a-0352-5444-1048-a5f8b98e8235/manifest</t>
   </si>
   <si>
-    <t>88番</t>
+    <t>八十八番 : [八幡村-飯山町]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/eec35f9a-57e0-06d7-8d66-9677b8ac08af.json</t>
@@ -1898,7 +1898,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/eec35f9a-57e0-06d7-8d66-9677b8ac08af/manifest</t>
   </si>
   <si>
-    <t>89番</t>
+    <t>八拾九番 : 三分啚 : [浅貝-布施]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ebe69498-7390-234d-481e-637d73926ff5.json</t>
@@ -1922,7 +1922,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ebe69498-7390-234d-481e-637d73926ff5/manifest</t>
   </si>
   <si>
-    <t>98番</t>
+    <t>九十八番 : 三分圖 : [勝見-五十嵐濵]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0c01d6ca-5751-8947-8143-fcf0ee3d18f1.json</t>
@@ -1946,7 +1946,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0c01d6ca-5751-8947-8143-fcf0ee3d18f1/manifest</t>
   </si>
   <si>
-    <t>100番</t>
+    <t>百○○番 : 三分圖 : [関屋濵-塩谷]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/440cf55b-033f-a5e6-9749-3e4b20a82b9f.json</t>
@@ -1970,7 +1970,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/440cf55b-033f-a5e6-9749-3e4b20a82b9f/manifest</t>
   </si>
   <si>
-    <t>101番</t>
+    <t>百〇一番 : 三分図 : [塩谷-笹川]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f394d6ee-28b2-8e7e-0980-95fbb11e50c8.json</t>
@@ -1994,7 +1994,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f394d6ee-28b2-8e7e-0980-95fbb11e50c8/manifest</t>
   </si>
   <si>
-    <t>102番</t>
+    <t>百〇二番 : 三分図 : [大橋-原]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/51971aa4-1ab4-222c-20e5-938f734b1d19.json</t>
@@ -2018,7 +2018,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/51971aa4-1ab4-222c-20e5-938f734b1d19/manifest</t>
   </si>
   <si>
-    <t>103番</t>
+    <t>百〇三番 : 三分図 : [本内-尾濵]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fdfd4b34-8af3-213b-a143-4c1c0f1599fc.json</t>
@@ -2042,7 +2042,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fdfd4b34-8af3-213b-a143-4c1c0f1599fc/manifest</t>
   </si>
   <si>
-    <t>104番</t>
+    <t>百零四番 : 三分圖 : [笠石-五十邉]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8cc0214b-4812-5a69-910d-419b4ef00881.json</t>
@@ -2066,7 +2066,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8cc0214b-4812-5a69-910d-419b4ef00881/manifest</t>
   </si>
   <si>
-    <t>105番</t>
+    <t>百〇五番 : 三分圖 : [尾濵-波倉]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/302596c6-66df-6dc6-8940-e0b19b735341.json</t>
@@ -2090,7 +2090,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/302596c6-66df-6dc6-8940-e0b19b735341/manifest</t>
   </si>
   <si>
-    <t>106番</t>
+    <t>百〇六番 : 三分図 : [原-寺子]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/841f16f0-2064-4702-76e0-ef363c378fae.json</t>
@@ -2114,7 +2114,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/841f16f0-2064-4702-76e0-ef363c378fae/manifest</t>
   </si>
   <si>
-    <t>107番</t>
+    <t>百〇七番 : [波倉村-赤濵村]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/55052781-1682-201b-5052-e99de75156c6.json</t>
@@ -2138,7 +2138,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/55052781-1682-201b-5052-e99de75156c6/manifest</t>
   </si>
   <si>
-    <t>111番</t>
+    <t>百一十一番 : [大橋村-林﨑村]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c08c34e6-8e86-a080-6fc5-834e24bf1d90.json</t>
@@ -2162,7 +2162,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c08c34e6-8e86-a080-6fc5-834e24bf1d90/manifest</t>
   </si>
   <si>
-    <t>112番</t>
+    <t>百一十二番 : 三分啚 : [岩沼-高清水]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b06f7bc1-2145-a3b5-10e1-eeac7f120c17.json</t>
@@ -2186,7 +2186,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b06f7bc1-2145-a3b5-10e1-eeac7f120c17/manifest</t>
   </si>
   <si>
-    <t>113番</t>
+    <t>百一十三番 : [矢本村-岩尻村]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d1ea08d2-8f12-653b-67a1-0a07549a789a.json</t>
@@ -2210,7 +2210,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d1ea08d2-8f12-653b-67a1-0a07549a789a/manifest</t>
   </si>
   <si>
-    <t>114番</t>
+    <t>百一十四番 : [笹川村-三瀬村]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/158b9247-0412-3d99-3a57-a2bb12020b61.json</t>
@@ -2234,7 +2234,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/158b9247-0412-3d99-3a57-a2bb12020b61/manifest</t>
   </si>
   <si>
-    <t>116番</t>
+    <t>百一十六番 : [林﨑村-上院内村]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3e629cf3-2957-4a2f-78e3-7b47a83e1179.json</t>
@@ -2258,7 +2258,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3e629cf3-2957-4a2f-78e3-7b47a83e1179/manifest</t>
   </si>
   <si>
-    <t>120番</t>
+    <t>百二十〇番 : [羅賀村-吉里々々村]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7924e508-4765-997d-1f8b-de2d0ec171a6.json</t>
@@ -2282,7 +2282,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7924e508-4765-997d-1f8b-de2d0ec171a6/manifest</t>
   </si>
   <si>
-    <t>121番</t>
+    <t>百二十一番 : [川又村-足軽町]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/02219f57-a73d-861a-7ca5-f4396dd47bea.json</t>
@@ -2306,7 +2306,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/02219f57-a73d-861a-7ca5-f4396dd47bea/manifest</t>
   </si>
   <si>
-    <t>122番</t>
+    <t>百二十二番 : 三分図 : [樂師堂-金沢]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e0fbbbec-5e18-2b45-326b-02b328b18dd9.json</t>
@@ -2330,7 +2330,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e0fbbbec-5e18-2b45-326b-02b328b18dd9/manifest</t>
   </si>
   <si>
-    <t>123番</t>
+    <t>百二十三番 : [新屋村-小濵村]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6b2afb7f-15d0-15d1-6461-180003409672.json</t>
@@ -2354,7 +2354,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6b2afb7f-15d0-15d1-6461-180003409672/manifest</t>
   </si>
   <si>
-    <t>123番属</t>
+    <t>百二十三番屬 : 三分啚 : [太平山-森吉山]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a652cee8-3920-a0e5-990e-8c6c86207d3a.json</t>
@@ -2378,7 +2378,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a652cee8-3920-a0e5-990e-8c6c86207d3a/manifest</t>
   </si>
   <si>
-    <t>124番</t>
+    <t>百二十四番 : 三分啚 : [八森-白沢]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b91a51eb-218c-6e4f-6230-3f646c479ae7.json</t>
@@ -2402,7 +2402,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b91a51eb-218c-6e4f-6230-3f646c479ae7/manifest</t>
   </si>
   <si>
-    <t>125番</t>
+    <t>百二十五番 : [カワサワ村-柳平村]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c743d416-9539-a67d-4977-afa42a4351e0.json</t>
@@ -2426,7 +2426,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c743d416-9539-a67d-4977-afa42a4351e0/manifest</t>
   </si>
   <si>
-    <t>126番</t>
+    <t>百二十六番 : [金濵村-羅賀村]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/adb193f6-244b-a461-5b01-251713c165c9.json</t>
@@ -2450,7 +2450,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/adb193f6-244b-a461-5b01-251713c165c9/manifest</t>
   </si>
   <si>
-    <t>127番</t>
+    <t>百二十七番 : 三分図 : [天滿舘-三ノ戸]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d5859699-9b10-607a-14b5-69a058799a03.json</t>

--- a/docs/collections/sokuchigenkozu/metadata/data.xlsx
+++ b/docs/collections/sokuchigenkozu/metadata/data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="919">
   <si>
     <t>タイトル</t>
   </si>
@@ -242,7 +242,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b7d2dc7b-56a6-6182-0a85-90b5657b01ea/manifest</t>
   </si>
   <si>
-    <t>甲州巨摩郡自身延山山門之石至福士村人家前 : 三分一里之元図</t>
+    <t>[1]甲州巨摩郡自身延山山門之石至福士村人家前 : 三分一里之元図</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|甲州巨摩郡 自 身延山山門之石 至 福士村人家前</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0c6ecc75-597f-4469-8ba1-b70a5ff27fd8.json</t>
@@ -266,7 +269,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0c6ecc75-597f-4469-8ba1-b70a5ff27fd8/manifest</t>
   </si>
   <si>
-    <t>自辻堂村東海道追分至大山歴テ田原村制札</t>
+    <t>[2]自辻堂村東海道追分至大山歴テ田原村制札</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|自 辻堂村東海道追分 至 大山歴テ田原村制礼</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/eea7a8bd-7951-30a9-8c0c-5c0a56787b38.json</t>
@@ -290,7 +296,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/eea7a8bd-7951-30a9-8c0c-5c0a56787b38/manifest</t>
   </si>
   <si>
-    <t>従武州大里郡熊谷宿歴川越至入間郡大仙波新田大印 : 六分一里之圖</t>
+    <t>[3]従武州大里郡熊谷宿歴川越至入間郡大仙波新田大印 : 六分一里之圖</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|従 武州大里郡熊谷宿歴川越 至 入間郡大仙波新田</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e3cd2bc9-2785-451c-57ec-9dd080779fca.json</t>
@@ -314,7 +323,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e3cd2bc9-2785-451c-57ec-9dd080779fca/manifest</t>
   </si>
   <si>
-    <t>自江府深川測処至大堀村 : 㐧一圖之内猫実 : 六分一里の圖</t>
+    <t>[4]自江府深川測処至大堀村 : 㐧一圖之内猫実 : 六分一里の圖</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|自 江府深川測処 至 大堀村</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d1ba2b6b-19cd-9336-9d31-eca0f7f1a602.json</t>
@@ -338,7 +350,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d1ba2b6b-19cd-9336-9d31-eca0f7f1a602/manifest</t>
   </si>
   <si>
-    <t>自信州筑摩郡洗馬宿大門村歴松本至更級郡川中嶋塩崎江戸善光寺道追分并姨捨山 : 六分一里之圖</t>
+    <t>[5]自信州筑摩郡洗馬宿大門村歴松本至更級郡川中嶋塩崎江戸善光寺道追分并姨捨山 : 六分一里之圖</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|自 信州筑摩郡洗馬宿大門村歴松本 至 更級郡川中島塩崎</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/86168cb3-3911-6091-322c-efab3c982238.json</t>
@@ -362,7 +377,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/86168cb3-3911-6091-322c-efab3c982238/manifest</t>
   </si>
   <si>
-    <t>従飛刕大野郡無數河村ム印高山町ヲ歴至信刕筑摩郡藪原宿制札 : 六分一里之図</t>
+    <t>[6]従飛刕大野郡無數河村ム印高山町ヲ歴至信刕筑摩郡藪原宿制札 : 六分一里之図</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|従 飛州大野郡無敷河村 至 信州筑摩郡藪原宿制札</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4fa5f500-6b90-482f-5ed9-874f653504d8.json</t>
@@ -386,7 +404,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4fa5f500-6b90-482f-5ed9-874f653504d8/manifest</t>
   </si>
   <si>
-    <t>従信州佐久郡借宿村下仁田通り至武州兒玉郡本庄宿制札多胡碑 : 六分一里之図</t>
+    <t>[7]従信州佐久郡借宿村下仁田通り至武州兒玉郡本庄宿制札多胡碑 : 六分一里之図</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|従 信州佐久郡借宿村下仁田通リ 至 武州児玉郡本庄宿制札 多胡碑</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8ea3dff1-5584-4016-1b93-8b4298a3415e.json</t>
@@ -410,7 +431,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8ea3dff1-5584-4016-1b93-8b4298a3415e/manifest</t>
   </si>
   <si>
-    <t>従周防國吉敷郡山口道塲門前町至佐波郡東佐波令制札, 長門阿武郡地福村字掛, 周防吉敷郡宮野村枝七房, 防藝州界亀尾川峠 : 六分一里之図</t>
+    <t>[8]従周防國吉敷郡山口道塲門前町至佐波郡東佐波令制札, 長門阿武郡地福村字掛, 周防吉敷郡宮野村枝七房, 防藝州界亀尾川峠 : 六分一里之図</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|従 周防国吉敷郡山口道場門前町 至 佐波郡東佐波令制札, 長門阿武郡地福村字□, 周防吉敷郡宮野村□七房, 防芸州界亀尾川峠</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a27d5425-9b21-7938-1910-fc869954009d.json</t>
@@ -434,7 +458,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a27d5425-9b21-7938-1910-fc869954009d/manifest</t>
   </si>
   <si>
-    <t>従長門豊浦郡小月宿制札至阿武郡萩市中入口 : 六分一里之図</t>
+    <t>[9]従長門豊浦郡小月宿制札至阿武郡萩市中入口 : 六分一里之図</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|従 長門豊浦郡小月宿制札 至 阿武郡萩市中入口</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cbee3a35-3741-65a3-7482-aa1c2850438c.json</t>
@@ -458,7 +485,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cbee3a35-3741-65a3-7482-aa1c2850438c/manifest</t>
   </si>
   <si>
-    <t>自中山道歴名古屋至岡崎趣甲州街道二</t>
+    <t>[10]自中山道歴名古屋至岡崎趣甲州街道二</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|自 中山道歴名古屋 至 岡崎趣甲州街道 2</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/24d93f3d-7479-01c5-6bab-8cae59aca1ba.json</t>
@@ -482,7 +512,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/24d93f3d-7479-01c5-6bab-8cae59aca1ba/manifest</t>
   </si>
   <si>
-    <t>自岡嵜趣甲州街道三</t>
+    <t>[11]自岡嵜趣甲州街道三</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|自 岡崎趣甲州街道 3</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/355c0ab5-3ceb-0797-9343-5b6c273a6509.json</t>
@@ -506,7 +539,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/355c0ab5-3ceb-0797-9343-5b6c273a6509/manifest</t>
   </si>
   <si>
-    <t>[自葛西川村歴亀戸村小名木村至入舩町] : 三寸六分一里</t>
+    <t>[12][自葛西川村歴亀戸村小名木村至入舩町] : 三寸六分一里</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|[記載なし][葛西川村, 亀戸村, 小名木村 等]</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/94371ff9-2ba1-9e62-a307-cfa886dc6da4.json</t>
@@ -530,7 +566,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/94371ff9-2ba1-9e62-a307-cfa886dc6da4/manifest</t>
   </si>
   <si>
-    <t>岡嵜ヨリ甲州街道ニ趣五</t>
+    <t>[13]岡嵜ヨリ甲州街道ニ趣五</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|岡崎ヨリ甲州街道ニ趣 5</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fb41fbbc-6232-59a6-a516-be7750d633ee.json</t>
@@ -554,7 +593,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fb41fbbc-6232-59a6-a516-be7750d633ee/manifest</t>
   </si>
   <si>
-    <t>従信州水内郡長野村内善光寺宿善光寺門前飯山湏坂松代ヲ歴テ至高井郡屋代宿旧測印 : 六分一里之図</t>
+    <t>[14]従信州水内郡長野村内善光寺宿善光寺門前飯山湏坂松代ヲ歴テ至高井郡屋代宿旧測印 : 六分一里之図</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|従 信州水内郡長野村内善光寺宿善光寺門前飯山須坂松代ヲ歴テ 至 高井郡屋代宿</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/68cf6f00-3081-069c-0fb2-306b821f9815.json</t>
@@ -578,7 +620,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/68cf6f00-3081-069c-0fb2-306b821f9815/manifest</t>
   </si>
   <si>
-    <t>中山道六分之原圖四 : 從塩名田宿至贅河宿 : 自上原村塚原村界至贄川宿</t>
+    <t>[15]中山道六分之原圖四 : 從塩名田宿至贅河宿 : 自上原村塚原村界至贄川宿</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中山道六分之原図 4</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/285997ad-158b-843a-05c7-cfe8d95f9877.json</t>
@@ -602,7 +647,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/285997ad-158b-843a-05c7-cfe8d95f9877/manifest</t>
   </si>
   <si>
-    <t>中山道六分之元圖第六 : 自中河原至本郷村</t>
+    <t>[16]中山道六分之元圖第六 : 自中河原至本郷村</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中山道六分之元図 第6</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a7a3db90-5f23-5e18-86da-823535a3770b.json</t>
@@ -626,7 +674,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a7a3db90-5f23-5e18-86da-823535a3770b/manifest</t>
   </si>
   <si>
-    <t>中山道六分之原図五 : 六分一里之元圖 : 従贄川至野尻字中河原</t>
+    <t>[17]中山道六分之原図五 : 六分一里之元圖 : 従贄川至野尻字中河原</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中山道六分之原図 5</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d0bb794d-3918-6f23-666c-ce0c66eb4196.json</t>
@@ -650,7 +701,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d0bb794d-3918-6f23-666c-ce0c66eb4196/manifest</t>
   </si>
   <si>
-    <t>従作州大庭郡下長田村字犬挟峠長印至伯州日野郡二部村字間地, 備中阿賀郡小坂部村未年壬二月残印, 同上房郡片岡村字塩坪前同年残印, 作州大庭郡久世村原方中嶋村境中印 : 六分一里之圖</t>
+    <t>[18]従作州大庭郡下長田村字犬挟峠長印至伯州日野郡二部村字間地, 備中阿賀郡小坂部村未年壬二月残印, 同上房郡片岡村字塩坪前同年残印, 作州大庭郡久世村原方中嶋村境中印 : 六分一里之圖</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|従 作州大庭郡下長田村字犬挟峠 至 伯州日野郡二部村字間地, 備中阿賀郡小坂部村, 同上房郡□□村字塩坪, 作州大庭郡久世村歴方中嶋村境</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/828d4f3b-68ec-2870-2331-aedb9954109d.json</t>
@@ -674,7 +728,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/828d4f3b-68ec-2870-2331-aedb9954109d/manifest</t>
   </si>
   <si>
-    <t>西国街道五 : 自備後安那郡川北村神辺至安藝豊田郡夲郷村測処又福山測所 : 六分啚</t>
+    <t>[19]西国街道五 : 自備後安那郡川北村神辺至安藝豊田郡夲郷村測処又福山測所 : 六分啚</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|両国街道 5 自 備後安那郡川北村 至 安芸豊田郡本郷村</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d76eef77-a2fb-0ad5-7929-ba1bd036620e.json</t>
@@ -698,7 +755,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d76eef77-a2fb-0ad5-7929-ba1bd036620e/manifest</t>
   </si>
   <si>
-    <t>西国街道六 : 藝刕従豊田郡本郷村測所至安藝郡上瀬野村一貫田</t>
+    <t>[20]西国街道六 : 藝刕従豊田郡本郷村測所至安藝郡上瀬野村一貫田</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|両国街道 6 芸州 従 豊田郡本郷村 至 安芸郡上瀬野村</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5d6c36e2-5d9f-862e-5c08-07f8641c0d62.json</t>
@@ -722,7 +782,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5d6c36e2-5d9f-862e-5c08-07f8641c0d62/manifest</t>
   </si>
   <si>
-    <t>西国街道四 : 従岡山下町至神辺又油木八川ニ至ル : 六分一里之図</t>
+    <t>[21]西国街道四 : 従岡山下町至神辺又油木八川ニ至ル : 六分一里之図</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|両国街道 4 従 岡山下町 至 神辺又油木, 八川ニ至ル</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0e76e3be-97ce-0bde-521c-ce96ae7d2efd.json</t>
@@ -746,7 +809,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0e76e3be-97ce-0bde-521c-ce96ae7d2efd/manifest</t>
   </si>
   <si>
-    <t>西国街道一 : [従]山城淀測処[至]播磨神戸村 : 六分一里之図</t>
+    <t>[22]西国街道一 : [従]山城淀測処[至]播磨神戸村 : 六分一里之図</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|両国街道 1 山城淀, 播磨神戸村</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a0374157-4f3e-6c85-348b-38363d4a841f.json</t>
@@ -770,7 +836,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a0374157-4f3e-6c85-348b-38363d4a841f/manifest</t>
   </si>
   <si>
-    <t>従摂刕豊嶌郡半町止宿至播刕加西郡坂本村測処</t>
+    <t>[23]従摂刕豊嶌郡半町止宿至播刕加西郡坂本村測処</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|従 摂州豊島郡半町止宿 至 播州加西郡坂本村</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/31606d80-64cd-7362-4302-35e960f900e8.json</t>
@@ -794,7 +863,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/31606d80-64cd-7362-4302-35e960f900e8/manifest</t>
   </si>
   <si>
-    <t>第三十七番 : 自田老村至唐舟之圖</t>
+    <t>[24]第三十七番 : 自田老村至唐舟之圖</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|第37番 自 田老村 至 唐舟之図</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d8694eeb-a144-4b6b-07d8-1a3bbca66089.json</t>
@@ -818,7 +890,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d8694eeb-a144-4b6b-07d8-1a3bbca66089/manifest</t>
   </si>
   <si>
-    <t>第卅八番 : 自唐舟至岩尻村圖</t>
+    <t>[25]第卅八番 : 自唐舟至岩尻村圖</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|第38番 自 唐舟 至 岩尻村図</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cff7647e-93b0-1c96-109e-dea91230a63e.json</t>
@@ -842,7 +917,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cff7647e-93b0-1c96-109e-dea91230a63e/manifest</t>
   </si>
   <si>
-    <t>第四番 : 自白川至矢吹六分圖 , 第五番 : 自矢吹至清水町圖</t>
+    <t>[26]第四番 : 自白川至矢吹六分圖 , 第五番 : 自矢吹至清水町圖</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|第4番 自 白川 至 矢吹, 第5番 自 矢吹 至 清水町図</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f2c3ea81-1462-3963-1747-6692f3cb29fa.json</t>
@@ -866,7 +944,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f2c3ea81-1462-3963-1747-6692f3cb29fa/manifest</t>
   </si>
   <si>
-    <t>西國街道三 : 自播磨揖西郡正条至備前御野郡岡山下町 : 六分之図</t>
+    <t>[27]西國街道三 : 自播磨揖西郡正条至備前御野郡岡山下町 : 六分之図</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|西国街道 3 自 播磨揖西郡正条 至 備前御野郡岡山</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/053829e7-2a8c-079b-3181-9cd265bf95a5.json</t>
@@ -890,7 +971,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/053829e7-2a8c-079b-3181-9cd265bf95a5/manifest</t>
   </si>
   <si>
-    <t>自大隅國桑原郡濵市村野尻ヲ歴テ加久藤本庄ニ至ル : 六分一里之図</t>
+    <t>[28]自大隅國桑原郡濵市村野尻ヲ歴テ加久藤本庄ニ至ル : 六分一里之図</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|自 大隅国桑原郡濱市村野尻ヲ歴テ加久藤, 本庄ニ至ル</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4ac68437-8c91-8042-9c2f-bb50ee060488.json</t>
@@ -914,7 +998,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4ac68437-8c91-8042-9c2f-bb50ee060488/manifest</t>
   </si>
   <si>
-    <t>日向本庄村佐土原幸脇ヲ歴恒冨村ニ至ル : 附米良道南方村椎葉道神門村ニ至ル : 六分一里之図</t>
+    <t>[29]日向本庄村佐土原幸脇ヲ歴恒冨村ニ至ル : 附米良道南方村椎葉道神門村ニ至ル : 六分一里之図</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|日向本庄村佐土原, 幸州ヲ歴恒冨村ニ至ル</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f3f2230c-9d58-2bb7-875f-2ec3e4092df2.json</t>
@@ -938,7 +1025,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f3f2230c-9d58-2bb7-875f-2ec3e4092df2/manifest</t>
   </si>
   <si>
-    <t>九州第七 : 日向國平岩才脇境ヨリ田吉村八手迠 : 六分之源図</t>
+    <t>[30]九州第七 : 日向國平岩才脇境ヨリ田吉村八手迠 : 六分之源図</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|九州第7 日向国 平岩才脇境ヨリ田吉村八手迄</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/04781c89-7280-6c75-3b54-5f93d96d9590.json</t>
@@ -962,7 +1052,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/04781c89-7280-6c75-3b54-5f93d96d9590/manifest</t>
   </si>
   <si>
-    <t>九州第八 : 日向自田吉村字八手至贄波海北村界 : 附牛ヶ嶺迠 : 六分之源図</t>
+    <t>[31]九州第八 : 日向自田吉村字八手至贄波海北村界 : 附牛ヶ嶺迠 : 六分之源図</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|九州第8 日向 田吉村字八手 至 贄波海北村界</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2003763f-55a3-9ffa-7684-536a955458c8.json</t>
@@ -986,7 +1079,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2003763f-55a3-9ffa-7684-536a955458c8/manifest</t>
   </si>
   <si>
-    <t>九州第十二 : 自廻村牧場至牛ヶ嶺</t>
+    <t>[32]九州第十二 : 自廻村牧場至牛ヶ嶺</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|九州第12 自 廻村牧場 至 牛ヶ嶺</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9cfe1650-28b3-8367-61b5-b20ab9ca10d3.json</t>
@@ -1010,7 +1106,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9cfe1650-28b3-8367-61b5-b20ab9ca10d3/manifest</t>
   </si>
   <si>
-    <t>九刕第十三 : 自鹿児嶋城下街道追分至御領村之内石垣浦 : 附肥後街道清藤村迠</t>
+    <t>[33]九刕第十三 : 自鹿児嶋城下街道追分至御領村之内石垣浦 : 附肥後街道清藤村迠</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|九州第13 自 鹿児島城下街道追分 至 御領村</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a9f0e478-44c6-4a8a-954e-9aacf0bc59c6.json</t>
@@ -1034,7 +1133,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a9f0e478-44c6-4a8a-954e-9aacf0bc59c6/manifest</t>
   </si>
   <si>
-    <t>九州第十四 : 自御領村石垣浦至串木野五反川 : 附肥後街道清藤村より市来湊迠</t>
+    <t>[34]九州第十四 : 自御領村石垣浦至串木野五反川 : 附肥後街道清藤村より市来湊迠</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|九州14 自 御領村 至 串木野五反川</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1872793a-16cb-96f4-5d5d-44874d800e1e.json</t>
@@ -1058,7 +1160,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1872793a-16cb-96f4-5d5d-44874d800e1e/manifest</t>
   </si>
   <si>
-    <t>九州第十五 : 自串木野五反川至薩肥国境</t>
+    <t>[35]九州第十五 : 自串木野五反川至薩肥国境</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|九州第15 自 串木野五反川 至 薩肥国境</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c93e2868-3dc1-3f38-81c1-9f9299e742b8.json</t>
@@ -1082,7 +1187,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c93e2868-3dc1-3f38-81c1-9f9299e742b8/manifest</t>
   </si>
   <si>
-    <t>九州第十七甲 : 自下松球麻村字段至有川村字合人吉街道</t>
+    <t>[36]九州第十七甲 : 自下松球麻村字段至有川村字合人吉街道</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|九州第17甲 自 下松球ヲ村字段 至 有川村</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/aa5277b2-2a68-564a-4701-407cce1315b9.json</t>
@@ -1106,7 +1214,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/aa5277b2-2a68-564a-4701-407cce1315b9/manifest</t>
   </si>
   <si>
-    <t>自美濃不破郡赤坂宿谷汲山ヲ歴テ至山縣郡岐阜町及厚見郡東鏡嶋鏡嶋村境 : 六分一里之図</t>
+    <t>[37]自美濃不破郡赤坂宿谷汲山ヲ歴テ至山縣郡岐阜町及厚見郡東鏡嶋鏡嶋村境 : 六分一里之図</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|自 美濃不破郡赤坂宿谷汲山ヲ歴テ 至 山県郡岐阜町及厚見郡東鏡島鏡島村境</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d938b608-1abf-69f9-8a44-69706dde9363.json</t>
@@ -1130,7 +1241,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d938b608-1abf-69f9-8a44-69706dde9363/manifest</t>
   </si>
   <si>
-    <t>中国第五番 : 三分図</t>
+    <t>[38]中国第五番 : 三分図</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中国第5番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/65838979-81ec-576b-5db2-0bc138df26aa.json</t>
@@ -1154,7 +1268,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/65838979-81ec-576b-5db2-0bc138df26aa/manifest</t>
   </si>
   <si>
-    <t>中国第六番 : 三分図</t>
+    <t>[39]中国第六番 : 三分図</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中国第6番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d55ba9e1-8361-6137-24b1-016c78878703.json</t>
@@ -1178,7 +1295,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d55ba9e1-8361-6137-24b1-016c78878703/manifest</t>
   </si>
   <si>
-    <t>中国第七番 : 三分之啚</t>
+    <t>[40]中国第七番 : 三分之啚</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中国第7番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1d7df6f4-145b-7c54-83b5-035c90427359.json</t>
@@ -1202,7 +1322,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1d7df6f4-145b-7c54-83b5-035c90427359/manifest</t>
   </si>
   <si>
-    <t>中國第九圖 : 三分一里 / 平野縮圖</t>
+    <t>[41]中國第九圖 : 三分一里 / 平野縮圖</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中国第9番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/95990629-523a-7921-4215-324413fe2e3a.json</t>
@@ -1226,7 +1349,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/95990629-523a-7921-4215-324413fe2e3a/manifest</t>
   </si>
   <si>
-    <t>中國第十番 : 三分一里之圖 / 平野縮圖</t>
+    <t>[42]中國第十番 : 三分一里之圖 / 平野縮圖</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中国第10番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7dcc56fc-61f3-106e-11e2-1fbe3da1124e.json</t>
@@ -1250,7 +1376,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7dcc56fc-61f3-106e-11e2-1fbe3da1124e/manifest</t>
   </si>
   <si>
-    <t>中國第拾壹番 : 三分清圖</t>
+    <t>[43]中國第拾壹番 : 三分清圖</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中国第11番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9cd385e0-99d9-8e18-7b28-dddb54884bc4.json</t>
@@ -1274,7 +1403,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9cd385e0-99d9-8e18-7b28-dddb54884bc4/manifest</t>
   </si>
   <si>
-    <t>中國十二番 : 三分一里之圖 / 平野縮圖</t>
+    <t>[44]中國十二番 : 三分一里之圖 / 平野縮圖</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中国12番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/54228905-4145-3425-78c1-567f03507de4.json</t>
@@ -1298,7 +1430,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/54228905-4145-3425-78c1-567f03507de4/manifest</t>
   </si>
   <si>
-    <t>中國第十三圖 : 三分一里図 / 平野縮圖</t>
+    <t>[45]中國第十三圖 : 三分一里図 / 平野縮圖</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中国第13番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1ac7f767-1b66-67e7-6697-2a2de86844e9.json</t>
@@ -1322,7 +1457,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1ac7f767-1b66-67e7-6697-2a2de86844e9/manifest</t>
   </si>
   <si>
-    <t>中國第十四番 : 三分一里圖 / 平野縮</t>
+    <t>[46]中國第十四番 : 三分一里圖 / 平野縮</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中国第14番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6ab43728-1ef6-125c-6c13-534d0290195e.json</t>
@@ -1346,7 +1484,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6ab43728-1ef6-125c-6c13-534d0290195e/manifest</t>
   </si>
   <si>
-    <t>中國拾五番 : 三分啚</t>
+    <t>[47]中國拾五番 : 三分啚</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中国15番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/12879a0e-60a6-1eaf-0e6a-fac487f49ce5.json</t>
@@ -1370,7 +1511,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/12879a0e-60a6-1eaf-0e6a-fac487f49ce5/manifest</t>
   </si>
   <si>
-    <t>中國第拾六番 : 三分啚</t>
+    <t>[48]中國第拾六番 : 三分啚</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中国第16番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/248668c6-50c2-1b90-a558-918849c140a0.json</t>
@@ -1394,7 +1538,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/248668c6-50c2-1b90-a558-918849c140a0/manifest</t>
   </si>
   <si>
-    <t>中國第拾七番</t>
+    <t>[49]中國第拾七番</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中国第17番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/08314ea5-1be0-5a1b-9bcf-09c51b240ffd.json</t>
@@ -1418,7 +1565,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/08314ea5-1be0-5a1b-9bcf-09c51b240ffd/manifest</t>
   </si>
   <si>
-    <t>中國第十八圖 : 三分一里圖 / 平野縮</t>
+    <t>[50]中國第十八圖 : 三分一里圖 / 平野縮</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中国第18番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9a90cecc-0f65-a5f4-5e0d-2fae249057fb.json</t>
@@ -1442,7 +1592,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9a90cecc-0f65-a5f4-5e0d-2fae249057fb/manifest</t>
   </si>
   <si>
-    <t>中國第拾九番 : 三分啚</t>
+    <t>[51]中國第拾九番 : 三分啚</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中国19番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e0834548-a0f6-7b1f-3fc5-949c2ff374fd.json</t>
@@ -1466,7 +1619,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e0834548-a0f6-7b1f-3fc5-949c2ff374fd/manifest</t>
   </si>
   <si>
-    <t>中国二十三番 : 三分図</t>
+    <t>[52]中国二十三番 : 三分図</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中国23番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/08901ba3-64ce-7293-1703-e4fc4e955c7b.json</t>
@@ -1490,7 +1646,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/08901ba3-64ce-7293-1703-e4fc4e955c7b/manifest</t>
   </si>
   <si>
-    <t>中国弐拾七番 : 三分啚</t>
+    <t>[53]中国弐拾七番 : 三分啚</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中国27番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2638742c-1cc1-8e30-8bf4-9bbf3dd77783.json</t>
@@ -1514,7 +1673,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2638742c-1cc1-8e30-8bf4-9bbf3dd77783/manifest</t>
   </si>
   <si>
-    <t>中国廿八番 : 三分図</t>
+    <t>[54]中国廿八番 : 三分図</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中国28番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9f730109-4c30-778a-0a70-cda4fd4b4cb1.json</t>
@@ -1538,7 +1700,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9f730109-4c30-778a-0a70-cda4fd4b4cb1/manifest</t>
   </si>
   <si>
-    <t>中国廿九番 : 三分啚</t>
+    <t>[55]中国廿九番 : 三分啚</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中国29番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b50add2e-9cf8-4e80-6d7c-385a482c1d0f.json</t>
@@ -1562,7 +1727,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b50add2e-9cf8-4e80-6d7c-385a482c1d0f/manifest</t>
   </si>
   <si>
-    <t>中国三十壹番 : 三分圖</t>
+    <t>[56]中国三十壹番 : 三分圖</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|中国31番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a48739d6-5abb-3d54-0779-14cf9ab85764.json</t>
@@ -1586,7 +1754,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a48739d6-5abb-3d54-0779-14cf9ab85764/manifest</t>
   </si>
   <si>
-    <t>五十二番 : [高畑村-伊賀村]</t>
+    <t>[57]五十二番 : [高畑村-伊賀村]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|52番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/75bedba5-7b1d-31fc-15be-b4a1a2c56171.json</t>
@@ -1610,7 +1781,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/75bedba5-7b1d-31fc-15be-b4a1a2c56171/manifest</t>
   </si>
   <si>
-    <t>第五十五番 : [北比良村-橋爪村]</t>
+    <t>[58]第五十五番 : [北比良村-橋爪村]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|55番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cd181886-57c3-276c-2d0e-1417026a5c00.json</t>
@@ -1634,7 +1808,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cd181886-57c3-276c-2d0e-1417026a5c00/manifest</t>
   </si>
   <si>
-    <t>五十八番 : [元比田村-片野村]</t>
+    <t>[59]五十八番 : [元比田村-片野村]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|58番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3b6bf159-46cb-0328-36bc-1860e2bf5e2b.json</t>
@@ -1658,7 +1835,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3b6bf159-46cb-0328-36bc-1860e2bf5e2b/manifest</t>
   </si>
   <si>
-    <t>五十八番属 : [加賀白山-冨士庄山]</t>
+    <t>[60]五十八番属 : [加賀白山-冨士庄山]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|58番属</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7564e3ba-41f4-97f3-608c-7b8e524e4f09.json</t>
@@ -1682,7 +1862,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7564e3ba-41f4-97f3-608c-7b8e524e4f09/manifest</t>
   </si>
   <si>
-    <t>五十九番 : [片野村-大野村]</t>
+    <t>[61]五十九番 : [片野村-大野村]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|59番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b840752a-a204-65df-68c2-cc310f205a8e.json</t>
@@ -1706,7 +1889,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b840752a-a204-65df-68c2-cc310f205a8e/manifest</t>
   </si>
   <si>
-    <t>六十五番 : [大井宿-細畑村]</t>
+    <t>[62]六十五番 : [大井宿-細畑村]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|65番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c9d00e33-76ea-a419-3f44-3bd087c8a560.json</t>
@@ -1730,7 +1916,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c9d00e33-76ea-a419-3f44-3bd087c8a560/manifest</t>
   </si>
   <si>
-    <t>六十六番 : [曽代村-付知村]</t>
+    <t>[63]六十六番 : [曽代村-付知村]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|66番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d7ab22f9-773f-36f7-085d-3397c1a4362f.json</t>
@@ -1754,7 +1943,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d7ab22f9-773f-36f7-085d-3397c1a4362f/manifest</t>
   </si>
   <si>
-    <t>七十番 : [芋木村-川田村]</t>
+    <t>[64]七十番 : [芋木村-川田村]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|70番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/05ec4eaf-700f-1568-247f-e938c63030d2.json</t>
@@ -1778,7 +1970,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/05ec4eaf-700f-1568-247f-e938c63030d2/manifest</t>
   </si>
   <si>
-    <t>七十二番 : [蒲原-法京村]</t>
+    <t>[65]七十二番 : [蒲原-法京村]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|72番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4056c19f-0495-a797-3f31-d1206b137cc4.json</t>
@@ -1802,7 +1997,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4056c19f-0495-a797-3f31-d1206b137cc4/manifest</t>
   </si>
   <si>
-    <t>七十五番上 : [神津島, 式根島, 新島] : 三分啚</t>
+    <t>[66]七十五番上 : [神津島, 式根島, 新島] : 三分啚</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|75番上</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/25870962-112e-7e74-a06f-80f7db8b4be9.json</t>
@@ -1826,7 +2024,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/25870962-112e-7e74-a06f-80f7db8b4be9/manifest</t>
   </si>
   <si>
-    <t>七十五番下属 : [青ケ島]</t>
+    <t>[67]七十五番下属 : [青ケ島]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|75番下属</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3957e247-27be-0ab1-a0d2-041e50263235.json</t>
@@ -1850,7 +2051,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3957e247-27be-0ab1-a0d2-041e50263235/manifest</t>
   </si>
   <si>
-    <t>八十七番 : [奈良井宿-馬場峠]</t>
+    <t>[68]八十七番 : [奈良井宿-馬場峠]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|87番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6620e99a-0352-5444-1048-a5f8b98e8235.json</t>
@@ -1874,7 +2078,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6620e99a-0352-5444-1048-a5f8b98e8235/manifest</t>
   </si>
   <si>
-    <t>八十八番 : [八幡村-飯山町]</t>
+    <t>[69]八十八番 : [八幡村-飯山町]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|88番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/eec35f9a-57e0-06d7-8d66-9677b8ac08af.json</t>
@@ -1898,7 +2105,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/eec35f9a-57e0-06d7-8d66-9677b8ac08af/manifest</t>
   </si>
   <si>
-    <t>八拾九番 : 三分啚 : [浅貝-布施]</t>
+    <t>[70]八拾九番 : 三分啚 : [浅貝-布施]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|89番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ebe69498-7390-234d-481e-637d73926ff5.json</t>
@@ -1922,7 +2132,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ebe69498-7390-234d-481e-637d73926ff5/manifest</t>
   </si>
   <si>
-    <t>九十八番 : 三分圖 : [勝見-五十嵐濵]</t>
+    <t>[71]九十八番 : 三分圖 : [勝見-五十嵐濵]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|98番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0c01d6ca-5751-8947-8143-fcf0ee3d18f1.json</t>
@@ -1946,7 +2159,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0c01d6ca-5751-8947-8143-fcf0ee3d18f1/manifest</t>
   </si>
   <si>
-    <t>百○○番 : 三分圖 : [関屋濵-塩谷]</t>
+    <t>[72]百○○番 : 三分圖 : [関屋濵-塩谷]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|100番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/440cf55b-033f-a5e6-9749-3e4b20a82b9f.json</t>
@@ -1970,7 +2186,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/440cf55b-033f-a5e6-9749-3e4b20a82b9f/manifest</t>
   </si>
   <si>
-    <t>百〇一番 : 三分図 : [塩谷-笹川]</t>
+    <t>[73]百〇一番 : 三分図 : [塩谷-笹川]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|101番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f394d6ee-28b2-8e7e-0980-95fbb11e50c8.json</t>
@@ -1994,7 +2213,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f394d6ee-28b2-8e7e-0980-95fbb11e50c8/manifest</t>
   </si>
   <si>
-    <t>百〇二番 : 三分図 : [大橋-原]</t>
+    <t>[74]百〇二番 : 三分図 : [大橋-原]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|102番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/51971aa4-1ab4-222c-20e5-938f734b1d19.json</t>
@@ -2018,7 +2240,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/51971aa4-1ab4-222c-20e5-938f734b1d19/manifest</t>
   </si>
   <si>
-    <t>百〇三番 : 三分図 : [本内-尾濵]</t>
+    <t>[75]百〇三番 : 三分図 : [本内-尾濵]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|103番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fdfd4b34-8af3-213b-a143-4c1c0f1599fc.json</t>
@@ -2042,7 +2267,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fdfd4b34-8af3-213b-a143-4c1c0f1599fc/manifest</t>
   </si>
   <si>
-    <t>百零四番 : 三分圖 : [笠石-五十邉]</t>
+    <t>[76]百零四番 : 三分圖 : [笠石-五十邉]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|104番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8cc0214b-4812-5a69-910d-419b4ef00881.json</t>
@@ -2066,7 +2294,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8cc0214b-4812-5a69-910d-419b4ef00881/manifest</t>
   </si>
   <si>
-    <t>百〇五番 : 三分圖 : [尾濵-波倉]</t>
+    <t>[77]百〇五番 : 三分圖 : [尾濵-波倉]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|105番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/302596c6-66df-6dc6-8940-e0b19b735341.json</t>
@@ -2090,7 +2321,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/302596c6-66df-6dc6-8940-e0b19b735341/manifest</t>
   </si>
   <si>
-    <t>百〇六番 : 三分図 : [原-寺子]</t>
+    <t>[78]百〇六番 : 三分図 : [原-寺子]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|106番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/841f16f0-2064-4702-76e0-ef363c378fae.json</t>
@@ -2114,7 +2348,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/841f16f0-2064-4702-76e0-ef363c378fae/manifest</t>
   </si>
   <si>
-    <t>百〇七番 : [波倉村-赤濵村]</t>
+    <t>[79]百〇七番 : [波倉村-赤濵村]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|107番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/55052781-1682-201b-5052-e99de75156c6.json</t>
@@ -2138,7 +2375,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/55052781-1682-201b-5052-e99de75156c6/manifest</t>
   </si>
   <si>
-    <t>百一十一番 : [大橋村-林﨑村]</t>
+    <t>[80]百一十一番 : [大橋村-林﨑村]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|111番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c08c34e6-8e86-a080-6fc5-834e24bf1d90.json</t>
@@ -2162,7 +2402,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c08c34e6-8e86-a080-6fc5-834e24bf1d90/manifest</t>
   </si>
   <si>
-    <t>百一十二番 : 三分啚 : [岩沼-高清水]</t>
+    <t>[81]百一十二番 : 三分啚 : [岩沼-高清水]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|112番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b06f7bc1-2145-a3b5-10e1-eeac7f120c17.json</t>
@@ -2186,7 +2429,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b06f7bc1-2145-a3b5-10e1-eeac7f120c17/manifest</t>
   </si>
   <si>
-    <t>百一十三番 : [矢本村-岩尻村]</t>
+    <t>[82]百一十三番 : [矢本村-岩尻村]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|113番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d1ea08d2-8f12-653b-67a1-0a07549a789a.json</t>
@@ -2210,7 +2456,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d1ea08d2-8f12-653b-67a1-0a07549a789a/manifest</t>
   </si>
   <si>
-    <t>百一十四番 : [笹川村-三瀬村]</t>
+    <t>[83]百一十四番 : [笹川村-三瀬村]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|114番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/158b9247-0412-3d99-3a57-a2bb12020b61.json</t>
@@ -2234,7 +2483,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/158b9247-0412-3d99-3a57-a2bb12020b61/manifest</t>
   </si>
   <si>
-    <t>百一十六番 : [林﨑村-上院内村]</t>
+    <t>[84]百一十六番 : [林﨑村-上院内村]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|116番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3e629cf3-2957-4a2f-78e3-7b47a83e1179.json</t>
@@ -2258,7 +2510,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3e629cf3-2957-4a2f-78e3-7b47a83e1179/manifest</t>
   </si>
   <si>
-    <t>百二十〇番 : [羅賀村-吉里々々村]</t>
+    <t>[85]百二十〇番 : [羅賀村-吉里々々村]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|120番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7924e508-4765-997d-1f8b-de2d0ec171a6.json</t>
@@ -2282,7 +2537,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7924e508-4765-997d-1f8b-de2d0ec171a6/manifest</t>
   </si>
   <si>
-    <t>百二十一番 : [川又村-足軽町]</t>
+    <t>[86]百二十一番 : [川又村-足軽町]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|121番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/02219f57-a73d-861a-7ca5-f4396dd47bea.json</t>
@@ -2306,7 +2564,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/02219f57-a73d-861a-7ca5-f4396dd47bea/manifest</t>
   </si>
   <si>
-    <t>百二十二番 : 三分図 : [樂師堂-金沢]</t>
+    <t>[87]百二十二番 : 三分図 : [樂師堂-金沢]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|122番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e0fbbbec-5e18-2b45-326b-02b328b18dd9.json</t>
@@ -2330,7 +2591,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e0fbbbec-5e18-2b45-326b-02b328b18dd9/manifest</t>
   </si>
   <si>
-    <t>百二十三番 : [新屋村-小濵村]</t>
+    <t>[88]百二十三番 : [新屋村-小濵村]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|123番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6b2afb7f-15d0-15d1-6461-180003409672.json</t>
@@ -2354,7 +2618,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6b2afb7f-15d0-15d1-6461-180003409672/manifest</t>
   </si>
   <si>
-    <t>百二十三番屬 : 三分啚 : [太平山-森吉山]</t>
+    <t>[89]百二十三番屬 : 三分啚 : [太平山-森吉山]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|123番属</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a652cee8-3920-a0e5-990e-8c6c86207d3a.json</t>
@@ -2378,7 +2645,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a652cee8-3920-a0e5-990e-8c6c86207d3a/manifest</t>
   </si>
   <si>
-    <t>百二十四番 : 三分啚 : [八森-白沢]</t>
+    <t>[90]百二十四番 : 三分啚 : [八森-白沢]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|124番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b91a51eb-218c-6e4f-6230-3f646c479ae7.json</t>
@@ -2402,7 +2672,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b91a51eb-218c-6e4f-6230-3f646c479ae7/manifest</t>
   </si>
   <si>
-    <t>百二十五番 : [カワサワ村-柳平村]</t>
+    <t>[91]百二十五番 : [カワサワ村-柳平村]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|125番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c743d416-9539-a67d-4977-afa42a4351e0.json</t>
@@ -2426,7 +2699,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c743d416-9539-a67d-4977-afa42a4351e0/manifest</t>
   </si>
   <si>
-    <t>百二十六番 : [金濵村-羅賀村]</t>
+    <t>[92]百二十六番 : [金濵村-羅賀村]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|126番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/adb193f6-244b-a461-5b01-251713c165c9.json</t>
@@ -2450,7 +2726,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/adb193f6-244b-a461-5b01-251713c165c9/manifest</t>
   </si>
   <si>
-    <t>百二十七番 : 三分図 : [天滿舘-三ノ戸]</t>
+    <t>[93]百二十七番 : 三分図 : [天滿舘-三ノ戸]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|127番</t>
   </si>
   <si>
     <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d5859699-9b10-607a-14b5-69a058799a03.json</t>
@@ -3088,7 +3367,7 @@
         <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
         <v>58</v>
@@ -3106,25 +3385,25 @@
         <v>62</v>
       </c>
       <c r="J4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L4" t="s">
         <v>65</v>
       </c>
       <c r="M4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N4" t="s">
         <v>67</v>
       </c>
       <c r="O4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q4" t="s">
         <v>70</v>
@@ -3137,11 +3416,11 @@
         <v>72</v>
       </c>
       <c r="U4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V4" t="s"/>
       <c r="W4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X4" t="s"/>
       <c r="Y4" t="s"/>
@@ -3153,7 +3432,7 @@
     </row>
     <row r="5" spans="1:28">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -3162,7 +3441,7 @@
         <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
         <v>58</v>
@@ -3180,25 +3459,25 @@
         <v>62</v>
       </c>
       <c r="J5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L5" t="s">
         <v>65</v>
       </c>
       <c r="M5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N5" t="s">
         <v>67</v>
       </c>
       <c r="O5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q5" t="s">
         <v>70</v>
@@ -3211,11 +3490,11 @@
         <v>72</v>
       </c>
       <c r="U5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="V5" t="s"/>
       <c r="W5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="X5" t="s"/>
       <c r="Y5" t="s"/>
@@ -3227,7 +3506,7 @@
     </row>
     <row r="6" spans="1:28">
       <c r="A6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -3236,7 +3515,7 @@
         <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
         <v>58</v>
@@ -3254,25 +3533,25 @@
         <v>62</v>
       </c>
       <c r="J6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="L6" t="s">
         <v>65</v>
       </c>
       <c r="M6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="N6" t="s">
         <v>67</v>
       </c>
       <c r="O6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="P6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Q6" t="s">
         <v>70</v>
@@ -3285,11 +3564,11 @@
         <v>72</v>
       </c>
       <c r="U6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="V6" t="s"/>
       <c r="W6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="X6" t="s"/>
       <c r="Y6" t="s"/>
@@ -3301,7 +3580,7 @@
     </row>
     <row r="7" spans="1:28">
       <c r="A7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
@@ -3310,7 +3589,7 @@
         <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
         <v>58</v>
@@ -3328,25 +3607,25 @@
         <v>62</v>
       </c>
       <c r="J7" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K7" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="L7" t="s">
         <v>65</v>
       </c>
       <c r="M7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="N7" t="s">
         <v>67</v>
       </c>
       <c r="O7" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="P7" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="Q7" t="s">
         <v>70</v>
@@ -3359,11 +3638,11 @@
         <v>72</v>
       </c>
       <c r="U7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="V7" t="s"/>
       <c r="W7" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="X7" t="s"/>
       <c r="Y7" t="s"/>
@@ -3375,7 +3654,7 @@
     </row>
     <row r="8" spans="1:28">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B8" t="s">
         <v>55</v>
@@ -3384,7 +3663,7 @@
         <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
         <v>58</v>
@@ -3402,25 +3681,25 @@
         <v>62</v>
       </c>
       <c r="J8" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K8" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="L8" t="s">
         <v>65</v>
       </c>
       <c r="M8" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="N8" t="s">
         <v>67</v>
       </c>
       <c r="O8" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="P8" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="Q8" t="s">
         <v>70</v>
@@ -3433,11 +3712,11 @@
         <v>72</v>
       </c>
       <c r="U8" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="V8" t="s"/>
       <c r="W8" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="X8" t="s"/>
       <c r="Y8" t="s"/>
@@ -3449,7 +3728,7 @@
     </row>
     <row r="9" spans="1:28">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B9" t="s">
         <v>55</v>
@@ -3458,7 +3737,7 @@
         <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="E9" t="s">
         <v>58</v>
@@ -3476,25 +3755,25 @@
         <v>62</v>
       </c>
       <c r="J9" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="K9" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="L9" t="s">
         <v>65</v>
       </c>
       <c r="M9" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="N9" t="s">
         <v>67</v>
       </c>
       <c r="O9" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="P9" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="Q9" t="s">
         <v>70</v>
@@ -3507,11 +3786,11 @@
         <v>72</v>
       </c>
       <c r="U9" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="V9" t="s"/>
       <c r="W9" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="X9" t="s"/>
       <c r="Y9" t="s"/>
@@ -3523,7 +3802,7 @@
     </row>
     <row r="10" spans="1:28">
       <c r="A10" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B10" t="s">
         <v>55</v>
@@ -3532,7 +3811,7 @@
         <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>130</v>
       </c>
       <c r="E10" t="s">
         <v>58</v>
@@ -3550,25 +3829,25 @@
         <v>62</v>
       </c>
       <c r="J10" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="K10" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="L10" t="s">
         <v>65</v>
       </c>
       <c r="M10" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="N10" t="s">
         <v>67</v>
       </c>
       <c r="O10" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="P10" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="Q10" t="s">
         <v>70</v>
@@ -3581,11 +3860,11 @@
         <v>72</v>
       </c>
       <c r="U10" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="V10" t="s"/>
       <c r="W10" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="X10" t="s"/>
       <c r="Y10" t="s"/>
@@ -3597,7 +3876,7 @@
     </row>
     <row r="11" spans="1:28">
       <c r="A11" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B11" t="s">
         <v>55</v>
@@ -3606,7 +3885,7 @@
         <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="E11" t="s">
         <v>58</v>
@@ -3624,25 +3903,25 @@
         <v>62</v>
       </c>
       <c r="J11" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="K11" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="L11" t="s">
         <v>65</v>
       </c>
       <c r="M11" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="N11" t="s">
         <v>67</v>
       </c>
       <c r="O11" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="P11" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="Q11" t="s">
         <v>70</v>
@@ -3655,11 +3934,11 @@
         <v>72</v>
       </c>
       <c r="U11" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="V11" t="s"/>
       <c r="W11" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="X11" t="s"/>
       <c r="Y11" t="s"/>
@@ -3671,7 +3950,7 @@
     </row>
     <row r="12" spans="1:28">
       <c r="A12" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s">
         <v>55</v>
@@ -3680,7 +3959,7 @@
         <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>148</v>
       </c>
       <c r="E12" t="s">
         <v>58</v>
@@ -3698,25 +3977,25 @@
         <v>62</v>
       </c>
       <c r="J12" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="K12" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="L12" t="s">
         <v>65</v>
       </c>
       <c r="M12" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="N12" t="s">
         <v>67</v>
       </c>
       <c r="O12" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="P12" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="Q12" t="s">
         <v>70</v>
@@ -3729,11 +4008,11 @@
         <v>72</v>
       </c>
       <c r="U12" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="V12" t="s"/>
       <c r="W12" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="X12" t="s"/>
       <c r="Y12" t="s"/>
@@ -3745,7 +4024,7 @@
     </row>
     <row r="13" spans="1:28">
       <c r="A13" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s">
         <v>55</v>
@@ -3754,7 +4033,7 @@
         <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>157</v>
       </c>
       <c r="E13" t="s">
         <v>58</v>
@@ -3772,25 +4051,25 @@
         <v>62</v>
       </c>
       <c r="J13" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="K13" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="L13" t="s">
         <v>65</v>
       </c>
       <c r="M13" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="N13" t="s">
         <v>67</v>
       </c>
       <c r="O13" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="P13" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="Q13" t="s">
         <v>70</v>
@@ -3803,11 +4082,11 @@
         <v>72</v>
       </c>
       <c r="U13" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="V13" t="s"/>
       <c r="W13" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="X13" t="s"/>
       <c r="Y13" t="s"/>
@@ -3819,7 +4098,7 @@
     </row>
     <row r="14" spans="1:28">
       <c r="A14" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s">
         <v>55</v>
@@ -3828,7 +4107,7 @@
         <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>166</v>
       </c>
       <c r="E14" t="s">
         <v>58</v>
@@ -3846,25 +4125,25 @@
         <v>62</v>
       </c>
       <c r="J14" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="K14" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s">
         <v>65</v>
       </c>
       <c r="M14" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s">
         <v>67</v>
       </c>
       <c r="O14" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="P14" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="Q14" t="s">
         <v>70</v>
@@ -3877,11 +4156,11 @@
         <v>72</v>
       </c>
       <c r="U14" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="V14" t="s"/>
       <c r="W14" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="X14" t="s"/>
       <c r="Y14" t="s"/>
@@ -3893,7 +4172,7 @@
     </row>
     <row r="15" spans="1:28">
       <c r="A15" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s">
         <v>55</v>
@@ -3902,7 +4181,7 @@
         <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>175</v>
       </c>
       <c r="E15" t="s">
         <v>58</v>
@@ -3920,25 +4199,25 @@
         <v>62</v>
       </c>
       <c r="J15" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="K15" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="L15" t="s">
         <v>65</v>
       </c>
       <c r="M15" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s">
         <v>67</v>
       </c>
       <c r="O15" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="P15" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="Q15" t="s">
         <v>70</v>
@@ -3951,11 +4230,11 @@
         <v>72</v>
       </c>
       <c r="U15" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="V15" t="s"/>
       <c r="W15" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="X15" t="s"/>
       <c r="Y15" t="s"/>
@@ -3967,7 +4246,7 @@
     </row>
     <row r="16" spans="1:28">
       <c r="A16" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s">
         <v>55</v>
@@ -3976,7 +4255,7 @@
         <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>184</v>
       </c>
       <c r="E16" t="s">
         <v>58</v>
@@ -3994,25 +4273,25 @@
         <v>62</v>
       </c>
       <c r="J16" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="K16" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="L16" t="s">
         <v>65</v>
       </c>
       <c r="M16" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s">
         <v>67</v>
       </c>
       <c r="O16" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="P16" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="Q16" t="s">
         <v>70</v>
@@ -4025,11 +4304,11 @@
         <v>72</v>
       </c>
       <c r="U16" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="V16" t="s"/>
       <c r="W16" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="X16" t="s"/>
       <c r="Y16" t="s"/>
@@ -4041,7 +4320,7 @@
     </row>
     <row r="17" spans="1:28">
       <c r="A17" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="B17" t="s">
         <v>55</v>
@@ -4050,7 +4329,7 @@
         <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>57</v>
+        <v>193</v>
       </c>
       <c r="E17" t="s">
         <v>58</v>
@@ -4068,25 +4347,25 @@
         <v>62</v>
       </c>
       <c r="J17" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="K17" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="L17" t="s">
         <v>65</v>
       </c>
       <c r="M17" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="N17" t="s">
         <v>67</v>
       </c>
       <c r="O17" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="P17" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="Q17" t="s">
         <v>70</v>
@@ -4099,11 +4378,11 @@
         <v>72</v>
       </c>
       <c r="U17" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="V17" t="s"/>
       <c r="W17" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="X17" t="s"/>
       <c r="Y17" t="s"/>
@@ -4115,7 +4394,7 @@
     </row>
     <row r="18" spans="1:28">
       <c r="A18" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s">
         <v>55</v>
@@ -4124,7 +4403,7 @@
         <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>202</v>
       </c>
       <c r="E18" t="s">
         <v>58</v>
@@ -4142,25 +4421,25 @@
         <v>62</v>
       </c>
       <c r="J18" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="K18" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="L18" t="s">
         <v>65</v>
       </c>
       <c r="M18" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="N18" t="s">
         <v>67</v>
       </c>
       <c r="O18" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="P18" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="Q18" t="s">
         <v>70</v>
@@ -4173,11 +4452,11 @@
         <v>72</v>
       </c>
       <c r="U18" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="V18" t="s"/>
       <c r="W18" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="X18" t="s"/>
       <c r="Y18" t="s"/>
@@ -4189,7 +4468,7 @@
     </row>
     <row r="19" spans="1:28">
       <c r="A19" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="B19" t="s">
         <v>55</v>
@@ -4198,7 +4477,7 @@
         <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>211</v>
       </c>
       <c r="E19" t="s">
         <v>58</v>
@@ -4216,25 +4495,25 @@
         <v>62</v>
       </c>
       <c r="J19" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="K19" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="L19" t="s">
         <v>65</v>
       </c>
       <c r="M19" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="N19" t="s">
         <v>67</v>
       </c>
       <c r="O19" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="P19" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="Q19" t="s">
         <v>70</v>
@@ -4247,11 +4526,11 @@
         <v>72</v>
       </c>
       <c r="U19" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="V19" t="s"/>
       <c r="W19" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="X19" t="s"/>
       <c r="Y19" t="s"/>
@@ -4263,7 +4542,7 @@
     </row>
     <row r="20" spans="1:28">
       <c r="A20" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="B20" t="s">
         <v>55</v>
@@ -4272,7 +4551,7 @@
         <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>220</v>
       </c>
       <c r="E20" t="s">
         <v>58</v>
@@ -4290,25 +4569,25 @@
         <v>62</v>
       </c>
       <c r="J20" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="K20" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="L20" t="s">
         <v>65</v>
       </c>
       <c r="M20" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="N20" t="s">
         <v>67</v>
       </c>
       <c r="O20" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="P20" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="Q20" t="s">
         <v>70</v>
@@ -4321,11 +4600,11 @@
         <v>72</v>
       </c>
       <c r="U20" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="V20" t="s"/>
       <c r="W20" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="X20" t="s"/>
       <c r="Y20" t="s"/>
@@ -4337,7 +4616,7 @@
     </row>
     <row r="21" spans="1:28">
       <c r="A21" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="B21" t="s">
         <v>55</v>
@@ -4346,7 +4625,7 @@
         <v>56</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>229</v>
       </c>
       <c r="E21" t="s">
         <v>58</v>
@@ -4364,25 +4643,25 @@
         <v>62</v>
       </c>
       <c r="J21" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="K21" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="L21" t="s">
         <v>65</v>
       </c>
       <c r="M21" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="N21" t="s">
         <v>67</v>
       </c>
       <c r="O21" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="P21" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="Q21" t="s">
         <v>70</v>
@@ -4395,11 +4674,11 @@
         <v>72</v>
       </c>
       <c r="U21" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="V21" t="s"/>
       <c r="W21" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="X21" t="s"/>
       <c r="Y21" t="s"/>
@@ -4411,7 +4690,7 @@
     </row>
     <row r="22" spans="1:28">
       <c r="A22" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="B22" t="s">
         <v>55</v>
@@ -4420,7 +4699,7 @@
         <v>56</v>
       </c>
       <c r="D22" t="s">
-        <v>57</v>
+        <v>238</v>
       </c>
       <c r="E22" t="s">
         <v>58</v>
@@ -4438,25 +4717,25 @@
         <v>62</v>
       </c>
       <c r="J22" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="K22" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="L22" t="s">
         <v>65</v>
       </c>
       <c r="M22" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="N22" t="s">
         <v>67</v>
       </c>
       <c r="O22" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="P22" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="Q22" t="s">
         <v>70</v>
@@ -4469,11 +4748,11 @@
         <v>72</v>
       </c>
       <c r="U22" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="V22" t="s"/>
       <c r="W22" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="X22" t="s"/>
       <c r="Y22" t="s"/>
@@ -4485,7 +4764,7 @@
     </row>
     <row r="23" spans="1:28">
       <c r="A23" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="B23" t="s">
         <v>55</v>
@@ -4494,7 +4773,7 @@
         <v>56</v>
       </c>
       <c r="D23" t="s">
-        <v>57</v>
+        <v>247</v>
       </c>
       <c r="E23" t="s">
         <v>58</v>
@@ -4512,25 +4791,25 @@
         <v>62</v>
       </c>
       <c r="J23" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="K23" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="L23" t="s">
         <v>65</v>
       </c>
       <c r="M23" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="N23" t="s">
         <v>67</v>
       </c>
       <c r="O23" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="P23" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="Q23" t="s">
         <v>70</v>
@@ -4543,11 +4822,11 @@
         <v>72</v>
       </c>
       <c r="U23" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="V23" t="s"/>
       <c r="W23" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="X23" t="s"/>
       <c r="Y23" t="s"/>
@@ -4559,7 +4838,7 @@
     </row>
     <row r="24" spans="1:28">
       <c r="A24" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="B24" t="s">
         <v>55</v>
@@ -4568,7 +4847,7 @@
         <v>56</v>
       </c>
       <c r="D24" t="s">
-        <v>57</v>
+        <v>256</v>
       </c>
       <c r="E24" t="s">
         <v>58</v>
@@ -4586,25 +4865,25 @@
         <v>62</v>
       </c>
       <c r="J24" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="K24" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="L24" t="s">
         <v>65</v>
       </c>
       <c r="M24" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="N24" t="s">
         <v>67</v>
       </c>
       <c r="O24" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="P24" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="Q24" t="s">
         <v>70</v>
@@ -4617,11 +4896,11 @@
         <v>72</v>
       </c>
       <c r="U24" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="V24" t="s"/>
       <c r="W24" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="X24" t="s"/>
       <c r="Y24" t="s"/>
@@ -4633,7 +4912,7 @@
     </row>
     <row r="25" spans="1:28">
       <c r="A25" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="B25" t="s">
         <v>55</v>
@@ -4642,7 +4921,7 @@
         <v>56</v>
       </c>
       <c r="D25" t="s">
-        <v>57</v>
+        <v>265</v>
       </c>
       <c r="E25" t="s">
         <v>58</v>
@@ -4660,25 +4939,25 @@
         <v>62</v>
       </c>
       <c r="J25" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="K25" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="L25" t="s">
         <v>65</v>
       </c>
       <c r="M25" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="N25" t="s">
         <v>67</v>
       </c>
       <c r="O25" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="P25" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="Q25" t="s">
         <v>70</v>
@@ -4691,11 +4970,11 @@
         <v>72</v>
       </c>
       <c r="U25" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="V25" t="s"/>
       <c r="W25" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="X25" t="s"/>
       <c r="Y25" t="s"/>
@@ -4707,7 +4986,7 @@
     </row>
     <row r="26" spans="1:28">
       <c r="A26" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="B26" t="s">
         <v>55</v>
@@ -4716,7 +4995,7 @@
         <v>56</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>274</v>
       </c>
       <c r="E26" t="s">
         <v>58</v>
@@ -4734,25 +5013,25 @@
         <v>62</v>
       </c>
       <c r="J26" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="K26" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="L26" t="s">
         <v>65</v>
       </c>
       <c r="M26" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="N26" t="s">
         <v>67</v>
       </c>
       <c r="O26" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="P26" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="Q26" t="s">
         <v>70</v>
@@ -4765,11 +5044,11 @@
         <v>72</v>
       </c>
       <c r="U26" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="V26" t="s"/>
       <c r="W26" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="X26" t="s"/>
       <c r="Y26" t="s"/>
@@ -4781,7 +5060,7 @@
     </row>
     <row r="27" spans="1:28">
       <c r="A27" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="B27" t="s">
         <v>55</v>
@@ -4790,7 +5069,7 @@
         <v>56</v>
       </c>
       <c r="D27" t="s">
-        <v>57</v>
+        <v>283</v>
       </c>
       <c r="E27" t="s">
         <v>58</v>
@@ -4808,25 +5087,25 @@
         <v>62</v>
       </c>
       <c r="J27" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="K27" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="L27" t="s">
         <v>65</v>
       </c>
       <c r="M27" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="N27" t="s">
         <v>67</v>
       </c>
       <c r="O27" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="P27" t="s">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="Q27" t="s">
         <v>70</v>
@@ -4839,11 +5118,11 @@
         <v>72</v>
       </c>
       <c r="U27" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="V27" t="s"/>
       <c r="W27" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="X27" t="s"/>
       <c r="Y27" t="s"/>
@@ -4855,7 +5134,7 @@
     </row>
     <row r="28" spans="1:28">
       <c r="A28" t="s">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="B28" t="s">
         <v>55</v>
@@ -4864,7 +5143,7 @@
         <v>56</v>
       </c>
       <c r="D28" t="s">
-        <v>57</v>
+        <v>292</v>
       </c>
       <c r="E28" t="s">
         <v>58</v>
@@ -4882,25 +5161,25 @@
         <v>62</v>
       </c>
       <c r="J28" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="K28" t="s">
-        <v>269</v>
+        <v>294</v>
       </c>
       <c r="L28" t="s">
         <v>65</v>
       </c>
       <c r="M28" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="N28" t="s">
         <v>67</v>
       </c>
       <c r="O28" t="s">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="P28" t="s">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="Q28" t="s">
         <v>70</v>
@@ -4913,11 +5192,11 @@
         <v>72</v>
       </c>
       <c r="U28" t="s">
-        <v>273</v>
+        <v>298</v>
       </c>
       <c r="V28" t="s"/>
       <c r="W28" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="X28" t="s"/>
       <c r="Y28" t="s"/>
@@ -4929,7 +5208,7 @@
     </row>
     <row r="29" spans="1:28">
       <c r="A29" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="B29" t="s">
         <v>55</v>
@@ -4938,7 +5217,7 @@
         <v>56</v>
       </c>
       <c r="D29" t="s">
-        <v>57</v>
+        <v>301</v>
       </c>
       <c r="E29" t="s">
         <v>58</v>
@@ -4956,25 +5235,25 @@
         <v>62</v>
       </c>
       <c r="J29" t="s">
-        <v>276</v>
+        <v>302</v>
       </c>
       <c r="K29" t="s">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="L29" t="s">
         <v>65</v>
       </c>
       <c r="M29" t="s">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="N29" t="s">
         <v>67</v>
       </c>
       <c r="O29" t="s">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="P29" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="Q29" t="s">
         <v>70</v>
@@ -4987,11 +5266,11 @@
         <v>72</v>
       </c>
       <c r="U29" t="s">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="V29" t="s"/>
       <c r="W29" t="s">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="X29" t="s"/>
       <c r="Y29" t="s"/>
@@ -5003,7 +5282,7 @@
     </row>
     <row r="30" spans="1:28">
       <c r="A30" t="s">
-        <v>283</v>
+        <v>309</v>
       </c>
       <c r="B30" t="s">
         <v>55</v>
@@ -5012,7 +5291,7 @@
         <v>56</v>
       </c>
       <c r="D30" t="s">
-        <v>57</v>
+        <v>310</v>
       </c>
       <c r="E30" t="s">
         <v>58</v>
@@ -5030,25 +5309,25 @@
         <v>62</v>
       </c>
       <c r="J30" t="s">
-        <v>284</v>
+        <v>311</v>
       </c>
       <c r="K30" t="s">
-        <v>285</v>
+        <v>312</v>
       </c>
       <c r="L30" t="s">
         <v>65</v>
       </c>
       <c r="M30" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="N30" t="s">
         <v>67</v>
       </c>
       <c r="O30" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="P30" t="s">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="Q30" t="s">
         <v>70</v>
@@ -5061,11 +5340,11 @@
         <v>72</v>
       </c>
       <c r="U30" t="s">
-        <v>289</v>
+        <v>316</v>
       </c>
       <c r="V30" t="s"/>
       <c r="W30" t="s">
-        <v>290</v>
+        <v>317</v>
       </c>
       <c r="X30" t="s"/>
       <c r="Y30" t="s"/>
@@ -5077,7 +5356,7 @@
     </row>
     <row r="31" spans="1:28">
       <c r="A31" t="s">
-        <v>291</v>
+        <v>318</v>
       </c>
       <c r="B31" t="s">
         <v>55</v>
@@ -5086,7 +5365,7 @@
         <v>56</v>
       </c>
       <c r="D31" t="s">
-        <v>57</v>
+        <v>319</v>
       </c>
       <c r="E31" t="s">
         <v>58</v>
@@ -5104,25 +5383,25 @@
         <v>62</v>
       </c>
       <c r="J31" t="s">
-        <v>292</v>
+        <v>320</v>
       </c>
       <c r="K31" t="s">
-        <v>293</v>
+        <v>321</v>
       </c>
       <c r="L31" t="s">
         <v>65</v>
       </c>
       <c r="M31" t="s">
-        <v>294</v>
+        <v>322</v>
       </c>
       <c r="N31" t="s">
         <v>67</v>
       </c>
       <c r="O31" t="s">
-        <v>295</v>
+        <v>323</v>
       </c>
       <c r="P31" t="s">
-        <v>296</v>
+        <v>324</v>
       </c>
       <c r="Q31" t="s">
         <v>70</v>
@@ -5135,11 +5414,11 @@
         <v>72</v>
       </c>
       <c r="U31" t="s">
-        <v>297</v>
+        <v>325</v>
       </c>
       <c r="V31" t="s"/>
       <c r="W31" t="s">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="X31" t="s"/>
       <c r="Y31" t="s"/>
@@ -5151,7 +5430,7 @@
     </row>
     <row r="32" spans="1:28">
       <c r="A32" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="B32" t="s">
         <v>55</v>
@@ -5160,7 +5439,7 @@
         <v>56</v>
       </c>
       <c r="D32" t="s">
-        <v>57</v>
+        <v>328</v>
       </c>
       <c r="E32" t="s">
         <v>58</v>
@@ -5178,25 +5457,25 @@
         <v>62</v>
       </c>
       <c r="J32" t="s">
-        <v>300</v>
+        <v>329</v>
       </c>
       <c r="K32" t="s">
-        <v>301</v>
+        <v>330</v>
       </c>
       <c r="L32" t="s">
         <v>65</v>
       </c>
       <c r="M32" t="s">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="N32" t="s">
         <v>67</v>
       </c>
       <c r="O32" t="s">
-        <v>303</v>
+        <v>332</v>
       </c>
       <c r="P32" t="s">
-        <v>304</v>
+        <v>333</v>
       </c>
       <c r="Q32" t="s">
         <v>70</v>
@@ -5209,11 +5488,11 @@
         <v>72</v>
       </c>
       <c r="U32" t="s">
-        <v>305</v>
+        <v>334</v>
       </c>
       <c r="V32" t="s"/>
       <c r="W32" t="s">
-        <v>306</v>
+        <v>335</v>
       </c>
       <c r="X32" t="s"/>
       <c r="Y32" t="s"/>
@@ -5225,7 +5504,7 @@
     </row>
     <row r="33" spans="1:28">
       <c r="A33" t="s">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="B33" t="s">
         <v>55</v>
@@ -5234,7 +5513,7 @@
         <v>56</v>
       </c>
       <c r="D33" t="s">
-        <v>57</v>
+        <v>337</v>
       </c>
       <c r="E33" t="s">
         <v>58</v>
@@ -5252,25 +5531,25 @@
         <v>62</v>
       </c>
       <c r="J33" t="s">
-        <v>308</v>
+        <v>338</v>
       </c>
       <c r="K33" t="s">
-        <v>309</v>
+        <v>339</v>
       </c>
       <c r="L33" t="s">
         <v>65</v>
       </c>
       <c r="M33" t="s">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="N33" t="s">
         <v>67</v>
       </c>
       <c r="O33" t="s">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="P33" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="Q33" t="s">
         <v>70</v>
@@ -5283,11 +5562,11 @@
         <v>72</v>
       </c>
       <c r="U33" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="V33" t="s"/>
       <c r="W33" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
       <c r="X33" t="s"/>
       <c r="Y33" t="s"/>
@@ -5299,7 +5578,7 @@
     </row>
     <row r="34" spans="1:28">
       <c r="A34" t="s">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="B34" t="s">
         <v>55</v>
@@ -5308,7 +5587,7 @@
         <v>56</v>
       </c>
       <c r="D34" t="s">
-        <v>57</v>
+        <v>346</v>
       </c>
       <c r="E34" t="s">
         <v>58</v>
@@ -5326,25 +5605,25 @@
         <v>62</v>
       </c>
       <c r="J34" t="s">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="K34" t="s">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="L34" t="s">
         <v>65</v>
       </c>
       <c r="M34" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="N34" t="s">
         <v>67</v>
       </c>
       <c r="O34" t="s">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="P34" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="Q34" t="s">
         <v>70</v>
@@ -5357,11 +5636,11 @@
         <v>72</v>
       </c>
       <c r="U34" t="s">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="V34" t="s"/>
       <c r="W34" t="s">
-        <v>322</v>
+        <v>353</v>
       </c>
       <c r="X34" t="s"/>
       <c r="Y34" t="s"/>
@@ -5373,7 +5652,7 @@
     </row>
     <row r="35" spans="1:28">
       <c r="A35" t="s">
-        <v>323</v>
+        <v>354</v>
       </c>
       <c r="B35" t="s">
         <v>55</v>
@@ -5382,7 +5661,7 @@
         <v>56</v>
       </c>
       <c r="D35" t="s">
-        <v>57</v>
+        <v>355</v>
       </c>
       <c r="E35" t="s">
         <v>58</v>
@@ -5400,25 +5679,25 @@
         <v>62</v>
       </c>
       <c r="J35" t="s">
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="K35" t="s">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="L35" t="s">
         <v>65</v>
       </c>
       <c r="M35" t="s">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="N35" t="s">
         <v>67</v>
       </c>
       <c r="O35" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="P35" t="s">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="Q35" t="s">
         <v>70</v>
@@ -5431,11 +5710,11 @@
         <v>72</v>
       </c>
       <c r="U35" t="s">
-        <v>329</v>
+        <v>361</v>
       </c>
       <c r="V35" t="s"/>
       <c r="W35" t="s">
-        <v>330</v>
+        <v>362</v>
       </c>
       <c r="X35" t="s"/>
       <c r="Y35" t="s"/>
@@ -5447,7 +5726,7 @@
     </row>
     <row r="36" spans="1:28">
       <c r="A36" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="B36" t="s">
         <v>55</v>
@@ -5456,7 +5735,7 @@
         <v>56</v>
       </c>
       <c r="D36" t="s">
-        <v>57</v>
+        <v>364</v>
       </c>
       <c r="E36" t="s">
         <v>58</v>
@@ -5474,25 +5753,25 @@
         <v>62</v>
       </c>
       <c r="J36" t="s">
-        <v>332</v>
+        <v>365</v>
       </c>
       <c r="K36" t="s">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="L36" t="s">
         <v>65</v>
       </c>
       <c r="M36" t="s">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="N36" t="s">
         <v>67</v>
       </c>
       <c r="O36" t="s">
-        <v>335</v>
+        <v>368</v>
       </c>
       <c r="P36" t="s">
-        <v>336</v>
+        <v>369</v>
       </c>
       <c r="Q36" t="s">
         <v>70</v>
@@ -5505,11 +5784,11 @@
         <v>72</v>
       </c>
       <c r="U36" t="s">
-        <v>337</v>
+        <v>370</v>
       </c>
       <c r="V36" t="s"/>
       <c r="W36" t="s">
-        <v>338</v>
+        <v>371</v>
       </c>
       <c r="X36" t="s"/>
       <c r="Y36" t="s"/>
@@ -5521,7 +5800,7 @@
     </row>
     <row r="37" spans="1:28">
       <c r="A37" t="s">
-        <v>339</v>
+        <v>372</v>
       </c>
       <c r="B37" t="s">
         <v>55</v>
@@ -5530,7 +5809,7 @@
         <v>56</v>
       </c>
       <c r="D37" t="s">
-        <v>57</v>
+        <v>373</v>
       </c>
       <c r="E37" t="s">
         <v>58</v>
@@ -5548,25 +5827,25 @@
         <v>62</v>
       </c>
       <c r="J37" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="K37" t="s">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="L37" t="s">
         <v>65</v>
       </c>
       <c r="M37" t="s">
-        <v>342</v>
+        <v>376</v>
       </c>
       <c r="N37" t="s">
         <v>67</v>
       </c>
       <c r="O37" t="s">
-        <v>343</v>
+        <v>377</v>
       </c>
       <c r="P37" t="s">
-        <v>344</v>
+        <v>378</v>
       </c>
       <c r="Q37" t="s">
         <v>70</v>
@@ -5579,11 +5858,11 @@
         <v>72</v>
       </c>
       <c r="U37" t="s">
-        <v>345</v>
+        <v>379</v>
       </c>
       <c r="V37" t="s"/>
       <c r="W37" t="s">
-        <v>346</v>
+        <v>380</v>
       </c>
       <c r="X37" t="s"/>
       <c r="Y37" t="s"/>
@@ -5595,7 +5874,7 @@
     </row>
     <row r="38" spans="1:28">
       <c r="A38" t="s">
-        <v>347</v>
+        <v>381</v>
       </c>
       <c r="B38" t="s">
         <v>55</v>
@@ -5604,7 +5883,7 @@
         <v>56</v>
       </c>
       <c r="D38" t="s">
-        <v>57</v>
+        <v>382</v>
       </c>
       <c r="E38" t="s">
         <v>58</v>
@@ -5622,25 +5901,25 @@
         <v>62</v>
       </c>
       <c r="J38" t="s">
-        <v>348</v>
+        <v>383</v>
       </c>
       <c r="K38" t="s">
-        <v>349</v>
+        <v>384</v>
       </c>
       <c r="L38" t="s">
         <v>65</v>
       </c>
       <c r="M38" t="s">
-        <v>350</v>
+        <v>385</v>
       </c>
       <c r="N38" t="s">
         <v>67</v>
       </c>
       <c r="O38" t="s">
-        <v>351</v>
+        <v>386</v>
       </c>
       <c r="P38" t="s">
-        <v>352</v>
+        <v>387</v>
       </c>
       <c r="Q38" t="s">
         <v>70</v>
@@ -5653,11 +5932,11 @@
         <v>72</v>
       </c>
       <c r="U38" t="s">
-        <v>353</v>
+        <v>388</v>
       </c>
       <c r="V38" t="s"/>
       <c r="W38" t="s">
-        <v>354</v>
+        <v>389</v>
       </c>
       <c r="X38" t="s"/>
       <c r="Y38" t="s"/>
@@ -5669,7 +5948,7 @@
     </row>
     <row r="39" spans="1:28">
       <c r="A39" t="s">
-        <v>355</v>
+        <v>390</v>
       </c>
       <c r="B39" t="s">
         <v>55</v>
@@ -5678,7 +5957,7 @@
         <v>56</v>
       </c>
       <c r="D39" t="s">
-        <v>57</v>
+        <v>391</v>
       </c>
       <c r="E39" t="s">
         <v>58</v>
@@ -5696,25 +5975,25 @@
         <v>62</v>
       </c>
       <c r="J39" t="s">
-        <v>356</v>
+        <v>392</v>
       </c>
       <c r="K39" t="s">
-        <v>357</v>
+        <v>393</v>
       </c>
       <c r="L39" t="s">
         <v>65</v>
       </c>
       <c r="M39" t="s">
-        <v>358</v>
+        <v>394</v>
       </c>
       <c r="N39" t="s">
         <v>67</v>
       </c>
       <c r="O39" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
       <c r="P39" t="s">
-        <v>360</v>
+        <v>396</v>
       </c>
       <c r="Q39" t="s">
         <v>70</v>
@@ -5727,11 +6006,11 @@
         <v>72</v>
       </c>
       <c r="U39" t="s">
-        <v>361</v>
+        <v>397</v>
       </c>
       <c r="V39" t="s"/>
       <c r="W39" t="s">
-        <v>362</v>
+        <v>398</v>
       </c>
       <c r="X39" t="s"/>
       <c r="Y39" t="s"/>
@@ -5743,7 +6022,7 @@
     </row>
     <row r="40" spans="1:28">
       <c r="A40" t="s">
-        <v>363</v>
+        <v>399</v>
       </c>
       <c r="B40" t="s">
         <v>55</v>
@@ -5752,7 +6031,7 @@
         <v>56</v>
       </c>
       <c r="D40" t="s">
-        <v>57</v>
+        <v>400</v>
       </c>
       <c r="E40" t="s">
         <v>58</v>
@@ -5770,25 +6049,25 @@
         <v>62</v>
       </c>
       <c r="J40" t="s">
-        <v>364</v>
+        <v>401</v>
       </c>
       <c r="K40" t="s">
-        <v>365</v>
+        <v>402</v>
       </c>
       <c r="L40" t="s">
         <v>65</v>
       </c>
       <c r="M40" t="s">
-        <v>366</v>
+        <v>403</v>
       </c>
       <c r="N40" t="s">
         <v>67</v>
       </c>
       <c r="O40" t="s">
-        <v>367</v>
+        <v>404</v>
       </c>
       <c r="P40" t="s">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="Q40" t="s">
         <v>70</v>
@@ -5801,11 +6080,11 @@
         <v>72</v>
       </c>
       <c r="U40" t="s">
-        <v>369</v>
+        <v>406</v>
       </c>
       <c r="V40" t="s"/>
       <c r="W40" t="s">
-        <v>370</v>
+        <v>407</v>
       </c>
       <c r="X40" t="s"/>
       <c r="Y40" t="s"/>
@@ -5817,7 +6096,7 @@
     </row>
     <row r="41" spans="1:28">
       <c r="A41" t="s">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="B41" t="s">
         <v>55</v>
@@ -5826,7 +6105,7 @@
         <v>56</v>
       </c>
       <c r="D41" t="s">
-        <v>57</v>
+        <v>409</v>
       </c>
       <c r="E41" t="s">
         <v>58</v>
@@ -5844,25 +6123,25 @@
         <v>62</v>
       </c>
       <c r="J41" t="s">
-        <v>372</v>
+        <v>410</v>
       </c>
       <c r="K41" t="s">
-        <v>373</v>
+        <v>411</v>
       </c>
       <c r="L41" t="s">
         <v>65</v>
       </c>
       <c r="M41" t="s">
-        <v>374</v>
+        <v>412</v>
       </c>
       <c r="N41" t="s">
         <v>67</v>
       </c>
       <c r="O41" t="s">
-        <v>375</v>
+        <v>413</v>
       </c>
       <c r="P41" t="s">
-        <v>376</v>
+        <v>414</v>
       </c>
       <c r="Q41" t="s">
         <v>70</v>
@@ -5875,11 +6154,11 @@
         <v>72</v>
       </c>
       <c r="U41" t="s">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="V41" t="s"/>
       <c r="W41" t="s">
-        <v>378</v>
+        <v>416</v>
       </c>
       <c r="X41" t="s"/>
       <c r="Y41" t="s"/>
@@ -5891,7 +6170,7 @@
     </row>
     <row r="42" spans="1:28">
       <c r="A42" t="s">
-        <v>379</v>
+        <v>417</v>
       </c>
       <c r="B42" t="s">
         <v>55</v>
@@ -5900,7 +6179,7 @@
         <v>56</v>
       </c>
       <c r="D42" t="s">
-        <v>57</v>
+        <v>418</v>
       </c>
       <c r="E42" t="s">
         <v>58</v>
@@ -5918,25 +6197,25 @@
         <v>62</v>
       </c>
       <c r="J42" t="s">
-        <v>380</v>
+        <v>419</v>
       </c>
       <c r="K42" t="s">
-        <v>381</v>
+        <v>420</v>
       </c>
       <c r="L42" t="s">
         <v>65</v>
       </c>
       <c r="M42" t="s">
-        <v>382</v>
+        <v>421</v>
       </c>
       <c r="N42" t="s">
         <v>67</v>
       </c>
       <c r="O42" t="s">
-        <v>383</v>
+        <v>422</v>
       </c>
       <c r="P42" t="s">
-        <v>384</v>
+        <v>423</v>
       </c>
       <c r="Q42" t="s">
         <v>70</v>
@@ -5949,11 +6228,11 @@
         <v>72</v>
       </c>
       <c r="U42" t="s">
-        <v>385</v>
+        <v>424</v>
       </c>
       <c r="V42" t="s"/>
       <c r="W42" t="s">
-        <v>386</v>
+        <v>425</v>
       </c>
       <c r="X42" t="s"/>
       <c r="Y42" t="s"/>
@@ -5965,7 +6244,7 @@
     </row>
     <row r="43" spans="1:28">
       <c r="A43" t="s">
-        <v>387</v>
+        <v>426</v>
       </c>
       <c r="B43" t="s">
         <v>55</v>
@@ -5974,7 +6253,7 @@
         <v>56</v>
       </c>
       <c r="D43" t="s">
-        <v>57</v>
+        <v>427</v>
       </c>
       <c r="E43" t="s">
         <v>58</v>
@@ -5992,25 +6271,25 @@
         <v>62</v>
       </c>
       <c r="J43" t="s">
-        <v>388</v>
+        <v>428</v>
       </c>
       <c r="K43" t="s">
-        <v>389</v>
+        <v>429</v>
       </c>
       <c r="L43" t="s">
         <v>65</v>
       </c>
       <c r="M43" t="s">
-        <v>390</v>
+        <v>430</v>
       </c>
       <c r="N43" t="s">
         <v>67</v>
       </c>
       <c r="O43" t="s">
-        <v>391</v>
+        <v>431</v>
       </c>
       <c r="P43" t="s">
-        <v>392</v>
+        <v>432</v>
       </c>
       <c r="Q43" t="s">
         <v>70</v>
@@ -6023,11 +6302,11 @@
         <v>72</v>
       </c>
       <c r="U43" t="s">
-        <v>393</v>
+        <v>433</v>
       </c>
       <c r="V43" t="s"/>
       <c r="W43" t="s">
-        <v>394</v>
+        <v>434</v>
       </c>
       <c r="X43" t="s"/>
       <c r="Y43" t="s"/>
@@ -6039,7 +6318,7 @@
     </row>
     <row r="44" spans="1:28">
       <c r="A44" t="s">
-        <v>395</v>
+        <v>435</v>
       </c>
       <c r="B44" t="s">
         <v>55</v>
@@ -6048,7 +6327,7 @@
         <v>56</v>
       </c>
       <c r="D44" t="s">
-        <v>57</v>
+        <v>436</v>
       </c>
       <c r="E44" t="s">
         <v>58</v>
@@ -6066,25 +6345,25 @@
         <v>62</v>
       </c>
       <c r="J44" t="s">
-        <v>396</v>
+        <v>437</v>
       </c>
       <c r="K44" t="s">
-        <v>397</v>
+        <v>438</v>
       </c>
       <c r="L44" t="s">
         <v>65</v>
       </c>
       <c r="M44" t="s">
-        <v>398</v>
+        <v>439</v>
       </c>
       <c r="N44" t="s">
         <v>67</v>
       </c>
       <c r="O44" t="s">
-        <v>399</v>
+        <v>440</v>
       </c>
       <c r="P44" t="s">
-        <v>400</v>
+        <v>441</v>
       </c>
       <c r="Q44" t="s">
         <v>70</v>
@@ -6097,11 +6376,11 @@
         <v>72</v>
       </c>
       <c r="U44" t="s">
-        <v>401</v>
+        <v>442</v>
       </c>
       <c r="V44" t="s"/>
       <c r="W44" t="s">
-        <v>402</v>
+        <v>443</v>
       </c>
       <c r="X44" t="s"/>
       <c r="Y44" t="s"/>
@@ -6113,7 +6392,7 @@
     </row>
     <row r="45" spans="1:28">
       <c r="A45" t="s">
-        <v>403</v>
+        <v>444</v>
       </c>
       <c r="B45" t="s">
         <v>55</v>
@@ -6122,7 +6401,7 @@
         <v>56</v>
       </c>
       <c r="D45" t="s">
-        <v>57</v>
+        <v>445</v>
       </c>
       <c r="E45" t="s">
         <v>58</v>
@@ -6140,25 +6419,25 @@
         <v>62</v>
       </c>
       <c r="J45" t="s">
-        <v>404</v>
+        <v>446</v>
       </c>
       <c r="K45" t="s">
-        <v>405</v>
+        <v>447</v>
       </c>
       <c r="L45" t="s">
         <v>65</v>
       </c>
       <c r="M45" t="s">
-        <v>406</v>
+        <v>448</v>
       </c>
       <c r="N45" t="s">
         <v>67</v>
       </c>
       <c r="O45" t="s">
-        <v>407</v>
+        <v>449</v>
       </c>
       <c r="P45" t="s">
-        <v>408</v>
+        <v>450</v>
       </c>
       <c r="Q45" t="s">
         <v>70</v>
@@ -6171,11 +6450,11 @@
         <v>72</v>
       </c>
       <c r="U45" t="s">
-        <v>409</v>
+        <v>451</v>
       </c>
       <c r="V45" t="s"/>
       <c r="W45" t="s">
-        <v>410</v>
+        <v>452</v>
       </c>
       <c r="X45" t="s"/>
       <c r="Y45" t="s"/>
@@ -6187,7 +6466,7 @@
     </row>
     <row r="46" spans="1:28">
       <c r="A46" t="s">
-        <v>411</v>
+        <v>453</v>
       </c>
       <c r="B46" t="s">
         <v>55</v>
@@ -6196,7 +6475,7 @@
         <v>56</v>
       </c>
       <c r="D46" t="s">
-        <v>57</v>
+        <v>454</v>
       </c>
       <c r="E46" t="s">
         <v>58</v>
@@ -6214,25 +6493,25 @@
         <v>62</v>
       </c>
       <c r="J46" t="s">
-        <v>412</v>
+        <v>455</v>
       </c>
       <c r="K46" t="s">
-        <v>413</v>
+        <v>456</v>
       </c>
       <c r="L46" t="s">
         <v>65</v>
       </c>
       <c r="M46" t="s">
-        <v>414</v>
+        <v>457</v>
       </c>
       <c r="N46" t="s">
         <v>67</v>
       </c>
       <c r="O46" t="s">
-        <v>415</v>
+        <v>458</v>
       </c>
       <c r="P46" t="s">
-        <v>416</v>
+        <v>459</v>
       </c>
       <c r="Q46" t="s">
         <v>70</v>
@@ -6245,11 +6524,11 @@
         <v>72</v>
       </c>
       <c r="U46" t="s">
-        <v>417</v>
+        <v>460</v>
       </c>
       <c r="V46" t="s"/>
       <c r="W46" t="s">
-        <v>418</v>
+        <v>461</v>
       </c>
       <c r="X46" t="s"/>
       <c r="Y46" t="s"/>
@@ -6261,7 +6540,7 @@
     </row>
     <row r="47" spans="1:28">
       <c r="A47" t="s">
-        <v>419</v>
+        <v>462</v>
       </c>
       <c r="B47" t="s">
         <v>55</v>
@@ -6270,7 +6549,7 @@
         <v>56</v>
       </c>
       <c r="D47" t="s">
-        <v>57</v>
+        <v>463</v>
       </c>
       <c r="E47" t="s">
         <v>58</v>
@@ -6288,25 +6567,25 @@
         <v>62</v>
       </c>
       <c r="J47" t="s">
-        <v>420</v>
+        <v>464</v>
       </c>
       <c r="K47" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="L47" t="s">
         <v>65</v>
       </c>
       <c r="M47" t="s">
-        <v>422</v>
+        <v>466</v>
       </c>
       <c r="N47" t="s">
         <v>67</v>
       </c>
       <c r="O47" t="s">
-        <v>423</v>
+        <v>467</v>
       </c>
       <c r="P47" t="s">
-        <v>424</v>
+        <v>468</v>
       </c>
       <c r="Q47" t="s">
         <v>70</v>
@@ -6319,11 +6598,11 @@
         <v>72</v>
       </c>
       <c r="U47" t="s">
-        <v>425</v>
+        <v>469</v>
       </c>
       <c r="V47" t="s"/>
       <c r="W47" t="s">
-        <v>426</v>
+        <v>470</v>
       </c>
       <c r="X47" t="s"/>
       <c r="Y47" t="s"/>
@@ -6335,7 +6614,7 @@
     </row>
     <row r="48" spans="1:28">
       <c r="A48" t="s">
-        <v>427</v>
+        <v>471</v>
       </c>
       <c r="B48" t="s">
         <v>55</v>
@@ -6344,7 +6623,7 @@
         <v>56</v>
       </c>
       <c r="D48" t="s">
-        <v>57</v>
+        <v>472</v>
       </c>
       <c r="E48" t="s">
         <v>58</v>
@@ -6362,25 +6641,25 @@
         <v>62</v>
       </c>
       <c r="J48" t="s">
-        <v>428</v>
+        <v>473</v>
       </c>
       <c r="K48" t="s">
-        <v>429</v>
+        <v>474</v>
       </c>
       <c r="L48" t="s">
         <v>65</v>
       </c>
       <c r="M48" t="s">
-        <v>430</v>
+        <v>475</v>
       </c>
       <c r="N48" t="s">
         <v>67</v>
       </c>
       <c r="O48" t="s">
-        <v>431</v>
+        <v>476</v>
       </c>
       <c r="P48" t="s">
-        <v>432</v>
+        <v>477</v>
       </c>
       <c r="Q48" t="s">
         <v>70</v>
@@ -6393,11 +6672,11 @@
         <v>72</v>
       </c>
       <c r="U48" t="s">
-        <v>433</v>
+        <v>478</v>
       </c>
       <c r="V48" t="s"/>
       <c r="W48" t="s">
-        <v>434</v>
+        <v>479</v>
       </c>
       <c r="X48" t="s"/>
       <c r="Y48" t="s"/>
@@ -6409,7 +6688,7 @@
     </row>
     <row r="49" spans="1:28">
       <c r="A49" t="s">
-        <v>435</v>
+        <v>480</v>
       </c>
       <c r="B49" t="s">
         <v>55</v>
@@ -6418,7 +6697,7 @@
         <v>56</v>
       </c>
       <c r="D49" t="s">
-        <v>57</v>
+        <v>481</v>
       </c>
       <c r="E49" t="s">
         <v>58</v>
@@ -6436,25 +6715,25 @@
         <v>62</v>
       </c>
       <c r="J49" t="s">
-        <v>436</v>
+        <v>482</v>
       </c>
       <c r="K49" t="s">
-        <v>437</v>
+        <v>483</v>
       </c>
       <c r="L49" t="s">
         <v>65</v>
       </c>
       <c r="M49" t="s">
-        <v>438</v>
+        <v>484</v>
       </c>
       <c r="N49" t="s">
         <v>67</v>
       </c>
       <c r="O49" t="s">
-        <v>439</v>
+        <v>485</v>
       </c>
       <c r="P49" t="s">
-        <v>440</v>
+        <v>486</v>
       </c>
       <c r="Q49" t="s">
         <v>70</v>
@@ -6467,11 +6746,11 @@
         <v>72</v>
       </c>
       <c r="U49" t="s">
-        <v>441</v>
+        <v>487</v>
       </c>
       <c r="V49" t="s"/>
       <c r="W49" t="s">
-        <v>442</v>
+        <v>488</v>
       </c>
       <c r="X49" t="s"/>
       <c r="Y49" t="s"/>
@@ -6483,7 +6762,7 @@
     </row>
     <row r="50" spans="1:28">
       <c r="A50" t="s">
-        <v>443</v>
+        <v>489</v>
       </c>
       <c r="B50" t="s">
         <v>55</v>
@@ -6492,7 +6771,7 @@
         <v>56</v>
       </c>
       <c r="D50" t="s">
-        <v>57</v>
+        <v>490</v>
       </c>
       <c r="E50" t="s">
         <v>58</v>
@@ -6510,25 +6789,25 @@
         <v>62</v>
       </c>
       <c r="J50" t="s">
-        <v>444</v>
+        <v>491</v>
       </c>
       <c r="K50" t="s">
-        <v>445</v>
+        <v>492</v>
       </c>
       <c r="L50" t="s">
         <v>65</v>
       </c>
       <c r="M50" t="s">
-        <v>446</v>
+        <v>493</v>
       </c>
       <c r="N50" t="s">
         <v>67</v>
       </c>
       <c r="O50" t="s">
-        <v>447</v>
+        <v>494</v>
       </c>
       <c r="P50" t="s">
-        <v>448</v>
+        <v>495</v>
       </c>
       <c r="Q50" t="s">
         <v>70</v>
@@ -6541,11 +6820,11 @@
         <v>72</v>
       </c>
       <c r="U50" t="s">
-        <v>449</v>
+        <v>496</v>
       </c>
       <c r="V50" t="s"/>
       <c r="W50" t="s">
-        <v>450</v>
+        <v>497</v>
       </c>
       <c r="X50" t="s"/>
       <c r="Y50" t="s"/>
@@ -6557,7 +6836,7 @@
     </row>
     <row r="51" spans="1:28">
       <c r="A51" t="s">
-        <v>451</v>
+        <v>498</v>
       </c>
       <c r="B51" t="s">
         <v>55</v>
@@ -6566,7 +6845,7 @@
         <v>56</v>
       </c>
       <c r="D51" t="s">
-        <v>57</v>
+        <v>499</v>
       </c>
       <c r="E51" t="s">
         <v>58</v>
@@ -6584,25 +6863,25 @@
         <v>62</v>
       </c>
       <c r="J51" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="K51" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="L51" t="s">
         <v>65</v>
       </c>
       <c r="M51" t="s">
-        <v>454</v>
+        <v>502</v>
       </c>
       <c r="N51" t="s">
         <v>67</v>
       </c>
       <c r="O51" t="s">
-        <v>455</v>
+        <v>503</v>
       </c>
       <c r="P51" t="s">
-        <v>456</v>
+        <v>504</v>
       </c>
       <c r="Q51" t="s">
         <v>70</v>
@@ -6615,11 +6894,11 @@
         <v>72</v>
       </c>
       <c r="U51" t="s">
-        <v>457</v>
+        <v>505</v>
       </c>
       <c r="V51" t="s"/>
       <c r="W51" t="s">
-        <v>458</v>
+        <v>506</v>
       </c>
       <c r="X51" t="s"/>
       <c r="Y51" t="s"/>
@@ -6631,7 +6910,7 @@
     </row>
     <row r="52" spans="1:28">
       <c r="A52" t="s">
-        <v>459</v>
+        <v>507</v>
       </c>
       <c r="B52" t="s">
         <v>55</v>
@@ -6640,7 +6919,7 @@
         <v>56</v>
       </c>
       <c r="D52" t="s">
-        <v>57</v>
+        <v>508</v>
       </c>
       <c r="E52" t="s">
         <v>58</v>
@@ -6658,25 +6937,25 @@
         <v>62</v>
       </c>
       <c r="J52" t="s">
-        <v>460</v>
+        <v>509</v>
       </c>
       <c r="K52" t="s">
-        <v>461</v>
+        <v>510</v>
       </c>
       <c r="L52" t="s">
         <v>65</v>
       </c>
       <c r="M52" t="s">
-        <v>462</v>
+        <v>511</v>
       </c>
       <c r="N52" t="s">
         <v>67</v>
       </c>
       <c r="O52" t="s">
-        <v>463</v>
+        <v>512</v>
       </c>
       <c r="P52" t="s">
-        <v>464</v>
+        <v>513</v>
       </c>
       <c r="Q52" t="s">
         <v>70</v>
@@ -6689,11 +6968,11 @@
         <v>72</v>
       </c>
       <c r="U52" t="s">
-        <v>465</v>
+        <v>514</v>
       </c>
       <c r="V52" t="s"/>
       <c r="W52" t="s">
-        <v>466</v>
+        <v>515</v>
       </c>
       <c r="X52" t="s"/>
       <c r="Y52" t="s"/>
@@ -6705,7 +6984,7 @@
     </row>
     <row r="53" spans="1:28">
       <c r="A53" t="s">
-        <v>467</v>
+        <v>516</v>
       </c>
       <c r="B53" t="s">
         <v>55</v>
@@ -6714,7 +6993,7 @@
         <v>56</v>
       </c>
       <c r="D53" t="s">
-        <v>57</v>
+        <v>517</v>
       </c>
       <c r="E53" t="s">
         <v>58</v>
@@ -6732,25 +7011,25 @@
         <v>62</v>
       </c>
       <c r="J53" t="s">
-        <v>468</v>
+        <v>518</v>
       </c>
       <c r="K53" t="s">
-        <v>469</v>
+        <v>519</v>
       </c>
       <c r="L53" t="s">
         <v>65</v>
       </c>
       <c r="M53" t="s">
-        <v>470</v>
+        <v>520</v>
       </c>
       <c r="N53" t="s">
         <v>67</v>
       </c>
       <c r="O53" t="s">
-        <v>471</v>
+        <v>521</v>
       </c>
       <c r="P53" t="s">
-        <v>472</v>
+        <v>522</v>
       </c>
       <c r="Q53" t="s">
         <v>70</v>
@@ -6763,11 +7042,11 @@
         <v>72</v>
       </c>
       <c r="U53" t="s">
-        <v>473</v>
+        <v>523</v>
       </c>
       <c r="V53" t="s"/>
       <c r="W53" t="s">
-        <v>474</v>
+        <v>524</v>
       </c>
       <c r="X53" t="s"/>
       <c r="Y53" t="s"/>
@@ -6779,7 +7058,7 @@
     </row>
     <row r="54" spans="1:28">
       <c r="A54" t="s">
-        <v>475</v>
+        <v>525</v>
       </c>
       <c r="B54" t="s">
         <v>55</v>
@@ -6788,7 +7067,7 @@
         <v>56</v>
       </c>
       <c r="D54" t="s">
-        <v>57</v>
+        <v>526</v>
       </c>
       <c r="E54" t="s">
         <v>58</v>
@@ -6806,25 +7085,25 @@
         <v>62</v>
       </c>
       <c r="J54" t="s">
-        <v>476</v>
+        <v>527</v>
       </c>
       <c r="K54" t="s">
-        <v>477</v>
+        <v>528</v>
       </c>
       <c r="L54" t="s">
         <v>65</v>
       </c>
       <c r="M54" t="s">
-        <v>478</v>
+        <v>529</v>
       </c>
       <c r="N54" t="s">
         <v>67</v>
       </c>
       <c r="O54" t="s">
-        <v>479</v>
+        <v>530</v>
       </c>
       <c r="P54" t="s">
-        <v>480</v>
+        <v>531</v>
       </c>
       <c r="Q54" t="s">
         <v>70</v>
@@ -6837,11 +7116,11 @@
         <v>72</v>
       </c>
       <c r="U54" t="s">
-        <v>481</v>
+        <v>532</v>
       </c>
       <c r="V54" t="s"/>
       <c r="W54" t="s">
-        <v>482</v>
+        <v>533</v>
       </c>
       <c r="X54" t="s"/>
       <c r="Y54" t="s"/>
@@ -6853,7 +7132,7 @@
     </row>
     <row r="55" spans="1:28">
       <c r="A55" t="s">
-        <v>483</v>
+        <v>534</v>
       </c>
       <c r="B55" t="s">
         <v>55</v>
@@ -6862,7 +7141,7 @@
         <v>56</v>
       </c>
       <c r="D55" t="s">
-        <v>57</v>
+        <v>535</v>
       </c>
       <c r="E55" t="s">
         <v>58</v>
@@ -6880,25 +7159,25 @@
         <v>62</v>
       </c>
       <c r="J55" t="s">
-        <v>484</v>
+        <v>536</v>
       </c>
       <c r="K55" t="s">
-        <v>485</v>
+        <v>537</v>
       </c>
       <c r="L55" t="s">
         <v>65</v>
       </c>
       <c r="M55" t="s">
-        <v>486</v>
+        <v>538</v>
       </c>
       <c r="N55" t="s">
         <v>67</v>
       </c>
       <c r="O55" t="s">
-        <v>487</v>
+        <v>539</v>
       </c>
       <c r="P55" t="s">
-        <v>488</v>
+        <v>540</v>
       </c>
       <c r="Q55" t="s">
         <v>70</v>
@@ -6911,11 +7190,11 @@
         <v>72</v>
       </c>
       <c r="U55" t="s">
-        <v>489</v>
+        <v>541</v>
       </c>
       <c r="V55" t="s"/>
       <c r="W55" t="s">
-        <v>490</v>
+        <v>542</v>
       </c>
       <c r="X55" t="s"/>
       <c r="Y55" t="s"/>
@@ -6927,7 +7206,7 @@
     </row>
     <row r="56" spans="1:28">
       <c r="A56" t="s">
-        <v>491</v>
+        <v>543</v>
       </c>
       <c r="B56" t="s">
         <v>55</v>
@@ -6936,7 +7215,7 @@
         <v>56</v>
       </c>
       <c r="D56" t="s">
-        <v>57</v>
+        <v>544</v>
       </c>
       <c r="E56" t="s">
         <v>58</v>
@@ -6954,25 +7233,25 @@
         <v>62</v>
       </c>
       <c r="J56" t="s">
-        <v>492</v>
+        <v>545</v>
       </c>
       <c r="K56" t="s">
-        <v>493</v>
+        <v>546</v>
       </c>
       <c r="L56" t="s">
         <v>65</v>
       </c>
       <c r="M56" t="s">
-        <v>494</v>
+        <v>547</v>
       </c>
       <c r="N56" t="s">
         <v>67</v>
       </c>
       <c r="O56" t="s">
-        <v>495</v>
+        <v>548</v>
       </c>
       <c r="P56" t="s">
-        <v>496</v>
+        <v>549</v>
       </c>
       <c r="Q56" t="s">
         <v>70</v>
@@ -6985,11 +7264,11 @@
         <v>72</v>
       </c>
       <c r="U56" t="s">
-        <v>497</v>
+        <v>550</v>
       </c>
       <c r="V56" t="s"/>
       <c r="W56" t="s">
-        <v>498</v>
+        <v>551</v>
       </c>
       <c r="X56" t="s"/>
       <c r="Y56" t="s"/>
@@ -7001,7 +7280,7 @@
     </row>
     <row r="57" spans="1:28">
       <c r="A57" t="s">
-        <v>499</v>
+        <v>552</v>
       </c>
       <c r="B57" t="s">
         <v>55</v>
@@ -7010,7 +7289,7 @@
         <v>56</v>
       </c>
       <c r="D57" t="s">
-        <v>57</v>
+        <v>553</v>
       </c>
       <c r="E57" t="s">
         <v>58</v>
@@ -7028,25 +7307,25 @@
         <v>62</v>
       </c>
       <c r="J57" t="s">
-        <v>500</v>
+        <v>554</v>
       </c>
       <c r="K57" t="s">
-        <v>501</v>
+        <v>555</v>
       </c>
       <c r="L57" t="s">
         <v>65</v>
       </c>
       <c r="M57" t="s">
-        <v>502</v>
+        <v>556</v>
       </c>
       <c r="N57" t="s">
         <v>67</v>
       </c>
       <c r="O57" t="s">
-        <v>503</v>
+        <v>557</v>
       </c>
       <c r="P57" t="s">
-        <v>504</v>
+        <v>558</v>
       </c>
       <c r="Q57" t="s">
         <v>70</v>
@@ -7059,11 +7338,11 @@
         <v>72</v>
       </c>
       <c r="U57" t="s">
-        <v>505</v>
+        <v>559</v>
       </c>
       <c r="V57" t="s"/>
       <c r="W57" t="s">
-        <v>506</v>
+        <v>560</v>
       </c>
       <c r="X57" t="s"/>
       <c r="Y57" t="s"/>
@@ -7075,7 +7354,7 @@
     </row>
     <row r="58" spans="1:28">
       <c r="A58" t="s">
-        <v>507</v>
+        <v>561</v>
       </c>
       <c r="B58" t="s">
         <v>55</v>
@@ -7084,7 +7363,7 @@
         <v>56</v>
       </c>
       <c r="D58" t="s">
-        <v>57</v>
+        <v>562</v>
       </c>
       <c r="E58" t="s">
         <v>58</v>
@@ -7102,25 +7381,25 @@
         <v>62</v>
       </c>
       <c r="J58" t="s">
-        <v>508</v>
+        <v>563</v>
       </c>
       <c r="K58" t="s">
-        <v>509</v>
+        <v>564</v>
       </c>
       <c r="L58" t="s">
         <v>65</v>
       </c>
       <c r="M58" t="s">
-        <v>510</v>
+        <v>565</v>
       </c>
       <c r="N58" t="s">
         <v>67</v>
       </c>
       <c r="O58" t="s">
-        <v>511</v>
+        <v>566</v>
       </c>
       <c r="P58" t="s">
-        <v>512</v>
+        <v>567</v>
       </c>
       <c r="Q58" t="s">
         <v>70</v>
@@ -7133,11 +7412,11 @@
         <v>72</v>
       </c>
       <c r="U58" t="s">
-        <v>513</v>
+        <v>568</v>
       </c>
       <c r="V58" t="s"/>
       <c r="W58" t="s">
-        <v>514</v>
+        <v>569</v>
       </c>
       <c r="X58" t="s"/>
       <c r="Y58" t="s"/>
@@ -7149,7 +7428,7 @@
     </row>
     <row r="59" spans="1:28">
       <c r="A59" t="s">
-        <v>515</v>
+        <v>570</v>
       </c>
       <c r="B59" t="s">
         <v>55</v>
@@ -7158,7 +7437,7 @@
         <v>56</v>
       </c>
       <c r="D59" t="s">
-        <v>57</v>
+        <v>571</v>
       </c>
       <c r="E59" t="s">
         <v>58</v>
@@ -7176,25 +7455,25 @@
         <v>62</v>
       </c>
       <c r="J59" t="s">
-        <v>516</v>
+        <v>572</v>
       </c>
       <c r="K59" t="s">
-        <v>517</v>
+        <v>573</v>
       </c>
       <c r="L59" t="s">
         <v>65</v>
       </c>
       <c r="M59" t="s">
-        <v>518</v>
+        <v>574</v>
       </c>
       <c r="N59" t="s">
         <v>67</v>
       </c>
       <c r="O59" t="s">
-        <v>519</v>
+        <v>575</v>
       </c>
       <c r="P59" t="s">
-        <v>520</v>
+        <v>576</v>
       </c>
       <c r="Q59" t="s">
         <v>70</v>
@@ -7207,11 +7486,11 @@
         <v>72</v>
       </c>
       <c r="U59" t="s">
-        <v>521</v>
+        <v>577</v>
       </c>
       <c r="V59" t="s"/>
       <c r="W59" t="s">
-        <v>522</v>
+        <v>578</v>
       </c>
       <c r="X59" t="s"/>
       <c r="Y59" t="s"/>
@@ -7223,7 +7502,7 @@
     </row>
     <row r="60" spans="1:28">
       <c r="A60" t="s">
-        <v>523</v>
+        <v>579</v>
       </c>
       <c r="B60" t="s">
         <v>55</v>
@@ -7232,7 +7511,7 @@
         <v>56</v>
       </c>
       <c r="D60" t="s">
-        <v>57</v>
+        <v>580</v>
       </c>
       <c r="E60" t="s">
         <v>58</v>
@@ -7250,25 +7529,25 @@
         <v>62</v>
       </c>
       <c r="J60" t="s">
-        <v>524</v>
+        <v>581</v>
       </c>
       <c r="K60" t="s">
-        <v>525</v>
+        <v>582</v>
       </c>
       <c r="L60" t="s">
         <v>65</v>
       </c>
       <c r="M60" t="s">
-        <v>526</v>
+        <v>583</v>
       </c>
       <c r="N60" t="s">
         <v>67</v>
       </c>
       <c r="O60" t="s">
-        <v>527</v>
+        <v>584</v>
       </c>
       <c r="P60" t="s">
-        <v>528</v>
+        <v>585</v>
       </c>
       <c r="Q60" t="s">
         <v>70</v>
@@ -7281,11 +7560,11 @@
         <v>72</v>
       </c>
       <c r="U60" t="s">
-        <v>529</v>
+        <v>586</v>
       </c>
       <c r="V60" t="s"/>
       <c r="W60" t="s">
-        <v>530</v>
+        <v>587</v>
       </c>
       <c r="X60" t="s"/>
       <c r="Y60" t="s"/>
@@ -7297,7 +7576,7 @@
     </row>
     <row r="61" spans="1:28">
       <c r="A61" t="s">
-        <v>531</v>
+        <v>588</v>
       </c>
       <c r="B61" t="s">
         <v>55</v>
@@ -7306,7 +7585,7 @@
         <v>56</v>
       </c>
       <c r="D61" t="s">
-        <v>57</v>
+        <v>589</v>
       </c>
       <c r="E61" t="s">
         <v>58</v>
@@ -7324,25 +7603,25 @@
         <v>62</v>
       </c>
       <c r="J61" t="s">
-        <v>532</v>
+        <v>590</v>
       </c>
       <c r="K61" t="s">
-        <v>533</v>
+        <v>591</v>
       </c>
       <c r="L61" t="s">
         <v>65</v>
       </c>
       <c r="M61" t="s">
-        <v>534</v>
+        <v>592</v>
       </c>
       <c r="N61" t="s">
         <v>67</v>
       </c>
       <c r="O61" t="s">
-        <v>535</v>
+        <v>593</v>
       </c>
       <c r="P61" t="s">
-        <v>536</v>
+        <v>594</v>
       </c>
       <c r="Q61" t="s">
         <v>70</v>
@@ -7355,11 +7634,11 @@
         <v>72</v>
       </c>
       <c r="U61" t="s">
-        <v>537</v>
+        <v>595</v>
       </c>
       <c r="V61" t="s"/>
       <c r="W61" t="s">
-        <v>538</v>
+        <v>596</v>
       </c>
       <c r="X61" t="s"/>
       <c r="Y61" t="s"/>
@@ -7371,7 +7650,7 @@
     </row>
     <row r="62" spans="1:28">
       <c r="A62" t="s">
-        <v>539</v>
+        <v>597</v>
       </c>
       <c r="B62" t="s">
         <v>55</v>
@@ -7380,7 +7659,7 @@
         <v>56</v>
       </c>
       <c r="D62" t="s">
-        <v>57</v>
+        <v>598</v>
       </c>
       <c r="E62" t="s">
         <v>58</v>
@@ -7398,25 +7677,25 @@
         <v>62</v>
       </c>
       <c r="J62" t="s">
-        <v>540</v>
+        <v>599</v>
       </c>
       <c r="K62" t="s">
-        <v>541</v>
+        <v>600</v>
       </c>
       <c r="L62" t="s">
         <v>65</v>
       </c>
       <c r="M62" t="s">
-        <v>542</v>
+        <v>601</v>
       </c>
       <c r="N62" t="s">
         <v>67</v>
       </c>
       <c r="O62" t="s">
-        <v>543</v>
+        <v>602</v>
       </c>
       <c r="P62" t="s">
-        <v>544</v>
+        <v>603</v>
       </c>
       <c r="Q62" t="s">
         <v>70</v>
@@ -7429,11 +7708,11 @@
         <v>72</v>
       </c>
       <c r="U62" t="s">
-        <v>545</v>
+        <v>604</v>
       </c>
       <c r="V62" t="s"/>
       <c r="W62" t="s">
-        <v>546</v>
+        <v>605</v>
       </c>
       <c r="X62" t="s"/>
       <c r="Y62" t="s"/>
@@ -7445,7 +7724,7 @@
     </row>
     <row r="63" spans="1:28">
       <c r="A63" t="s">
-        <v>547</v>
+        <v>606</v>
       </c>
       <c r="B63" t="s">
         <v>55</v>
@@ -7454,7 +7733,7 @@
         <v>56</v>
       </c>
       <c r="D63" t="s">
-        <v>57</v>
+        <v>607</v>
       </c>
       <c r="E63" t="s">
         <v>58</v>
@@ -7472,25 +7751,25 @@
         <v>62</v>
       </c>
       <c r="J63" t="s">
-        <v>548</v>
+        <v>608</v>
       </c>
       <c r="K63" t="s">
-        <v>549</v>
+        <v>609</v>
       </c>
       <c r="L63" t="s">
         <v>65</v>
       </c>
       <c r="M63" t="s">
-        <v>550</v>
+        <v>610</v>
       </c>
       <c r="N63" t="s">
         <v>67</v>
       </c>
       <c r="O63" t="s">
-        <v>551</v>
+        <v>611</v>
       </c>
       <c r="P63" t="s">
-        <v>552</v>
+        <v>612</v>
       </c>
       <c r="Q63" t="s">
         <v>70</v>
@@ -7503,11 +7782,11 @@
         <v>72</v>
       </c>
       <c r="U63" t="s">
-        <v>553</v>
+        <v>613</v>
       </c>
       <c r="V63" t="s"/>
       <c r="W63" t="s">
-        <v>554</v>
+        <v>614</v>
       </c>
       <c r="X63" t="s"/>
       <c r="Y63" t="s"/>
@@ -7519,7 +7798,7 @@
     </row>
     <row r="64" spans="1:28">
       <c r="A64" t="s">
-        <v>555</v>
+        <v>615</v>
       </c>
       <c r="B64" t="s">
         <v>55</v>
@@ -7528,7 +7807,7 @@
         <v>56</v>
       </c>
       <c r="D64" t="s">
-        <v>57</v>
+        <v>616</v>
       </c>
       <c r="E64" t="s">
         <v>58</v>
@@ -7546,25 +7825,25 @@
         <v>62</v>
       </c>
       <c r="J64" t="s">
-        <v>556</v>
+        <v>617</v>
       </c>
       <c r="K64" t="s">
-        <v>557</v>
+        <v>618</v>
       </c>
       <c r="L64" t="s">
         <v>65</v>
       </c>
       <c r="M64" t="s">
-        <v>558</v>
+        <v>619</v>
       </c>
       <c r="N64" t="s">
         <v>67</v>
       </c>
       <c r="O64" t="s">
-        <v>559</v>
+        <v>620</v>
       </c>
       <c r="P64" t="s">
-        <v>560</v>
+        <v>621</v>
       </c>
       <c r="Q64" t="s">
         <v>70</v>
@@ -7577,11 +7856,11 @@
         <v>72</v>
       </c>
       <c r="U64" t="s">
-        <v>561</v>
+        <v>622</v>
       </c>
       <c r="V64" t="s"/>
       <c r="W64" t="s">
-        <v>562</v>
+        <v>623</v>
       </c>
       <c r="X64" t="s"/>
       <c r="Y64" t="s"/>
@@ -7593,7 +7872,7 @@
     </row>
     <row r="65" spans="1:28">
       <c r="A65" t="s">
-        <v>563</v>
+        <v>624</v>
       </c>
       <c r="B65" t="s">
         <v>55</v>
@@ -7602,7 +7881,7 @@
         <v>56</v>
       </c>
       <c r="D65" t="s">
-        <v>57</v>
+        <v>625</v>
       </c>
       <c r="E65" t="s">
         <v>58</v>
@@ -7620,25 +7899,25 @@
         <v>62</v>
       </c>
       <c r="J65" t="s">
-        <v>564</v>
+        <v>626</v>
       </c>
       <c r="K65" t="s">
-        <v>565</v>
+        <v>627</v>
       </c>
       <c r="L65" t="s">
         <v>65</v>
       </c>
       <c r="M65" t="s">
-        <v>566</v>
+        <v>628</v>
       </c>
       <c r="N65" t="s">
         <v>67</v>
       </c>
       <c r="O65" t="s">
-        <v>567</v>
+        <v>629</v>
       </c>
       <c r="P65" t="s">
-        <v>568</v>
+        <v>630</v>
       </c>
       <c r="Q65" t="s">
         <v>70</v>
@@ -7651,11 +7930,11 @@
         <v>72</v>
       </c>
       <c r="U65" t="s">
-        <v>569</v>
+        <v>631</v>
       </c>
       <c r="V65" t="s"/>
       <c r="W65" t="s">
-        <v>570</v>
+        <v>632</v>
       </c>
       <c r="X65" t="s"/>
       <c r="Y65" t="s"/>
@@ -7667,7 +7946,7 @@
     </row>
     <row r="66" spans="1:28">
       <c r="A66" t="s">
-        <v>571</v>
+        <v>633</v>
       </c>
       <c r="B66" t="s">
         <v>55</v>
@@ -7676,7 +7955,7 @@
         <v>56</v>
       </c>
       <c r="D66" t="s">
-        <v>57</v>
+        <v>634</v>
       </c>
       <c r="E66" t="s">
         <v>58</v>
@@ -7694,25 +7973,25 @@
         <v>62</v>
       </c>
       <c r="J66" t="s">
-        <v>572</v>
+        <v>635</v>
       </c>
       <c r="K66" t="s">
-        <v>573</v>
+        <v>636</v>
       </c>
       <c r="L66" t="s">
         <v>65</v>
       </c>
       <c r="M66" t="s">
-        <v>574</v>
+        <v>637</v>
       </c>
       <c r="N66" t="s">
         <v>67</v>
       </c>
       <c r="O66" t="s">
-        <v>575</v>
+        <v>638</v>
       </c>
       <c r="P66" t="s">
-        <v>576</v>
+        <v>639</v>
       </c>
       <c r="Q66" t="s">
         <v>70</v>
@@ -7725,11 +8004,11 @@
         <v>72</v>
       </c>
       <c r="U66" t="s">
-        <v>577</v>
+        <v>640</v>
       </c>
       <c r="V66" t="s"/>
       <c r="W66" t="s">
-        <v>578</v>
+        <v>641</v>
       </c>
       <c r="X66" t="s"/>
       <c r="Y66" t="s"/>
@@ -7741,7 +8020,7 @@
     </row>
     <row r="67" spans="1:28">
       <c r="A67" t="s">
-        <v>579</v>
+        <v>642</v>
       </c>
       <c r="B67" t="s">
         <v>55</v>
@@ -7750,7 +8029,7 @@
         <v>56</v>
       </c>
       <c r="D67" t="s">
-        <v>57</v>
+        <v>643</v>
       </c>
       <c r="E67" t="s">
         <v>58</v>
@@ -7768,25 +8047,25 @@
         <v>62</v>
       </c>
       <c r="J67" t="s">
-        <v>580</v>
+        <v>644</v>
       </c>
       <c r="K67" t="s">
-        <v>581</v>
+        <v>645</v>
       </c>
       <c r="L67" t="s">
         <v>65</v>
       </c>
       <c r="M67" t="s">
-        <v>582</v>
+        <v>646</v>
       </c>
       <c r="N67" t="s">
         <v>67</v>
       </c>
       <c r="O67" t="s">
-        <v>583</v>
+        <v>647</v>
       </c>
       <c r="P67" t="s">
-        <v>584</v>
+        <v>648</v>
       </c>
       <c r="Q67" t="s">
         <v>70</v>
@@ -7799,11 +8078,11 @@
         <v>72</v>
       </c>
       <c r="U67" t="s">
-        <v>585</v>
+        <v>649</v>
       </c>
       <c r="V67" t="s"/>
       <c r="W67" t="s">
-        <v>586</v>
+        <v>650</v>
       </c>
       <c r="X67" t="s"/>
       <c r="Y67" t="s"/>
@@ -7815,7 +8094,7 @@
     </row>
     <row r="68" spans="1:28">
       <c r="A68" t="s">
-        <v>587</v>
+        <v>651</v>
       </c>
       <c r="B68" t="s">
         <v>55</v>
@@ -7824,7 +8103,7 @@
         <v>56</v>
       </c>
       <c r="D68" t="s">
-        <v>57</v>
+        <v>652</v>
       </c>
       <c r="E68" t="s">
         <v>58</v>
@@ -7842,25 +8121,25 @@
         <v>62</v>
       </c>
       <c r="J68" t="s">
-        <v>588</v>
+        <v>653</v>
       </c>
       <c r="K68" t="s">
-        <v>589</v>
+        <v>654</v>
       </c>
       <c r="L68" t="s">
         <v>65</v>
       </c>
       <c r="M68" t="s">
-        <v>590</v>
+        <v>655</v>
       </c>
       <c r="N68" t="s">
         <v>67</v>
       </c>
       <c r="O68" t="s">
-        <v>591</v>
+        <v>656</v>
       </c>
       <c r="P68" t="s">
-        <v>592</v>
+        <v>657</v>
       </c>
       <c r="Q68" t="s">
         <v>70</v>
@@ -7873,11 +8152,11 @@
         <v>72</v>
       </c>
       <c r="U68" t="s">
-        <v>593</v>
+        <v>658</v>
       </c>
       <c r="V68" t="s"/>
       <c r="W68" t="s">
-        <v>594</v>
+        <v>659</v>
       </c>
       <c r="X68" t="s"/>
       <c r="Y68" t="s"/>
@@ -7889,7 +8168,7 @@
     </row>
     <row r="69" spans="1:28">
       <c r="A69" t="s">
-        <v>595</v>
+        <v>660</v>
       </c>
       <c r="B69" t="s">
         <v>55</v>
@@ -7898,7 +8177,7 @@
         <v>56</v>
       </c>
       <c r="D69" t="s">
-        <v>57</v>
+        <v>661</v>
       </c>
       <c r="E69" t="s">
         <v>58</v>
@@ -7916,25 +8195,25 @@
         <v>62</v>
       </c>
       <c r="J69" t="s">
-        <v>596</v>
+        <v>662</v>
       </c>
       <c r="K69" t="s">
-        <v>597</v>
+        <v>663</v>
       </c>
       <c r="L69" t="s">
         <v>65</v>
       </c>
       <c r="M69" t="s">
-        <v>598</v>
+        <v>664</v>
       </c>
       <c r="N69" t="s">
         <v>67</v>
       </c>
       <c r="O69" t="s">
-        <v>599</v>
+        <v>665</v>
       </c>
       <c r="P69" t="s">
-        <v>600</v>
+        <v>666</v>
       </c>
       <c r="Q69" t="s">
         <v>70</v>
@@ -7947,11 +8226,11 @@
         <v>72</v>
       </c>
       <c r="U69" t="s">
-        <v>601</v>
+        <v>667</v>
       </c>
       <c r="V69" t="s"/>
       <c r="W69" t="s">
-        <v>602</v>
+        <v>668</v>
       </c>
       <c r="X69" t="s"/>
       <c r="Y69" t="s"/>
@@ -7963,7 +8242,7 @@
     </row>
     <row r="70" spans="1:28">
       <c r="A70" t="s">
-        <v>603</v>
+        <v>669</v>
       </c>
       <c r="B70" t="s">
         <v>55</v>
@@ -7972,7 +8251,7 @@
         <v>56</v>
       </c>
       <c r="D70" t="s">
-        <v>57</v>
+        <v>670</v>
       </c>
       <c r="E70" t="s">
         <v>58</v>
@@ -7990,25 +8269,25 @@
         <v>62</v>
       </c>
       <c r="J70" t="s">
-        <v>604</v>
+        <v>671</v>
       </c>
       <c r="K70" t="s">
-        <v>605</v>
+        <v>672</v>
       </c>
       <c r="L70" t="s">
         <v>65</v>
       </c>
       <c r="M70" t="s">
-        <v>606</v>
+        <v>673</v>
       </c>
       <c r="N70" t="s">
         <v>67</v>
       </c>
       <c r="O70" t="s">
-        <v>607</v>
+        <v>674</v>
       </c>
       <c r="P70" t="s">
-        <v>608</v>
+        <v>675</v>
       </c>
       <c r="Q70" t="s">
         <v>70</v>
@@ -8021,11 +8300,11 @@
         <v>72</v>
       </c>
       <c r="U70" t="s">
-        <v>609</v>
+        <v>676</v>
       </c>
       <c r="V70" t="s"/>
       <c r="W70" t="s">
-        <v>610</v>
+        <v>677</v>
       </c>
       <c r="X70" t="s"/>
       <c r="Y70" t="s"/>
@@ -8037,7 +8316,7 @@
     </row>
     <row r="71" spans="1:28">
       <c r="A71" t="s">
-        <v>611</v>
+        <v>678</v>
       </c>
       <c r="B71" t="s">
         <v>55</v>
@@ -8046,7 +8325,7 @@
         <v>56</v>
       </c>
       <c r="D71" t="s">
-        <v>57</v>
+        <v>679</v>
       </c>
       <c r="E71" t="s">
         <v>58</v>
@@ -8064,25 +8343,25 @@
         <v>62</v>
       </c>
       <c r="J71" t="s">
-        <v>612</v>
+        <v>680</v>
       </c>
       <c r="K71" t="s">
-        <v>613</v>
+        <v>681</v>
       </c>
       <c r="L71" t="s">
         <v>65</v>
       </c>
       <c r="M71" t="s">
-        <v>614</v>
+        <v>682</v>
       </c>
       <c r="N71" t="s">
         <v>67</v>
       </c>
       <c r="O71" t="s">
-        <v>615</v>
+        <v>683</v>
       </c>
       <c r="P71" t="s">
-        <v>616</v>
+        <v>684</v>
       </c>
       <c r="Q71" t="s">
         <v>70</v>
@@ -8095,11 +8374,11 @@
         <v>72</v>
       </c>
       <c r="U71" t="s">
-        <v>617</v>
+        <v>685</v>
       </c>
       <c r="V71" t="s"/>
       <c r="W71" t="s">
-        <v>618</v>
+        <v>686</v>
       </c>
       <c r="X71" t="s"/>
       <c r="Y71" t="s"/>
@@ -8111,7 +8390,7 @@
     </row>
     <row r="72" spans="1:28">
       <c r="A72" t="s">
-        <v>619</v>
+        <v>687</v>
       </c>
       <c r="B72" t="s">
         <v>55</v>
@@ -8120,7 +8399,7 @@
         <v>56</v>
       </c>
       <c r="D72" t="s">
-        <v>57</v>
+        <v>688</v>
       </c>
       <c r="E72" t="s">
         <v>58</v>
@@ -8138,25 +8417,25 @@
         <v>62</v>
       </c>
       <c r="J72" t="s">
-        <v>620</v>
+        <v>689</v>
       </c>
       <c r="K72" t="s">
-        <v>621</v>
+        <v>690</v>
       </c>
       <c r="L72" t="s">
         <v>65</v>
       </c>
       <c r="M72" t="s">
-        <v>622</v>
+        <v>691</v>
       </c>
       <c r="N72" t="s">
         <v>67</v>
       </c>
       <c r="O72" t="s">
-        <v>623</v>
+        <v>692</v>
       </c>
       <c r="P72" t="s">
-        <v>624</v>
+        <v>693</v>
       </c>
       <c r="Q72" t="s">
         <v>70</v>
@@ -8169,11 +8448,11 @@
         <v>72</v>
       </c>
       <c r="U72" t="s">
-        <v>625</v>
+        <v>694</v>
       </c>
       <c r="V72" t="s"/>
       <c r="W72" t="s">
-        <v>626</v>
+        <v>695</v>
       </c>
       <c r="X72" t="s"/>
       <c r="Y72" t="s"/>
@@ -8185,7 +8464,7 @@
     </row>
     <row r="73" spans="1:28">
       <c r="A73" t="s">
-        <v>627</v>
+        <v>696</v>
       </c>
       <c r="B73" t="s">
         <v>55</v>
@@ -8194,7 +8473,7 @@
         <v>56</v>
       </c>
       <c r="D73" t="s">
-        <v>57</v>
+        <v>697</v>
       </c>
       <c r="E73" t="s">
         <v>58</v>
@@ -8212,25 +8491,25 @@
         <v>62</v>
       </c>
       <c r="J73" t="s">
-        <v>628</v>
+        <v>698</v>
       </c>
       <c r="K73" t="s">
-        <v>629</v>
+        <v>699</v>
       </c>
       <c r="L73" t="s">
         <v>65</v>
       </c>
       <c r="M73" t="s">
-        <v>630</v>
+        <v>700</v>
       </c>
       <c r="N73" t="s">
         <v>67</v>
       </c>
       <c r="O73" t="s">
-        <v>631</v>
+        <v>701</v>
       </c>
       <c r="P73" t="s">
-        <v>632</v>
+        <v>702</v>
       </c>
       <c r="Q73" t="s">
         <v>70</v>
@@ -8243,11 +8522,11 @@
         <v>72</v>
       </c>
       <c r="U73" t="s">
-        <v>633</v>
+        <v>703</v>
       </c>
       <c r="V73" t="s"/>
       <c r="W73" t="s">
-        <v>634</v>
+        <v>704</v>
       </c>
       <c r="X73" t="s"/>
       <c r="Y73" t="s"/>
@@ -8259,7 +8538,7 @@
     </row>
     <row r="74" spans="1:28">
       <c r="A74" t="s">
-        <v>635</v>
+        <v>705</v>
       </c>
       <c r="B74" t="s">
         <v>55</v>
@@ -8268,7 +8547,7 @@
         <v>56</v>
       </c>
       <c r="D74" t="s">
-        <v>57</v>
+        <v>706</v>
       </c>
       <c r="E74" t="s">
         <v>58</v>
@@ -8286,25 +8565,25 @@
         <v>62</v>
       </c>
       <c r="J74" t="s">
-        <v>636</v>
+        <v>707</v>
       </c>
       <c r="K74" t="s">
-        <v>637</v>
+        <v>708</v>
       </c>
       <c r="L74" t="s">
         <v>65</v>
       </c>
       <c r="M74" t="s">
-        <v>638</v>
+        <v>709</v>
       </c>
       <c r="N74" t="s">
         <v>67</v>
       </c>
       <c r="O74" t="s">
-        <v>639</v>
+        <v>710</v>
       </c>
       <c r="P74" t="s">
-        <v>640</v>
+        <v>711</v>
       </c>
       <c r="Q74" t="s">
         <v>70</v>
@@ -8317,11 +8596,11 @@
         <v>72</v>
       </c>
       <c r="U74" t="s">
-        <v>641</v>
+        <v>712</v>
       </c>
       <c r="V74" t="s"/>
       <c r="W74" t="s">
-        <v>642</v>
+        <v>713</v>
       </c>
       <c r="X74" t="s"/>
       <c r="Y74" t="s"/>
@@ -8333,7 +8612,7 @@
     </row>
     <row r="75" spans="1:28">
       <c r="A75" t="s">
-        <v>643</v>
+        <v>714</v>
       </c>
       <c r="B75" t="s">
         <v>55</v>
@@ -8342,7 +8621,7 @@
         <v>56</v>
       </c>
       <c r="D75" t="s">
-        <v>57</v>
+        <v>715</v>
       </c>
       <c r="E75" t="s">
         <v>58</v>
@@ -8360,25 +8639,25 @@
         <v>62</v>
       </c>
       <c r="J75" t="s">
-        <v>644</v>
+        <v>716</v>
       </c>
       <c r="K75" t="s">
-        <v>645</v>
+        <v>717</v>
       </c>
       <c r="L75" t="s">
         <v>65</v>
       </c>
       <c r="M75" t="s">
-        <v>646</v>
+        <v>718</v>
       </c>
       <c r="N75" t="s">
         <v>67</v>
       </c>
       <c r="O75" t="s">
-        <v>647</v>
+        <v>719</v>
       </c>
       <c r="P75" t="s">
-        <v>648</v>
+        <v>720</v>
       </c>
       <c r="Q75" t="s">
         <v>70</v>
@@ -8391,11 +8670,11 @@
         <v>72</v>
       </c>
       <c r="U75" t="s">
-        <v>649</v>
+        <v>721</v>
       </c>
       <c r="V75" t="s"/>
       <c r="W75" t="s">
-        <v>650</v>
+        <v>722</v>
       </c>
       <c r="X75" t="s"/>
       <c r="Y75" t="s"/>
@@ -8407,7 +8686,7 @@
     </row>
     <row r="76" spans="1:28">
       <c r="A76" t="s">
-        <v>651</v>
+        <v>723</v>
       </c>
       <c r="B76" t="s">
         <v>55</v>
@@ -8416,7 +8695,7 @@
         <v>56</v>
       </c>
       <c r="D76" t="s">
-        <v>57</v>
+        <v>724</v>
       </c>
       <c r="E76" t="s">
         <v>58</v>
@@ -8434,25 +8713,25 @@
         <v>62</v>
       </c>
       <c r="J76" t="s">
-        <v>652</v>
+        <v>725</v>
       </c>
       <c r="K76" t="s">
-        <v>653</v>
+        <v>726</v>
       </c>
       <c r="L76" t="s">
         <v>65</v>
       </c>
       <c r="M76" t="s">
-        <v>654</v>
+        <v>727</v>
       </c>
       <c r="N76" t="s">
         <v>67</v>
       </c>
       <c r="O76" t="s">
-        <v>655</v>
+        <v>728</v>
       </c>
       <c r="P76" t="s">
-        <v>656</v>
+        <v>729</v>
       </c>
       <c r="Q76" t="s">
         <v>70</v>
@@ -8465,11 +8744,11 @@
         <v>72</v>
       </c>
       <c r="U76" t="s">
-        <v>657</v>
+        <v>730</v>
       </c>
       <c r="V76" t="s"/>
       <c r="W76" t="s">
-        <v>658</v>
+        <v>731</v>
       </c>
       <c r="X76" t="s"/>
       <c r="Y76" t="s"/>
@@ -8481,7 +8760,7 @@
     </row>
     <row r="77" spans="1:28">
       <c r="A77" t="s">
-        <v>659</v>
+        <v>732</v>
       </c>
       <c r="B77" t="s">
         <v>55</v>
@@ -8490,7 +8769,7 @@
         <v>56</v>
       </c>
       <c r="D77" t="s">
-        <v>57</v>
+        <v>733</v>
       </c>
       <c r="E77" t="s">
         <v>58</v>
@@ -8508,25 +8787,25 @@
         <v>62</v>
       </c>
       <c r="J77" t="s">
-        <v>660</v>
+        <v>734</v>
       </c>
       <c r="K77" t="s">
-        <v>661</v>
+        <v>735</v>
       </c>
       <c r="L77" t="s">
         <v>65</v>
       </c>
       <c r="M77" t="s">
-        <v>662</v>
+        <v>736</v>
       </c>
       <c r="N77" t="s">
         <v>67</v>
       </c>
       <c r="O77" t="s">
-        <v>663</v>
+        <v>737</v>
       </c>
       <c r="P77" t="s">
-        <v>664</v>
+        <v>738</v>
       </c>
       <c r="Q77" t="s">
         <v>70</v>
@@ -8539,11 +8818,11 @@
         <v>72</v>
       </c>
       <c r="U77" t="s">
-        <v>665</v>
+        <v>739</v>
       </c>
       <c r="V77" t="s"/>
       <c r="W77" t="s">
-        <v>666</v>
+        <v>740</v>
       </c>
       <c r="X77" t="s"/>
       <c r="Y77" t="s"/>
@@ -8555,7 +8834,7 @@
     </row>
     <row r="78" spans="1:28">
       <c r="A78" t="s">
-        <v>667</v>
+        <v>741</v>
       </c>
       <c r="B78" t="s">
         <v>55</v>
@@ -8564,7 +8843,7 @@
         <v>56</v>
       </c>
       <c r="D78" t="s">
-        <v>57</v>
+        <v>742</v>
       </c>
       <c r="E78" t="s">
         <v>58</v>
@@ -8582,25 +8861,25 @@
         <v>62</v>
       </c>
       <c r="J78" t="s">
-        <v>668</v>
+        <v>743</v>
       </c>
       <c r="K78" t="s">
-        <v>669</v>
+        <v>744</v>
       </c>
       <c r="L78" t="s">
         <v>65</v>
       </c>
       <c r="M78" t="s">
-        <v>670</v>
+        <v>745</v>
       </c>
       <c r="N78" t="s">
         <v>67</v>
       </c>
       <c r="O78" t="s">
-        <v>671</v>
+        <v>746</v>
       </c>
       <c r="P78" t="s">
-        <v>672</v>
+        <v>747</v>
       </c>
       <c r="Q78" t="s">
         <v>70</v>
@@ -8613,11 +8892,11 @@
         <v>72</v>
       </c>
       <c r="U78" t="s">
-        <v>673</v>
+        <v>748</v>
       </c>
       <c r="V78" t="s"/>
       <c r="W78" t="s">
-        <v>674</v>
+        <v>749</v>
       </c>
       <c r="X78" t="s"/>
       <c r="Y78" t="s"/>
@@ -8629,7 +8908,7 @@
     </row>
     <row r="79" spans="1:28">
       <c r="A79" t="s">
-        <v>675</v>
+        <v>750</v>
       </c>
       <c r="B79" t="s">
         <v>55</v>
@@ -8638,7 +8917,7 @@
         <v>56</v>
       </c>
       <c r="D79" t="s">
-        <v>57</v>
+        <v>751</v>
       </c>
       <c r="E79" t="s">
         <v>58</v>
@@ -8656,25 +8935,25 @@
         <v>62</v>
       </c>
       <c r="J79" t="s">
-        <v>676</v>
+        <v>752</v>
       </c>
       <c r="K79" t="s">
-        <v>677</v>
+        <v>753</v>
       </c>
       <c r="L79" t="s">
         <v>65</v>
       </c>
       <c r="M79" t="s">
-        <v>678</v>
+        <v>754</v>
       </c>
       <c r="N79" t="s">
         <v>67</v>
       </c>
       <c r="O79" t="s">
-        <v>679</v>
+        <v>755</v>
       </c>
       <c r="P79" t="s">
-        <v>680</v>
+        <v>756</v>
       </c>
       <c r="Q79" t="s">
         <v>70</v>
@@ -8687,11 +8966,11 @@
         <v>72</v>
       </c>
       <c r="U79" t="s">
-        <v>681</v>
+        <v>757</v>
       </c>
       <c r="V79" t="s"/>
       <c r="W79" t="s">
-        <v>682</v>
+        <v>758</v>
       </c>
       <c r="X79" t="s"/>
       <c r="Y79" t="s"/>
@@ -8703,7 +8982,7 @@
     </row>
     <row r="80" spans="1:28">
       <c r="A80" t="s">
-        <v>683</v>
+        <v>759</v>
       </c>
       <c r="B80" t="s">
         <v>55</v>
@@ -8712,7 +8991,7 @@
         <v>56</v>
       </c>
       <c r="D80" t="s">
-        <v>57</v>
+        <v>760</v>
       </c>
       <c r="E80" t="s">
         <v>58</v>
@@ -8730,25 +9009,25 @@
         <v>62</v>
       </c>
       <c r="J80" t="s">
-        <v>684</v>
+        <v>761</v>
       </c>
       <c r="K80" t="s">
-        <v>685</v>
+        <v>762</v>
       </c>
       <c r="L80" t="s">
         <v>65</v>
       </c>
       <c r="M80" t="s">
-        <v>686</v>
+        <v>763</v>
       </c>
       <c r="N80" t="s">
         <v>67</v>
       </c>
       <c r="O80" t="s">
-        <v>687</v>
+        <v>764</v>
       </c>
       <c r="P80" t="s">
-        <v>688</v>
+        <v>765</v>
       </c>
       <c r="Q80" t="s">
         <v>70</v>
@@ -8761,11 +9040,11 @@
         <v>72</v>
       </c>
       <c r="U80" t="s">
-        <v>689</v>
+        <v>766</v>
       </c>
       <c r="V80" t="s"/>
       <c r="W80" t="s">
-        <v>690</v>
+        <v>767</v>
       </c>
       <c r="X80" t="s"/>
       <c r="Y80" t="s"/>
@@ -8777,7 +9056,7 @@
     </row>
     <row r="81" spans="1:28">
       <c r="A81" t="s">
-        <v>691</v>
+        <v>768</v>
       </c>
       <c r="B81" t="s">
         <v>55</v>
@@ -8786,7 +9065,7 @@
         <v>56</v>
       </c>
       <c r="D81" t="s">
-        <v>57</v>
+        <v>769</v>
       </c>
       <c r="E81" t="s">
         <v>58</v>
@@ -8804,25 +9083,25 @@
         <v>62</v>
       </c>
       <c r="J81" t="s">
-        <v>692</v>
+        <v>770</v>
       </c>
       <c r="K81" t="s">
-        <v>693</v>
+        <v>771</v>
       </c>
       <c r="L81" t="s">
         <v>65</v>
       </c>
       <c r="M81" t="s">
-        <v>694</v>
+        <v>772</v>
       </c>
       <c r="N81" t="s">
         <v>67</v>
       </c>
       <c r="O81" t="s">
-        <v>695</v>
+        <v>773</v>
       </c>
       <c r="P81" t="s">
-        <v>696</v>
+        <v>774</v>
       </c>
       <c r="Q81" t="s">
         <v>70</v>
@@ -8835,11 +9114,11 @@
         <v>72</v>
       </c>
       <c r="U81" t="s">
-        <v>697</v>
+        <v>775</v>
       </c>
       <c r="V81" t="s"/>
       <c r="W81" t="s">
-        <v>698</v>
+        <v>776</v>
       </c>
       <c r="X81" t="s"/>
       <c r="Y81" t="s"/>
@@ -8851,7 +9130,7 @@
     </row>
     <row r="82" spans="1:28">
       <c r="A82" t="s">
-        <v>699</v>
+        <v>777</v>
       </c>
       <c r="B82" t="s">
         <v>55</v>
@@ -8860,7 +9139,7 @@
         <v>56</v>
       </c>
       <c r="D82" t="s">
-        <v>57</v>
+        <v>778</v>
       </c>
       <c r="E82" t="s">
         <v>58</v>
@@ -8878,25 +9157,25 @@
         <v>62</v>
       </c>
       <c r="J82" t="s">
-        <v>700</v>
+        <v>779</v>
       </c>
       <c r="K82" t="s">
-        <v>701</v>
+        <v>780</v>
       </c>
       <c r="L82" t="s">
         <v>65</v>
       </c>
       <c r="M82" t="s">
-        <v>702</v>
+        <v>781</v>
       </c>
       <c r="N82" t="s">
         <v>67</v>
       </c>
       <c r="O82" t="s">
-        <v>703</v>
+        <v>782</v>
       </c>
       <c r="P82" t="s">
-        <v>704</v>
+        <v>783</v>
       </c>
       <c r="Q82" t="s">
         <v>70</v>
@@ -8909,11 +9188,11 @@
         <v>72</v>
       </c>
       <c r="U82" t="s">
-        <v>705</v>
+        <v>784</v>
       </c>
       <c r="V82" t="s"/>
       <c r="W82" t="s">
-        <v>706</v>
+        <v>785</v>
       </c>
       <c r="X82" t="s"/>
       <c r="Y82" t="s"/>
@@ -8925,7 +9204,7 @@
     </row>
     <row r="83" spans="1:28">
       <c r="A83" t="s">
-        <v>707</v>
+        <v>786</v>
       </c>
       <c r="B83" t="s">
         <v>55</v>
@@ -8934,7 +9213,7 @@
         <v>56</v>
       </c>
       <c r="D83" t="s">
-        <v>57</v>
+        <v>787</v>
       </c>
       <c r="E83" t="s">
         <v>58</v>
@@ -8952,25 +9231,25 @@
         <v>62</v>
       </c>
       <c r="J83" t="s">
-        <v>708</v>
+        <v>788</v>
       </c>
       <c r="K83" t="s">
-        <v>709</v>
+        <v>789</v>
       </c>
       <c r="L83" t="s">
         <v>65</v>
       </c>
       <c r="M83" t="s">
-        <v>710</v>
+        <v>790</v>
       </c>
       <c r="N83" t="s">
         <v>67</v>
       </c>
       <c r="O83" t="s">
-        <v>711</v>
+        <v>791</v>
       </c>
       <c r="P83" t="s">
-        <v>712</v>
+        <v>792</v>
       </c>
       <c r="Q83" t="s">
         <v>70</v>
@@ -8983,11 +9262,11 @@
         <v>72</v>
       </c>
       <c r="U83" t="s">
-        <v>713</v>
+        <v>793</v>
       </c>
       <c r="V83" t="s"/>
       <c r="W83" t="s">
-        <v>714</v>
+        <v>794</v>
       </c>
       <c r="X83" t="s"/>
       <c r="Y83" t="s"/>
@@ -8999,7 +9278,7 @@
     </row>
     <row r="84" spans="1:28">
       <c r="A84" t="s">
-        <v>715</v>
+        <v>795</v>
       </c>
       <c r="B84" t="s">
         <v>55</v>
@@ -9008,7 +9287,7 @@
         <v>56</v>
       </c>
       <c r="D84" t="s">
-        <v>57</v>
+        <v>796</v>
       </c>
       <c r="E84" t="s">
         <v>58</v>
@@ -9026,25 +9305,25 @@
         <v>62</v>
       </c>
       <c r="J84" t="s">
-        <v>716</v>
+        <v>797</v>
       </c>
       <c r="K84" t="s">
-        <v>717</v>
+        <v>798</v>
       </c>
       <c r="L84" t="s">
         <v>65</v>
       </c>
       <c r="M84" t="s">
-        <v>718</v>
+        <v>799</v>
       </c>
       <c r="N84" t="s">
         <v>67</v>
       </c>
       <c r="O84" t="s">
-        <v>719</v>
+        <v>800</v>
       </c>
       <c r="P84" t="s">
-        <v>720</v>
+        <v>801</v>
       </c>
       <c r="Q84" t="s">
         <v>70</v>
@@ -9057,11 +9336,11 @@
         <v>72</v>
       </c>
       <c r="U84" t="s">
-        <v>721</v>
+        <v>802</v>
       </c>
       <c r="V84" t="s"/>
       <c r="W84" t="s">
-        <v>722</v>
+        <v>803</v>
       </c>
       <c r="X84" t="s"/>
       <c r="Y84" t="s"/>
@@ -9073,7 +9352,7 @@
     </row>
     <row r="85" spans="1:28">
       <c r="A85" t="s">
-        <v>723</v>
+        <v>804</v>
       </c>
       <c r="B85" t="s">
         <v>55</v>
@@ -9082,7 +9361,7 @@
         <v>56</v>
       </c>
       <c r="D85" t="s">
-        <v>57</v>
+        <v>805</v>
       </c>
       <c r="E85" t="s">
         <v>58</v>
@@ -9100,25 +9379,25 @@
         <v>62</v>
       </c>
       <c r="J85" t="s">
-        <v>724</v>
+        <v>806</v>
       </c>
       <c r="K85" t="s">
-        <v>725</v>
+        <v>807</v>
       </c>
       <c r="L85" t="s">
         <v>65</v>
       </c>
       <c r="M85" t="s">
-        <v>726</v>
+        <v>808</v>
       </c>
       <c r="N85" t="s">
         <v>67</v>
       </c>
       <c r="O85" t="s">
-        <v>727</v>
+        <v>809</v>
       </c>
       <c r="P85" t="s">
-        <v>728</v>
+        <v>810</v>
       </c>
       <c r="Q85" t="s">
         <v>70</v>
@@ -9131,11 +9410,11 @@
         <v>72</v>
       </c>
       <c r="U85" t="s">
-        <v>729</v>
+        <v>811</v>
       </c>
       <c r="V85" t="s"/>
       <c r="W85" t="s">
-        <v>730</v>
+        <v>812</v>
       </c>
       <c r="X85" t="s"/>
       <c r="Y85" t="s"/>
@@ -9147,7 +9426,7 @@
     </row>
     <row r="86" spans="1:28">
       <c r="A86" t="s">
-        <v>731</v>
+        <v>813</v>
       </c>
       <c r="B86" t="s">
         <v>55</v>
@@ -9156,7 +9435,7 @@
         <v>56</v>
       </c>
       <c r="D86" t="s">
-        <v>57</v>
+        <v>814</v>
       </c>
       <c r="E86" t="s">
         <v>58</v>
@@ -9174,25 +9453,25 @@
         <v>62</v>
       </c>
       <c r="J86" t="s">
-        <v>732</v>
+        <v>815</v>
       </c>
       <c r="K86" t="s">
-        <v>733</v>
+        <v>816</v>
       </c>
       <c r="L86" t="s">
         <v>65</v>
       </c>
       <c r="M86" t="s">
-        <v>734</v>
+        <v>817</v>
       </c>
       <c r="N86" t="s">
         <v>67</v>
       </c>
       <c r="O86" t="s">
-        <v>735</v>
+        <v>818</v>
       </c>
       <c r="P86" t="s">
-        <v>736</v>
+        <v>819</v>
       </c>
       <c r="Q86" t="s">
         <v>70</v>
@@ -9205,11 +9484,11 @@
         <v>72</v>
       </c>
       <c r="U86" t="s">
-        <v>737</v>
+        <v>820</v>
       </c>
       <c r="V86" t="s"/>
       <c r="W86" t="s">
-        <v>738</v>
+        <v>821</v>
       </c>
       <c r="X86" t="s"/>
       <c r="Y86" t="s"/>
@@ -9221,7 +9500,7 @@
     </row>
     <row r="87" spans="1:28">
       <c r="A87" t="s">
-        <v>739</v>
+        <v>822</v>
       </c>
       <c r="B87" t="s">
         <v>55</v>
@@ -9230,7 +9509,7 @@
         <v>56</v>
       </c>
       <c r="D87" t="s">
-        <v>57</v>
+        <v>823</v>
       </c>
       <c r="E87" t="s">
         <v>58</v>
@@ -9248,25 +9527,25 @@
         <v>62</v>
       </c>
       <c r="J87" t="s">
-        <v>740</v>
+        <v>824</v>
       </c>
       <c r="K87" t="s">
-        <v>741</v>
+        <v>825</v>
       </c>
       <c r="L87" t="s">
         <v>65</v>
       </c>
       <c r="M87" t="s">
-        <v>742</v>
+        <v>826</v>
       </c>
       <c r="N87" t="s">
         <v>67</v>
       </c>
       <c r="O87" t="s">
-        <v>743</v>
+        <v>827</v>
       </c>
       <c r="P87" t="s">
-        <v>744</v>
+        <v>828</v>
       </c>
       <c r="Q87" t="s">
         <v>70</v>
@@ -9279,11 +9558,11 @@
         <v>72</v>
       </c>
       <c r="U87" t="s">
-        <v>745</v>
+        <v>829</v>
       </c>
       <c r="V87" t="s"/>
       <c r="W87" t="s">
-        <v>746</v>
+        <v>830</v>
       </c>
       <c r="X87" t="s"/>
       <c r="Y87" t="s"/>
@@ -9295,7 +9574,7 @@
     </row>
     <row r="88" spans="1:28">
       <c r="A88" t="s">
-        <v>747</v>
+        <v>831</v>
       </c>
       <c r="B88" t="s">
         <v>55</v>
@@ -9304,7 +9583,7 @@
         <v>56</v>
       </c>
       <c r="D88" t="s">
-        <v>57</v>
+        <v>832</v>
       </c>
       <c r="E88" t="s">
         <v>58</v>
@@ -9322,25 +9601,25 @@
         <v>62</v>
       </c>
       <c r="J88" t="s">
-        <v>748</v>
+        <v>833</v>
       </c>
       <c r="K88" t="s">
-        <v>749</v>
+        <v>834</v>
       </c>
       <c r="L88" t="s">
         <v>65</v>
       </c>
       <c r="M88" t="s">
-        <v>750</v>
+        <v>835</v>
       </c>
       <c r="N88" t="s">
         <v>67</v>
       </c>
       <c r="O88" t="s">
-        <v>751</v>
+        <v>836</v>
       </c>
       <c r="P88" t="s">
-        <v>752</v>
+        <v>837</v>
       </c>
       <c r="Q88" t="s">
         <v>70</v>
@@ -9353,11 +9632,11 @@
         <v>72</v>
       </c>
       <c r="U88" t="s">
-        <v>753</v>
+        <v>838</v>
       </c>
       <c r="V88" t="s"/>
       <c r="W88" t="s">
-        <v>754</v>
+        <v>839</v>
       </c>
       <c r="X88" t="s"/>
       <c r="Y88" t="s"/>
@@ -9369,7 +9648,7 @@
     </row>
     <row r="89" spans="1:28">
       <c r="A89" t="s">
-        <v>755</v>
+        <v>840</v>
       </c>
       <c r="B89" t="s">
         <v>55</v>
@@ -9378,7 +9657,7 @@
         <v>56</v>
       </c>
       <c r="D89" t="s">
-        <v>57</v>
+        <v>841</v>
       </c>
       <c r="E89" t="s">
         <v>58</v>
@@ -9396,25 +9675,25 @@
         <v>62</v>
       </c>
       <c r="J89" t="s">
-        <v>756</v>
+        <v>842</v>
       </c>
       <c r="K89" t="s">
-        <v>757</v>
+        <v>843</v>
       </c>
       <c r="L89" t="s">
         <v>65</v>
       </c>
       <c r="M89" t="s">
-        <v>758</v>
+        <v>844</v>
       </c>
       <c r="N89" t="s">
         <v>67</v>
       </c>
       <c r="O89" t="s">
-        <v>759</v>
+        <v>845</v>
       </c>
       <c r="P89" t="s">
-        <v>760</v>
+        <v>846</v>
       </c>
       <c r="Q89" t="s">
         <v>70</v>
@@ -9427,11 +9706,11 @@
         <v>72</v>
       </c>
       <c r="U89" t="s">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="V89" t="s"/>
       <c r="W89" t="s">
-        <v>762</v>
+        <v>848</v>
       </c>
       <c r="X89" t="s"/>
       <c r="Y89" t="s"/>
@@ -9443,7 +9722,7 @@
     </row>
     <row r="90" spans="1:28">
       <c r="A90" t="s">
-        <v>763</v>
+        <v>849</v>
       </c>
       <c r="B90" t="s">
         <v>55</v>
@@ -9452,7 +9731,7 @@
         <v>56</v>
       </c>
       <c r="D90" t="s">
-        <v>57</v>
+        <v>850</v>
       </c>
       <c r="E90" t="s">
         <v>58</v>
@@ -9470,25 +9749,25 @@
         <v>62</v>
       </c>
       <c r="J90" t="s">
-        <v>764</v>
+        <v>851</v>
       </c>
       <c r="K90" t="s">
-        <v>765</v>
+        <v>852</v>
       </c>
       <c r="L90" t="s">
         <v>65</v>
       </c>
       <c r="M90" t="s">
-        <v>766</v>
+        <v>853</v>
       </c>
       <c r="N90" t="s">
         <v>67</v>
       </c>
       <c r="O90" t="s">
-        <v>767</v>
+        <v>854</v>
       </c>
       <c r="P90" t="s">
-        <v>768</v>
+        <v>855</v>
       </c>
       <c r="Q90" t="s">
         <v>70</v>
@@ -9501,11 +9780,11 @@
         <v>72</v>
       </c>
       <c r="U90" t="s">
-        <v>769</v>
+        <v>856</v>
       </c>
       <c r="V90" t="s"/>
       <c r="W90" t="s">
-        <v>770</v>
+        <v>857</v>
       </c>
       <c r="X90" t="s"/>
       <c r="Y90" t="s"/>
@@ -9517,7 +9796,7 @@
     </row>
     <row r="91" spans="1:28">
       <c r="A91" t="s">
-        <v>771</v>
+        <v>858</v>
       </c>
       <c r="B91" t="s">
         <v>55</v>
@@ -9526,7 +9805,7 @@
         <v>56</v>
       </c>
       <c r="D91" t="s">
-        <v>57</v>
+        <v>859</v>
       </c>
       <c r="E91" t="s">
         <v>58</v>
@@ -9544,25 +9823,25 @@
         <v>62</v>
       </c>
       <c r="J91" t="s">
-        <v>772</v>
+        <v>860</v>
       </c>
       <c r="K91" t="s">
-        <v>773</v>
+        <v>861</v>
       </c>
       <c r="L91" t="s">
         <v>65</v>
       </c>
       <c r="M91" t="s">
-        <v>774</v>
+        <v>862</v>
       </c>
       <c r="N91" t="s">
         <v>67</v>
       </c>
       <c r="O91" t="s">
-        <v>775</v>
+        <v>863</v>
       </c>
       <c r="P91" t="s">
-        <v>776</v>
+        <v>864</v>
       </c>
       <c r="Q91" t="s">
         <v>70</v>
@@ -9575,11 +9854,11 @@
         <v>72</v>
       </c>
       <c r="U91" t="s">
-        <v>777</v>
+        <v>865</v>
       </c>
       <c r="V91" t="s"/>
       <c r="W91" t="s">
-        <v>778</v>
+        <v>866</v>
       </c>
       <c r="X91" t="s"/>
       <c r="Y91" t="s"/>
@@ -9591,7 +9870,7 @@
     </row>
     <row r="92" spans="1:28">
       <c r="A92" t="s">
-        <v>779</v>
+        <v>867</v>
       </c>
       <c r="B92" t="s">
         <v>55</v>
@@ -9600,7 +9879,7 @@
         <v>56</v>
       </c>
       <c r="D92" t="s">
-        <v>57</v>
+        <v>868</v>
       </c>
       <c r="E92" t="s">
         <v>58</v>
@@ -9618,25 +9897,25 @@
         <v>62</v>
       </c>
       <c r="J92" t="s">
-        <v>780</v>
+        <v>869</v>
       </c>
       <c r="K92" t="s">
-        <v>781</v>
+        <v>870</v>
       </c>
       <c r="L92" t="s">
         <v>65</v>
       </c>
       <c r="M92" t="s">
-        <v>782</v>
+        <v>871</v>
       </c>
       <c r="N92" t="s">
         <v>67</v>
       </c>
       <c r="O92" t="s">
-        <v>783</v>
+        <v>872</v>
       </c>
       <c r="P92" t="s">
-        <v>784</v>
+        <v>873</v>
       </c>
       <c r="Q92" t="s">
         <v>70</v>
@@ -9649,11 +9928,11 @@
         <v>72</v>
       </c>
       <c r="U92" t="s">
-        <v>785</v>
+        <v>874</v>
       </c>
       <c r="V92" t="s"/>
       <c r="W92" t="s">
-        <v>786</v>
+        <v>875</v>
       </c>
       <c r="X92" t="s"/>
       <c r="Y92" t="s"/>
@@ -9665,7 +9944,7 @@
     </row>
     <row r="93" spans="1:28">
       <c r="A93" t="s">
-        <v>787</v>
+        <v>876</v>
       </c>
       <c r="B93" t="s">
         <v>55</v>
@@ -9674,7 +9953,7 @@
         <v>56</v>
       </c>
       <c r="D93" t="s">
-        <v>57</v>
+        <v>877</v>
       </c>
       <c r="E93" t="s">
         <v>58</v>
@@ -9692,25 +9971,25 @@
         <v>62</v>
       </c>
       <c r="J93" t="s">
-        <v>788</v>
+        <v>878</v>
       </c>
       <c r="K93" t="s">
-        <v>789</v>
+        <v>879</v>
       </c>
       <c r="L93" t="s">
         <v>65</v>
       </c>
       <c r="M93" t="s">
-        <v>790</v>
+        <v>880</v>
       </c>
       <c r="N93" t="s">
         <v>67</v>
       </c>
       <c r="O93" t="s">
-        <v>791</v>
+        <v>881</v>
       </c>
       <c r="P93" t="s">
-        <v>792</v>
+        <v>882</v>
       </c>
       <c r="Q93" t="s">
         <v>70</v>
@@ -9723,11 +10002,11 @@
         <v>72</v>
       </c>
       <c r="U93" t="s">
-        <v>793</v>
+        <v>883</v>
       </c>
       <c r="V93" t="s"/>
       <c r="W93" t="s">
-        <v>794</v>
+        <v>884</v>
       </c>
       <c r="X93" t="s"/>
       <c r="Y93" t="s"/>
@@ -9739,7 +10018,7 @@
     </row>
     <row r="94" spans="1:28">
       <c r="A94" t="s">
-        <v>795</v>
+        <v>885</v>
       </c>
       <c r="B94" t="s">
         <v>55</v>
@@ -9748,7 +10027,7 @@
         <v>56</v>
       </c>
       <c r="D94" t="s">
-        <v>57</v>
+        <v>886</v>
       </c>
       <c r="E94" t="s">
         <v>58</v>
@@ -9766,25 +10045,25 @@
         <v>62</v>
       </c>
       <c r="J94" t="s">
-        <v>796</v>
+        <v>887</v>
       </c>
       <c r="K94" t="s">
-        <v>797</v>
+        <v>888</v>
       </c>
       <c r="L94" t="s">
         <v>65</v>
       </c>
       <c r="M94" t="s">
-        <v>798</v>
+        <v>889</v>
       </c>
       <c r="N94" t="s">
         <v>67</v>
       </c>
       <c r="O94" t="s">
-        <v>799</v>
+        <v>890</v>
       </c>
       <c r="P94" t="s">
-        <v>800</v>
+        <v>891</v>
       </c>
       <c r="Q94" t="s">
         <v>70</v>
@@ -9797,11 +10076,11 @@
         <v>72</v>
       </c>
       <c r="U94" t="s">
-        <v>801</v>
+        <v>892</v>
       </c>
       <c r="V94" t="s"/>
       <c r="W94" t="s">
-        <v>802</v>
+        <v>893</v>
       </c>
       <c r="X94" t="s"/>
       <c r="Y94" t="s"/>
@@ -9813,7 +10092,7 @@
     </row>
     <row r="95" spans="1:28">
       <c r="A95" t="s">
-        <v>803</v>
+        <v>894</v>
       </c>
       <c r="B95" t="s">
         <v>55</v>
@@ -9822,7 +10101,7 @@
         <v>56</v>
       </c>
       <c r="D95" t="s">
-        <v>57</v>
+        <v>895</v>
       </c>
       <c r="E95" t="s">
         <v>58</v>
@@ -9840,25 +10119,25 @@
         <v>62</v>
       </c>
       <c r="J95" t="s">
-        <v>804</v>
+        <v>896</v>
       </c>
       <c r="K95" t="s">
-        <v>805</v>
+        <v>897</v>
       </c>
       <c r="L95" t="s">
         <v>65</v>
       </c>
       <c r="M95" t="s">
-        <v>806</v>
+        <v>898</v>
       </c>
       <c r="N95" t="s">
         <v>67</v>
       </c>
       <c r="O95" t="s">
-        <v>807</v>
+        <v>899</v>
       </c>
       <c r="P95" t="s">
-        <v>808</v>
+        <v>900</v>
       </c>
       <c r="Q95" t="s">
         <v>70</v>
@@ -9871,11 +10150,11 @@
         <v>72</v>
       </c>
       <c r="U95" t="s">
-        <v>809</v>
+        <v>901</v>
       </c>
       <c r="V95" t="s"/>
       <c r="W95" t="s">
-        <v>810</v>
+        <v>902</v>
       </c>
       <c r="X95" t="s"/>
       <c r="Y95" t="s"/>
@@ -9887,7 +10166,7 @@
     </row>
     <row r="96" spans="1:28">
       <c r="A96" t="s">
-        <v>811</v>
+        <v>903</v>
       </c>
       <c r="B96" t="s">
         <v>55</v>
@@ -9896,7 +10175,7 @@
         <v>56</v>
       </c>
       <c r="D96" t="s">
-        <v>57</v>
+        <v>904</v>
       </c>
       <c r="E96" t="s">
         <v>58</v>
@@ -9914,25 +10193,25 @@
         <v>62</v>
       </c>
       <c r="J96" t="s">
-        <v>812</v>
+        <v>905</v>
       </c>
       <c r="K96" t="s">
-        <v>813</v>
+        <v>906</v>
       </c>
       <c r="L96" t="s">
         <v>65</v>
       </c>
       <c r="M96" t="s">
-        <v>814</v>
+        <v>907</v>
       </c>
       <c r="N96" t="s">
         <v>67</v>
       </c>
       <c r="O96" t="s">
-        <v>815</v>
+        <v>908</v>
       </c>
       <c r="P96" t="s">
-        <v>816</v>
+        <v>909</v>
       </c>
       <c r="Q96" t="s">
         <v>70</v>
@@ -9945,11 +10224,11 @@
         <v>72</v>
       </c>
       <c r="U96" t="s">
-        <v>817</v>
+        <v>910</v>
       </c>
       <c r="V96" t="s"/>
       <c r="W96" t="s">
-        <v>818</v>
+        <v>911</v>
       </c>
       <c r="X96" t="s"/>
       <c r="Y96" t="s"/>
@@ -9961,7 +10240,7 @@
     </row>
     <row r="97" spans="1:28">
       <c r="A97" t="s">
-        <v>819</v>
+        <v>912</v>
       </c>
       <c r="B97" t="s">
         <v>55</v>
@@ -9988,25 +10267,25 @@
         <v>62</v>
       </c>
       <c r="J97" t="s">
-        <v>820</v>
+        <v>913</v>
       </c>
       <c r="K97" t="s">
-        <v>821</v>
+        <v>914</v>
       </c>
       <c r="L97" t="s">
         <v>65</v>
       </c>
       <c r="M97" t="s">
-        <v>822</v>
+        <v>915</v>
       </c>
       <c r="N97" t="s">
         <v>67</v>
       </c>
       <c r="O97" t="s">
-        <v>823</v>
+        <v>916</v>
       </c>
       <c r="P97" t="s">
-        <v>824</v>
+        <v>917</v>
       </c>
       <c r="Q97" t="s">
         <v>70</v>
@@ -10019,11 +10298,11 @@
         <v>72</v>
       </c>
       <c r="U97" t="s">
-        <v>817</v>
+        <v>910</v>
       </c>
       <c r="V97" t="s"/>
       <c r="W97" t="s">
-        <v>825</v>
+        <v>918</v>
       </c>
       <c r="X97" t="s"/>
       <c r="Y97" t="s"/>

--- a/docs/collections/sokuchigenkozu/metadata/data.xlsx
+++ b/docs/collections/sokuchigenkozu/metadata/data.xlsx
@@ -863,7 +863,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/31606d80-64cd-7362-4302-35e960f900e8/manifest</t>
   </si>
   <si>
-    <t>[24]第三十七番 : 自田老村至唐舟之圖</t>
+    <t>[24]第三十七番 : 自田老村至唐丹之圖</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|第37番 自 田老村 至 唐舟之図</t>
@@ -1754,7 +1754,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a48739d6-5abb-3d54-0779-14cf9ab85764/manifest</t>
   </si>
   <si>
-    <t>[57]五十二番 : [高畑村-伊賀村]</t>
+    <t>[57]五十二番 : [高畑村,伊賀村, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|52番</t>
@@ -1781,7 +1781,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/75bedba5-7b1d-31fc-15be-b4a1a2c56171/manifest</t>
   </si>
   <si>
-    <t>[58]第五十五番 : [北比良村-橋爪村]</t>
+    <t>[58]第五十五番 : [北比良村, 橋爪村, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|55番</t>
@@ -1808,7 +1808,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cd181886-57c3-276c-2d0e-1417026a5c00/manifest</t>
   </si>
   <si>
-    <t>[59]五十八番 : [元比田村-片野村]</t>
+    <t>[59]五十八番 : [元比田村, 片野村, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|58番</t>
@@ -1835,7 +1835,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3b6bf159-46cb-0328-36bc-1860e2bf5e2b/manifest</t>
   </si>
   <si>
-    <t>[60]五十八番属 : [加賀白山-冨士庄山]</t>
+    <t>[60]五十八番属 : [加賀白山, 冨士社山]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|58番属</t>
@@ -1862,7 +1862,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7564e3ba-41f4-97f3-608c-7b8e524e4f09/manifest</t>
   </si>
   <si>
-    <t>[61]五十九番 : [片野村-大野村]</t>
+    <t>[61]五十九番 : [片野村, 大野村, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|59番</t>
@@ -1889,7 +1889,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b840752a-a204-65df-68c2-cc310f205a8e/manifest</t>
   </si>
   <si>
-    <t>[62]六十五番 : [大井宿-細畑村]</t>
+    <t>[62]六十五番 : [茄子川村, 細畑村, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|65番</t>
@@ -1916,7 +1916,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c9d00e33-76ea-a419-3f44-3bd087c8a560/manifest</t>
   </si>
   <si>
-    <t>[63]六十六番 : [曽代村-付知村]</t>
+    <t>[63]六十六番 : [曽代村, 付知村, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|66番</t>
@@ -1943,7 +1943,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d7ab22f9-773f-36f7-085d-3397c1a4362f/manifest</t>
   </si>
   <si>
-    <t>[64]七十番 : [芋木村-川田村]</t>
+    <t>[64]七十番 : [芋木村, 川田村, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|70番</t>
@@ -1970,7 +1970,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/05ec4eaf-700f-1568-247f-e938c63030d2/manifest</t>
   </si>
   <si>
-    <t>[65]七十二番 : [蒲原-法京村]</t>
+    <t>[65]七十二番 : [蒲原, 法京村, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|72番</t>
@@ -1997,7 +1997,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4056c19f-0495-a797-3f31-d1206b137cc4/manifest</t>
   </si>
   <si>
-    <t>[66]七十五番上 : [神津島, 式根島, 新島] : 三分啚</t>
+    <t>[66]七十五番上 : 三分啚 : [神津島, 式根島, 新島, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|75番上</t>
@@ -2051,7 +2051,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3957e247-27be-0ab1-a0d2-041e50263235/manifest</t>
   </si>
   <si>
-    <t>[68]八十七番 : [奈良井宿-馬場峠]</t>
+    <t>[68]八十七番 : [奈良井宿, 馬場峠, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|87番</t>
@@ -2078,7 +2078,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6620e99a-0352-5444-1048-a5f8b98e8235/manifest</t>
   </si>
   <si>
-    <t>[69]八十八番 : [八幡村-飯山町]</t>
+    <t>[69]八十八番 : [八幡村, 飯山町, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|88番</t>
@@ -2105,7 +2105,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/eec35f9a-57e0-06d7-8d66-9677b8ac08af/manifest</t>
   </si>
   <si>
-    <t>[70]八拾九番 : 三分啚 : [浅貝-布施]</t>
+    <t>[70]八拾九番 : 三分啚 : [浅貝, 布施, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|89番</t>
@@ -2132,7 +2132,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ebe69498-7390-234d-481e-637d73926ff5/manifest</t>
   </si>
   <si>
-    <t>[71]九十八番 : 三分圖 : [勝見-五十嵐濵]</t>
+    <t>[71]九十八番 : 三分圖 : [勝見, 五十嵐濵, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|98番</t>
@@ -2159,7 +2159,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0c01d6ca-5751-8947-8143-fcf0ee3d18f1/manifest</t>
   </si>
   <si>
-    <t>[72]百○○番 : 三分圖 : [関屋濵-塩谷]</t>
+    <t>[72]百○○番 : 三分圖 : [関屋濵, 塩谷, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|100番</t>
@@ -2186,7 +2186,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/440cf55b-033f-a5e6-9749-3e4b20a82b9f/manifest</t>
   </si>
   <si>
-    <t>[73]百〇一番 : 三分図 : [塩谷-笹川]</t>
+    <t>[73]百〇一番 : 三分図 : [塩谷, 笹川, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|101番</t>
@@ -2213,7 +2213,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f394d6ee-28b2-8e7e-0980-95fbb11e50c8/manifest</t>
   </si>
   <si>
-    <t>[74]百〇二番 : 三分図 : [大橋-原]</t>
+    <t>[74]百〇二番 : 三分図 : [大橋, 原, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|102番</t>
@@ -2240,7 +2240,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/51971aa4-1ab4-222c-20e5-938f734b1d19/manifest</t>
   </si>
   <si>
-    <t>[75]百〇三番 : 三分図 : [本内-尾濵]</t>
+    <t>[75]百〇三番 : 三分図 : [本内, 尾濵, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|103番</t>
@@ -2267,7 +2267,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fdfd4b34-8af3-213b-a143-4c1c0f1599fc/manifest</t>
   </si>
   <si>
-    <t>[76]百零四番 : 三分圖 : [笠石-五十邉]</t>
+    <t>[76]百零四番 : 三分圖 : [笠石, 五十邉, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|104番</t>
@@ -2294,7 +2294,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8cc0214b-4812-5a69-910d-419b4ef00881/manifest</t>
   </si>
   <si>
-    <t>[77]百〇五番 : 三分圖 : [尾濵-波倉]</t>
+    <t>[77]百〇五番 : 三分圖 : [尾濵, 波倉, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|105番</t>
@@ -2321,7 +2321,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/302596c6-66df-6dc6-8940-e0b19b735341/manifest</t>
   </si>
   <si>
-    <t>[78]百〇六番 : 三分図 : [原-寺子]</t>
+    <t>[78]百〇六番 : 三分図 : [原, 寺子, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|106番</t>
@@ -2348,7 +2348,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/841f16f0-2064-4702-76e0-ef363c378fae/manifest</t>
   </si>
   <si>
-    <t>[79]百〇七番 : [波倉村-赤濵村]</t>
+    <t>[79]百〇七番 : [波倉村, 赤濵村, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|107番</t>
@@ -2375,7 +2375,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/55052781-1682-201b-5052-e99de75156c6/manifest</t>
   </si>
   <si>
-    <t>[80]百一十一番 : [大橋村-林﨑村]</t>
+    <t>[80]百一十一番 : [大橋村, 林﨑村, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|111番</t>
@@ -2402,7 +2402,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c08c34e6-8e86-a080-6fc5-834e24bf1d90/manifest</t>
   </si>
   <si>
-    <t>[81]百一十二番 : 三分啚 : [岩沼-高清水]</t>
+    <t>[81]百一十二番 : 三分啚 : [岩沼 高清水, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|112番</t>
@@ -2429,7 +2429,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b06f7bc1-2145-a3b5-10e1-eeac7f120c17/manifest</t>
   </si>
   <si>
-    <t>[82]百一十三番 : [矢本村-岩尻村]</t>
+    <t>[82]百一十三番 : [矢本村, 岩尻村, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|113番</t>
@@ -2456,7 +2456,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d1ea08d2-8f12-653b-67a1-0a07549a789a/manifest</t>
   </si>
   <si>
-    <t>[83]百一十四番 : [笹川村-三瀬村]</t>
+    <t>[83]百一十四番 : [笹川村, 三瀬村, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|114番</t>
@@ -2483,7 +2483,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/158b9247-0412-3d99-3a57-a2bb12020b61/manifest</t>
   </si>
   <si>
-    <t>[84]百一十六番 : [林﨑村-上院内村]</t>
+    <t>[84]百一十六番 : [林﨑村, 上院内村, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|116番</t>
@@ -2510,7 +2510,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3e629cf3-2957-4a2f-78e3-7b47a83e1179/manifest</t>
   </si>
   <si>
-    <t>[85]百二十〇番 : [羅賀村-吉里々々村]</t>
+    <t>[85]百二十〇番 : [羅賀村, 吉里々村, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|120番</t>
@@ -2537,7 +2537,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7924e508-4765-997d-1f8b-de2d0ec171a6/manifest</t>
   </si>
   <si>
-    <t>[86]百二十一番 : [川又村-足軽町]</t>
+    <t>[86]百二十一番 : [川又村, 足軽町, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|121番</t>
@@ -2564,7 +2564,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/02219f57-a73d-861a-7ca5-f4396dd47bea/manifest</t>
   </si>
   <si>
-    <t>[87]百二十二番 : 三分図 : [樂師堂-金沢]</t>
+    <t>[87]百二十二番 : 三分図 : [樂師堂, 金沢, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|122番</t>
@@ -2591,7 +2591,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e0fbbbec-5e18-2b45-326b-02b328b18dd9/manifest</t>
   </si>
   <si>
-    <t>[88]百二十三番 : [新屋村-小濵村]</t>
+    <t>[88]百二十三番 : [新屋村, 小濵村, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|123番</t>
@@ -2645,7 +2645,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a652cee8-3920-a0e5-990e-8c6c86207d3a/manifest</t>
   </si>
   <si>
-    <t>[90]百二十四番 : 三分啚 : [八森-白沢]</t>
+    <t>[90]百二十四番 : 三分啚 : [八森, 白沢, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|124番</t>
@@ -2672,7 +2672,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b91a51eb-218c-6e4f-6230-3f646c479ae7/manifest</t>
   </si>
   <si>
-    <t>[91]百二十五番 : [カワサワ村-柳平村]</t>
+    <t>[91]百二十五番 : [カワサワ村, 柳平村, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|125番</t>
@@ -2699,7 +2699,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c743d416-9539-a67d-4977-afa42a4351e0/manifest</t>
   </si>
   <si>
-    <t>[92]百二十六番 : [金濵村-羅賀村]</t>
+    <t>[92]百二十六番 : [金濵村, 羅賀村, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|126番</t>
@@ -2726,7 +2726,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/adb193f6-244b-a461-5b01-251713c165c9/manifest</t>
   </si>
   <si>
-    <t>[93]百二十七番 : 三分図 : [天滿舘-三ノ戸]</t>
+    <t>[93]百二十七番 : 三分図 : [天滿舘, 三ノ戸, ほか]</t>
   </si>
   <si>
     <t>測地原稿図|伊能図|127番</t>

--- a/docs/collections/sokuchigenkozu/metadata/data.xlsx
+++ b/docs/collections/sokuchigenkozu/metadata/data.xlsx
@@ -2726,6 +2726,30 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/adb193f6-244b-a461-5b01-251713c165c9/manifest</t>
   </si>
   <si>
+    <t>[箱]</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b70814df-1a49-a11e-4070-852f6c5142ed.json</t>
+  </si>
+  <si>
+    <t>b70814df-1a49-a11e-4070-852f6c5142ed</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/sokuchigenkozu/document/b70814df-1a49-a11e-4070-852f6c5142ed</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c25e017c1d24a2d7176f865d3684eedf7bfa27f5.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/533852</t>
+  </si>
+  <si>
+    <t>10000093</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b70814df-1a49-a11e-4070-852f6c5142ed/manifest</t>
+  </si>
+  <si>
     <t>[93]百二十七番 : 三分図 : [天滿舘, 三ノ戸, ほか]</t>
   </si>
   <si>
@@ -2747,31 +2771,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/533851</t>
   </si>
   <si>
-    <t>10000093</t>
-  </si>
-  <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d5859699-9b10-607a-14b5-69a058799a03/manifest</t>
-  </si>
-  <si>
-    <t>[箱]</t>
-  </si>
-  <si>
-    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b70814df-1a49-a11e-4070-852f6c5142ed.json</t>
-  </si>
-  <si>
-    <t>b70814df-1a49-a11e-4070-852f6c5142ed</t>
-  </si>
-  <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/sokuchigenkozu/document/b70814df-1a49-a11e-4070-852f6c5142ed</t>
-  </si>
-  <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c25e017c1d24a2d7176f865d3684eedf7bfa27f5.jpg</t>
-  </si>
-  <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/533852</t>
-  </si>
-  <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b70814df-1a49-a11e-4070-852f6c5142ed/manifest</t>
   </si>
 </sst>
 </file>
@@ -10175,7 +10175,7 @@
         <v>56</v>
       </c>
       <c r="D96" t="s">
-        <v>904</v>
+        <v>57</v>
       </c>
       <c r="E96" t="s">
         <v>58</v>
@@ -10193,25 +10193,25 @@
         <v>62</v>
       </c>
       <c r="J96" t="s">
+        <v>904</v>
+      </c>
+      <c r="K96" t="s">
         <v>905</v>
-      </c>
-      <c r="K96" t="s">
-        <v>906</v>
       </c>
       <c r="L96" t="s">
         <v>65</v>
       </c>
       <c r="M96" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="N96" t="s">
         <v>67</v>
       </c>
       <c r="O96" t="s">
+        <v>907</v>
+      </c>
+      <c r="P96" t="s">
         <v>908</v>
-      </c>
-      <c r="P96" t="s">
-        <v>909</v>
       </c>
       <c r="Q96" t="s">
         <v>70</v>
@@ -10224,23 +10224,23 @@
         <v>72</v>
       </c>
       <c r="U96" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="V96" t="s"/>
       <c r="W96" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="X96" t="s"/>
       <c r="Y96" t="s"/>
       <c r="Z96" t="s"/>
       <c r="AA96" t="s"/>
       <c r="AB96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:28">
       <c r="A97" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B97" t="s">
         <v>55</v>
@@ -10249,7 +10249,7 @@
         <v>56</v>
       </c>
       <c r="D97" t="s">
-        <v>57</v>
+        <v>912</v>
       </c>
       <c r="E97" t="s">
         <v>58</v>
@@ -10298,7 +10298,7 @@
         <v>72</v>
       </c>
       <c r="U97" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="V97" t="s"/>
       <c r="W97" t="s">
@@ -10309,7 +10309,7 @@
       <c r="Z97" t="s"/>
       <c r="AA97" t="s"/>
       <c r="AB97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/collections/sokuchigenkozu/metadata/data.xlsx
+++ b/docs/collections/sokuchigenkozu/metadata/data.xlsx
@@ -2726,6 +2726,33 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/adb193f6-244b-a461-5b01-251713c165c9/manifest</t>
   </si>
   <si>
+    <t>[93]百二十七番 : 三分図 : [天滿舘, 三ノ戸, ほか]</t>
+  </si>
+  <si>
+    <t>測地原稿図|伊能図|127番</t>
+  </si>
+  <si>
+    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d5859699-9b10-607a-14b5-69a058799a03.json</t>
+  </si>
+  <si>
+    <t>d5859699-9b10-607a-14b5-69a058799a03</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/sokuchigenkozu/document/d5859699-9b10-607a-14b5-69a058799a03</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e3cd2d448f7de9a5e0ece4f53ed8205500fa55c2.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/533851</t>
+  </si>
+  <si>
+    <t>10000093</t>
+  </si>
+  <si>
+    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d5859699-9b10-607a-14b5-69a058799a03/manifest</t>
+  </si>
+  <si>
     <t>[箱]</t>
   </si>
   <si>
@@ -2744,34 +2771,7 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/533852</t>
   </si>
   <si>
-    <t>10000093</t>
-  </si>
-  <si>
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b70814df-1a49-a11e-4070-852f6c5142ed/manifest</t>
-  </si>
-  <si>
-    <t>[93]百二十七番 : 三分図 : [天滿舘, 三ノ戸, ほか]</t>
-  </si>
-  <si>
-    <t>測地原稿図|伊能図|127番</t>
-  </si>
-  <si>
-    <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d5859699-9b10-607a-14b5-69a058799a03.json</t>
-  </si>
-  <si>
-    <t>d5859699-9b10-607a-14b5-69a058799a03</t>
-  </si>
-  <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/sokuchigenkozu/document/d5859699-9b10-607a-14b5-69a058799a03</t>
-  </si>
-  <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e3cd2d448f7de9a5e0ece4f53ed8205500fa55c2.jpg</t>
-  </si>
-  <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/533851</t>
-  </si>
-  <si>
-    <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d5859699-9b10-607a-14b5-69a058799a03/manifest</t>
   </si>
 </sst>
 </file>
@@ -10175,7 +10175,7 @@
         <v>56</v>
       </c>
       <c r="D96" t="s">
-        <v>57</v>
+        <v>904</v>
       </c>
       <c r="E96" t="s">
         <v>58</v>
@@ -10193,25 +10193,25 @@
         <v>62</v>
       </c>
       <c r="J96" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="K96" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="L96" t="s">
         <v>65</v>
       </c>
       <c r="M96" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="N96" t="s">
         <v>67</v>
       </c>
       <c r="O96" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="P96" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="Q96" t="s">
         <v>70</v>
@@ -10224,23 +10224,23 @@
         <v>72</v>
       </c>
       <c r="U96" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="V96" t="s"/>
       <c r="W96" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="X96" t="s"/>
       <c r="Y96" t="s"/>
       <c r="Z96" t="s"/>
       <c r="AA96" t="s"/>
       <c r="AB96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:28">
       <c r="A97" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B97" t="s">
         <v>55</v>
@@ -10249,7 +10249,7 @@
         <v>56</v>
       </c>
       <c r="D97" t="s">
-        <v>912</v>
+        <v>57</v>
       </c>
       <c r="E97" t="s">
         <v>58</v>
@@ -10298,7 +10298,7 @@
         <v>72</v>
       </c>
       <c r="U97" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="V97" t="s"/>
       <c r="W97" t="s">
@@ -10309,7 +10309,7 @@
       <c r="Z97" t="s"/>
       <c r="AA97" t="s"/>
       <c r="AB97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
